--- a/Översikt EMMABODA.xlsx
+++ b/Översikt EMMABODA.xlsx
@@ -567,7 +567,7 @@
         <v>44314</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         <v>45377.5588425926</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45369</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45818</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>44811</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>44054</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44238</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44488</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>45335</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>45068.42262731482</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>44445</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>45161.33116898148</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>44762</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>44570.72098379629</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>44495</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>44120</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>44984.36140046296</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45229.67172453704</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>44966.54540509259</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>44405.32738425926</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>44140</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>44082</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>44089</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>44120.38783564815</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>44459.43425925926</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>44105</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>44379.56671296297</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>44530.4546875</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>44496.52702546296</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>44441.48626157407</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>44488</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>44764.45645833333</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>44120.39879629629</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>44405.31638888889</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>44405.31894675926</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>44405</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>44496.5110300926</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>44530.4562037037</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>44405.32319444444</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>44228</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44454.86018518519</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>44117.6835300926</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>44264.36884259259</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>44454</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>44529</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>44251</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>44490</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>44211</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>44110</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>44601.34255787037</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>44431</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>44600</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44383.5654050926</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>44097</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>44280.65521990741</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44251</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>44507</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>44507.56921296296</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>44507</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>44507</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>44297</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>44416</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44416</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>44442</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>44240</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>44238</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>44728.83878472223</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>44599.69461805555</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>44211</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>44691</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>44628.35012731481</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>44326.44194444444</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44504.38268518518</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>44387</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>44379</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>44383.6131712963</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>44515.44268518518</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>44851.40596064815</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>44071</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>44070</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>44860.88715277778</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>44239</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>44118</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>44082</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>44240.59631944444</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>44462.69965277778</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>44278</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>44523</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>44648.3578587963</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>44628</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44347.43119212963</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>44788.65715277778</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>44416</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>44382.6675925926</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>44361.39021990741</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>44347.44501157408</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>44405</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>44392.4420949074</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>44062</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>44627.34532407407</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>44075</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>44071</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>44112</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>44462</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>44109</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>44240.57777777778</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>44148</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>44768.83986111111</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>44120</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>44498</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>44851.49548611111</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>44529.29797453704</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>44249</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>44172</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>44277</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>44320</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>44208</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>44208</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>44385</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         <v>44347.43444444444</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>44813</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>44809.43158564815</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>44771</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>44202</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>44202</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>44412</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>44587.42887731481</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>44433</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>44251</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>44496</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>44466.39774305555</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>44507</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>44507</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>44487</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>44405</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>44405</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>44383.61637731481</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>44147</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         <v>44416</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>44628.36534722222</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>44652</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>44600</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>44421</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>44120</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>44600.45854166667</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>44074</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44501</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>44116.37994212963</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>44600.45505787037</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>44110</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>44256</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>44293</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>44148</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>44148</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>44841.3953125</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         <v>44852.48653935185</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>44334.61043981482</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>44847.55930555556</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>44148</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>44295</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>44743.42285879629</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>44839.33949074074</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>44382.66943287037</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>44180</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>44488</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>44223</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>44722.49396990741</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>44083</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>44452.30709490741</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>44210.32178240741</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>44238</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>44532.70575231482</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>44120.39627314815</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
         <v>44076</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>44083</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>44615</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>44655.9318287037</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>44385</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>44412</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>44470.31766203704</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>44622.48368055555</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>44593.62412037037</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>44652</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>44524.72388888889</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>44699.83193287037</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>44712.48467592592</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>44589.43354166667</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>44162.37409722222</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>44110</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>44820</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>44706</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>44383.559375</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>44383.61515046296</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>44167</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>44302.5521875</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>44551</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>44454</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>44340</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>44431.41373842592</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>44600.45703703703</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>44530</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>44284.40975694444</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>44302.54723379629</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>44725</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>45200.41958333334</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>45740.50775462963</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>45196.6208449074</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>45189.35297453704</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>44743.38194444445</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>44788.66310185185</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>44518</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>45222</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>45048.43734953704</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>44433</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>45187.44503472222</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>45211</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>45219</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>45335</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>45204</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>44879</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>45113</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>44095</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>45049</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>45606.56679398148</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>45641.73396990741</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>45190</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>45007.52546296296</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>44418.40890046296</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>45691.38957175926</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>45636.63569444444</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>44690.6797337963</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>44739.37986111111</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>44524</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>44078</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>45392.57234953704</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>45392.58719907407</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>45415</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>45211</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>45719</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>45348.45074074074</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>45069</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14980,7 +14980,7 @@
         <v>45069</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>45397.44292824074</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>45164.64133101852</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>45068.41424768518</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>45719</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>45078.59818287037</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>45755.52962962963</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>45111.65074074074</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>45411.45418981482</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>45772.39434027778</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         <v>45049.61376157407</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15617,7 +15617,7 @@
         <v>45211</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>44315</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>45727.45439814815</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>44771.43327546296</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         <v>45126.36510416667</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>44698.34013888889</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>45317.44657407407</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>45440</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>45422.39476851852</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>45084</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>45373.48118055556</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>44236.8744212963</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>45117</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>44382</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16420,7 +16420,7 @@
         <v>45229.67283564815</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>45099.49768518518</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>45385.48972222222</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>45204</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>45296</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>44593.62643518519</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45335.67450231482</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>44816.64091435185</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>44228</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>44608</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>45369.42106481481</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>45273.62960648148</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>45349.85878472222</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>45204</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>45595.51280092593</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>45376.6791087963</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>45107.60460648148</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>45433.48228009259</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         <v>44210</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17518,7 +17518,7 @@
         <v>45579.47649305555</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>45126.47204861111</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>44236.88402777778</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>45716.34835648148</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>45743.46313657407</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         <v>45237.5672337963</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45461.49600694444</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17917,7 +17917,7 @@
         <v>45740.51246527778</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>44759.39475694444</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>44861</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>45317.44828703703</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>44326.32891203704</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18202,7 +18202,7 @@
         <v>44326.34681712963</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>44531.67679398148</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>44504.38146990741</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>45103.68170138889</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>45474.4828587963</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>45104</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>45341.38545138889</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>44347.43795138889</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>45400.91444444445</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45665.4533912037</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>44907.44033564815</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>45126.47646990741</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>45202.46894675926</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>45740.36450231481</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>45700</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>45281</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>44449</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>45155</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         <v>45474.61877314815</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>45211.67291666667</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>45211</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>44159</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>45733.69460648148</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>44897.65846064815</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>45692.20631944444</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>45716.35474537037</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>45716.39373842593</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>45539.28254629629</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>44071</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>45126.47756944445</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>44959</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>44977.37475694445</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>45327.39255787037</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>45161.329375</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>45323.75855324074</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>44088</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>45273.62567129629</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>44519</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20383,7 +20383,7 @@
         <v>45126.38699074074</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>44728.83686342592</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20497,7 +20497,7 @@
         <v>45561</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>45477.50987268519</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>45093.61918981482</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>45514.38017361111</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20730,7 +20730,7 @@
         <v>45574.45165509259</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20787,7 +20787,7 @@
         <v>44951</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20844,7 +20844,7 @@
         <v>45771</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>44203.61291666667</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>45161</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>44519</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21077,7 +21077,7 @@
         <v>44852.57822916667</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>45121</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21191,7 +21191,7 @@
         <v>45341.37961805556</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>44530.5225462963</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>44979.50762731482</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         <v>44953</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21419,7 +21419,7 @@
         <v>45323.40695601852</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21476,7 +21476,7 @@
         <v>44953</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>44572</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         <v>45531.38554398148</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21647,7 +21647,7 @@
         <v>45600.65333333334</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>44400.37826388889</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>44223</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>44593.76921296296</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>45551</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>44404</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>45523.52064814815</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22046,7 +22046,7 @@
         <v>45750.91766203703</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22103,7 +22103,7 @@
         <v>45189.50841435185</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>45189.50895833333</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>45632</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45215</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>44949.42457175926</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45769.35443287037</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>45684.66949074074</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45624.64013888889</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>44550.40824074074</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>45777.58511574074</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>45099</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>45070.62878472222</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>45534.66148148148</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>45126.31585648148</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>45777.37217592593</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>45777.3700462963</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>45484.49533564815</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>45777.51607638889</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>44896.4815625</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>45351.58540509259</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>45779.45815972222</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>45779.46054398148</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>44900.36804398148</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>45537</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>45782.455</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>45562.50462962963</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>45003.90380787037</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>44984.39417824074</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>45019.67677083334</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>44980</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>44271</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23870,7 +23870,7 @@
         <v>45475.36099537037</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>44840</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>45783.6937962963</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>45783.68928240741</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>45107</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>45783.69173611111</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>45317.45069444444</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>45475.46671296296</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>45415.60552083333</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>45638</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45610.70957175926</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>45582</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>44893.57989583333</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24616,7 +24616,7 @@
         <v>45587.54915509259</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24673,7 +24673,7 @@
         <v>45132</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24730,7 +24730,7 @@
         <v>44683</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>45565.4407175926</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>45445.3777662037</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>44600.50372685185</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24958,7 +24958,7 @@
         <v>45548</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>45554</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>44895</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>44056</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>45349.64855324074</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25248,7 +25248,7 @@
         <v>44995</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25305,7 +25305,7 @@
         <v>45037.64929398148</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25362,7 +25362,7 @@
         <v>45155</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25419,7 +25419,7 @@
         <v>44897.66574074074</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>44982.67675925926</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25533,7 +25533,7 @@
         <v>45609.51984953704</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>45688</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>44949</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>45484.35097222222</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>45349.90940972222</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>45386.35418981482</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>44993</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25932,7 +25932,7 @@
         <v>45007.53736111111</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25989,7 +25989,7 @@
         <v>45433</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26046,7 +26046,7 @@
         <v>45775.59086805556</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26103,7 +26103,7 @@
         <v>45400.68645833333</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26160,7 +26160,7 @@
         <v>44453</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26217,7 +26217,7 @@
         <v>45566.63414351852</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26274,7 +26274,7 @@
         <v>45789.54855324074</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26331,7 +26331,7 @@
         <v>44580.64971064815</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26388,7 +26388,7 @@
         <v>45481.92570601852</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>45146.35854166667</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>45022.634375</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26559,7 +26559,7 @@
         <v>45022.64363425926</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>45400</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26673,7 +26673,7 @@
         <v>44839</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>44955</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>45714.62857638889</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26844,7 +26844,7 @@
         <v>45636.63883101852</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26901,7 +26901,7 @@
         <v>44494</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26958,7 +26958,7 @@
         <v>45098.91159722222</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27015,7 +27015,7 @@
         <v>45211</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>45706.44140046297</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27129,7 +27129,7 @@
         <v>45790.40994212963</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27186,7 +27186,7 @@
         <v>44445</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27243,7 +27243,7 @@
         <v>45559</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>45691.394375</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>45040</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>45709</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>45743</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>45554</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>45166</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>45166</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>45455.38807870371</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         <v>45252.41863425926</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27823,7 +27823,7 @@
         <v>45126</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27880,7 +27880,7 @@
         <v>45126</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27937,7 +27937,7 @@
         <v>45191.56679398148</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27994,7 +27994,7 @@
         <v>45126</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28051,7 +28051,7 @@
         <v>45392.58935185185</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28108,7 +28108,7 @@
         <v>44995.57965277778</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28165,7 +28165,7 @@
         <v>45205.49876157408</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28222,7 +28222,7 @@
         <v>44973.864375</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
         <v>45167.65172453703</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28341,7 +28341,7 @@
         <v>45681.58681712963</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>44594</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28455,7 +28455,7 @@
         <v>44524</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28512,7 +28512,7 @@
         <v>44978.31736111111</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28569,7 +28569,7 @@
         <v>45707</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>45763</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>45741.70216435185</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28740,7 +28740,7 @@
         <v>44953</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28797,7 +28797,7 @@
         <v>44690</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28854,7 +28854,7 @@
         <v>45795.67989583333</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28911,7 +28911,7 @@
         <v>45644.45738425926</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>45021.50722222222</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29025,7 +29025,7 @@
         <v>45021.50942129629</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>45078.5972337963</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>45078.59965277778</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>45084.66810185185</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>45835.51372685185</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>45048.435</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>45727.64369212963</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>45072</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>45622.56673611111</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>45159.4650925926</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>45238</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>45573.3758912037</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>44978.32152777778</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>45769.60783564814</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>45182</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>44299</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>44222</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>45225.62575231482</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>44748.54626157408</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>45062.65315972222</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>45327.37474537037</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>45063</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30294,7 +30294,7 @@
         <v>45797.45761574074</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>45191.58287037037</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30408,7 +30408,7 @@
         <v>44783.34944444444</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30465,7 +30465,7 @@
         <v>45621</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>45095</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>44777</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>44960</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>45091</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>44652</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>44665.90422453704</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>45362.96539351852</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30921,7 +30921,7 @@
         <v>45797.44099537037</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30978,7 +30978,7 @@
         <v>45230</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31035,7 +31035,7 @@
         <v>45009.46947916667</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31092,7 +31092,7 @@
         <v>45009</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>45800.58695601852</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>45800.5805787037</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>45841.36670138889</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>44376.82413194444</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31377,7 +31377,7 @@
         <v>45422.47181712963</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>45559.60966435185</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31491,7 +31491,7 @@
         <v>45841.44533564815</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31548,7 +31548,7 @@
         <v>45537</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>45232</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31662,7 +31662,7 @@
         <v>45084</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31719,7 +31719,7 @@
         <v>45355.42155092592</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31776,7 +31776,7 @@
         <v>44700.61766203704</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>44977</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31890,7 +31890,7 @@
         <v>45230.63987268518</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31947,7 +31947,7 @@
         <v>45182.57702546296</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>45776</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>45776</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32118,7 +32118,7 @@
         <v>45799.55665509259</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32175,7 +32175,7 @@
         <v>45665.45535879629</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>45841.44762731482</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>45841.65936342593</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44965.4890162037</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>45099.4612037037</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>45629.44709490741</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32522,7 +32522,7 @@
         <v>45845</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>44852.5103125</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>45258</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32693,7 +32693,7 @@
         <v>45392.5746412037</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>44699.83489583333</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32807,7 +32807,7 @@
         <v>45803.56060185185</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>45574.38966435185</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32921,7 +32921,7 @@
         <v>45009.36045138889</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>45009.40710648148</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>45107</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33092,7 +33092,7 @@
         <v>45148.51032407407</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33149,7 +33149,7 @@
         <v>44922.58392361111</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33206,7 +33206,7 @@
         <v>45846</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33263,7 +33263,7 @@
         <v>45804.56436342592</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>45804.35590277778</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33377,7 +33377,7 @@
         <v>44958</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33434,7 +33434,7 @@
         <v>45531.50122685185</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33491,7 +33491,7 @@
         <v>45126</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>45434.59488425926</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33605,7 +33605,7 @@
         <v>45845.41</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33662,7 +33662,7 @@
         <v>45805</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33719,7 +33719,7 @@
         <v>45805</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
         <v>44743.42150462963</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33833,7 +33833,7 @@
         <v>44619</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33890,7 +33890,7 @@
         <v>45092</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33947,7 +33947,7 @@
         <v>45092</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34004,7 +34004,7 @@
         <v>45408</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34061,7 +34061,7 @@
         <v>45229.52315972222</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34118,7 +34118,7 @@
         <v>45394</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>45515.76115740741</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34232,7 +34232,7 @@
         <v>45852.58133101852</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>45673.67064814815</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34346,7 +34346,7 @@
         <v>44728.36712962963</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34403,7 +34403,7 @@
         <v>44473</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
         <v>45851.91469907408</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34517,7 +34517,7 @@
         <v>44235</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>45079</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>45188</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>45188</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34755,7 +34755,7 @@
         <v>45400.62210648148</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34812,7 +34812,7 @@
         <v>45645.58637731482</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>45851.91112268518</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>45107.47519675926</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34983,7 +34983,7 @@
         <v>45614.54209490741</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35040,7 +35040,7 @@
         <v>44673.38012731481</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35097,7 +35097,7 @@
         <v>44273</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35154,7 +35154,7 @@
         <v>45113.63261574074</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>45852.5841087963</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35268,7 +35268,7 @@
         <v>45596.75166666666</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>45164.64883101852</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>44749.78425925926</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>45849.46575231481</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>44726</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>45102</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35610,7 +35610,7 @@
         <v>45615</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35667,7 +35667,7 @@
         <v>45707</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35724,7 +35724,7 @@
         <v>44802.69710648148</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35781,7 +35781,7 @@
         <v>45852</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35838,7 +35838,7 @@
         <v>45102</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35895,7 +35895,7 @@
         <v>45401.43559027778</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35952,7 +35952,7 @@
         <v>44729.41611111111</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>45722</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>45258.50520833334</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>45258</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36180,7 +36180,7 @@
         <v>45736.56527777778</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>45735.47873842593</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36294,7 +36294,7 @@
         <v>45856.47141203703</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>45855.72674768518</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36408,7 +36408,7 @@
         <v>44781</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36465,7 +36465,7 @@
         <v>45148.50620370371</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>45475.36554398148</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36579,7 +36579,7 @@
         <v>45716.5465625</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36636,7 +36636,7 @@
         <v>45813.45756944444</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36693,7 +36693,7 @@
         <v>44384</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36755,7 +36755,7 @@
         <v>45775.59498842592</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36812,7 +36812,7 @@
         <v>45818</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36869,7 +36869,7 @@
         <v>45818</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36926,7 +36926,7 @@
         <v>45757.63991898148</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36983,7 +36983,7 @@
         <v>44799.28053240741</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37040,7 +37040,7 @@
         <v>45772.39091435185</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37097,7 +37097,7 @@
         <v>45772.39609953704</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37154,7 +37154,7 @@
         <v>45818</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37211,7 +37211,7 @@
         <v>45726.59443287037</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37268,7 +37268,7 @@
         <v>44984.56648148148</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37325,7 +37325,7 @@
         <v>44761.65730324074</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37382,7 +37382,7 @@
         <v>44827</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37439,7 +37439,7 @@
         <v>45301</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37496,7 +37496,7 @@
         <v>45113.64193287037</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37553,7 +37553,7 @@
         <v>45818</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>45727.45094907407</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>45309.61168981482</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37724,7 +37724,7 @@
         <v>45742.80981481481</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>45126.475625</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>44683.43862268519</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>45861.33920138889</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37952,7 +37952,7 @@
         <v>45819.69038194444</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38009,7 +38009,7 @@
         <v>45307.37699074074</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38066,7 +38066,7 @@
         <v>44349.62881944444</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>45716.34990740741</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>45190</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>45722</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>45310.58383101852</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>45477.69497685185</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38413,7 +38413,7 @@
         <v>45445.39274305556</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38470,7 +38470,7 @@
         <v>44851.49424768519</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38527,7 +38527,7 @@
         <v>45089.38663194444</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>45021.67435185185</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>45825.73362268518</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38698,7 +38698,7 @@
         <v>45826.36164351852</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38755,7 +38755,7 @@
         <v>45826.73186342593</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38812,7 +38812,7 @@
         <v>45826.35939814815</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38869,7 +38869,7 @@
         <v>45826.3639699074</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>45826.36921296296</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38983,7 +38983,7 @@
         <v>45067</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39040,7 +39040,7 @@
         <v>44893.48324074074</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39097,7 +39097,7 @@
         <v>45637.57834490741</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39154,7 +39154,7 @@
         <v>44278.36359953704</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39211,7 +39211,7 @@
         <v>45825.44528935185</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39268,7 +39268,7 @@
         <v>45867.57765046296</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39325,7 +39325,7 @@
         <v>45749.44238425926</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39382,7 +39382,7 @@
         <v>45826.35645833334</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39439,7 +39439,7 @@
         <v>45825.4341087963</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39496,7 +39496,7 @@
         <v>45615</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39553,7 +39553,7 @@
         <v>45716</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39610,7 +39610,7 @@
         <v>45716</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39667,7 +39667,7 @@
         <v>45028</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39724,7 +39724,7 @@
         <v>45159.46884259259</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>45772.39268518519</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39838,7 +39838,7 @@
         <v>44769.56326388889</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>45551.56715277778</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39957,7 +39957,7 @@
         <v>45832.38621527778</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40014,7 +40014,7 @@
         <v>45187.47203703703</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>45832.7072800926</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40128,7 +40128,7 @@
         <v>45401.4321412037</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40185,7 +40185,7 @@
         <v>44851.4281712963</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40242,7 +40242,7 @@
         <v>45196</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40299,7 +40299,7 @@
         <v>45863</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>45832.40292824074</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>45857</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>45392.58570601852</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>44897.54603009259</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>45323.39561342593</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40641,7 +40641,7 @@
         <v>44487.60532407407</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40698,7 +40698,7 @@
         <v>45323</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40755,7 +40755,7 @@
         <v>45524.50288194444</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>45637.58159722222</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40869,7 +40869,7 @@
         <v>44424</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40926,7 +40926,7 @@
         <v>45466.85056712963</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40983,7 +40983,7 @@
         <v>45327.39550925926</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>44488</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41102,7 +41102,7 @@
         <v>45296</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>45743</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41216,7 +41216,7 @@
         <v>44235</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>44993.56126157408</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         <v>44424</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>44143</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>44530.53258101852</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>44586</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>44278</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>44416</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>44447</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>44589.42831018518</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>44405.3347337963</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>45524.58461805555</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>44507</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44893.78201388889</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>44938.51150462963</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>44979.50945601852</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>45606.57038194445</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>45370.74839120371</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>45091.60043981481</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>45149.35745370371</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42361,7 +42361,7 @@
         <v>45191.37449074074</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42418,7 +42418,7 @@
         <v>44239</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>45155</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>45251.67181712963</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>44930.5281712963</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42646,7 +42646,7 @@
         <v>45181.58443287037</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>44728.36835648148</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>45425.51765046296</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>45036.45335648148</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>44834.45706018519</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>45051</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>45051.4380787037</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>45590.56064814814</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>44808.80826388889</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>44126.66101851852</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>44944</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43273,7 +43273,7 @@
         <v>45048</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>44487</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43392,7 +43392,7 @@
         <v>45514.3787037037</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43449,7 +43449,7 @@
         <v>45514.3809375</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43506,7 +43506,7 @@
         <v>45514.38158564815</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43563,7 +43563,7 @@
         <v>45625</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>45076.58376157407</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43682,7 +43682,7 @@
         <v>45392.57063657408</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
         <v>45217</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>45688</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43853,7 +43853,7 @@
         <v>44455</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43915,7 +43915,7 @@
         <v>45740.50475694444</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43972,7 +43972,7 @@
         <v>45117</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44029,7 +44029,7 @@
         <v>45180</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44086,7 +44086,7 @@
         <v>45668.41509259259</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44143,7 +44143,7 @@
         <v>45714</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44200,7 +44200,7 @@
         <v>44239</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44257,7 +44257,7 @@
         <v>44145</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>44054</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44371,7 +44371,7 @@
         <v>44207.35459490741</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>45757.64254629629</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44485,7 +44485,7 @@
         <v>45349.81209490741</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44542,7 +44542,7 @@
         <v>45349.86459490741</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>45641.74149305555</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>44791.33793981482</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>45310.58832175926</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>44911</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>45728</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44884,7 +44884,7 @@
         <v>45394.41221064814</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>44900</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>

--- a/Översikt EMMABODA.xlsx
+++ b/Översikt EMMABODA.xlsx
@@ -567,7 +567,7 @@
         <v>44314</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         <v>45377.5588425926</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45369</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45818</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>44811</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>44054</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44238</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44488</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>45335</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>45068.42262731482</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>44445</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>45161.33116898148</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>44762</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>44570.72098379629</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>44495</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>44120</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>44984.36140046296</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45229.67172453704</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>44966.54540509259</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>44405.32738425926</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>44140</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>44082</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>44089</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>44120.38783564815</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>44459.43425925926</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>44105</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>44379.56671296297</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>44530.4546875</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>44496.52702546296</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>44441.48626157407</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>44488</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>44764.45645833333</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>44120.39879629629</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>44405.31638888889</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>44405.31894675926</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>44405</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>44496.5110300926</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>44530.4562037037</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>44405.32319444444</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>44228</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44454.86018518519</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>44117.6835300926</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>44264.36884259259</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>44454</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>44529</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>44251</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>44490</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>44211</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>44110</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>44601.34255787037</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>44431</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>44600</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44383.5654050926</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>44097</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>44280.65521990741</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44251</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>44507</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>44507.56921296296</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>44507</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>44507</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>44297</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>44416</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44416</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>44442</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>44240</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>44238</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>44728.83878472223</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>44599.69461805555</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>44211</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>44691</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>44628.35012731481</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>44326.44194444444</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44504.38268518518</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>44387</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>44379</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>44383.6131712963</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>44515.44268518518</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>44851.40596064815</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>44071</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>44070</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>44860.88715277778</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>44239</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>44118</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>44082</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>44240.59631944444</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>44462.69965277778</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>44278</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>44523</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>44648.3578587963</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>44628</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44347.43119212963</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>44788.65715277778</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>44416</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>44382.6675925926</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>44361.39021990741</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>44347.44501157408</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>44405</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>44392.4420949074</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>44062</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>44627.34532407407</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>44075</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>44071</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>44112</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>44462</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>44109</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>44240.57777777778</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>44148</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>44768.83986111111</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>44120</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>44498</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>44851.49548611111</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>44529.29797453704</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>44249</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>44172</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>44277</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>44320</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>44208</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>44208</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>44385</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         <v>44347.43444444444</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>44813</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>44809.43158564815</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>44771</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>44202</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>44202</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         <v>44412</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>44587.42887731481</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>44433</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>44251</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>44496</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>44466.39774305555</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>44507</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>44507</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>44487</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>44405</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>44405</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>44383.61637731481</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>44147</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         <v>44416</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>44628.36534722222</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>44652</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>44600</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         <v>44421</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>44120</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>44600.45854166667</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>44074</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44501</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>44116.37994212963</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>44600.45505787037</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>44110</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>44256</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>44293</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>44148</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>44148</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>44841.3953125</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         <v>44852.48653935185</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>44334.61043981482</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>44847.55930555556</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>44148</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>44295</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>44743.42285879629</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>44839.33949074074</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>44382.66943287037</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>44180</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>44488</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>44223</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>44722.49396990741</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>44083</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>44452.30709490741</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>44210.32178240741</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>44238</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>44532.70575231482</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>44120.39627314815</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
         <v>44076</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>44083</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>44615</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>44655.9318287037</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>44385</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>44412</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>44470.31766203704</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>44622.48368055555</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>44593.62412037037</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>44652</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>44524.72388888889</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>44699.83193287037</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>44712.48467592592</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>44589.43354166667</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>44162.37409722222</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>44110</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>44820</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>44706</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>44383.559375</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>44383.61515046296</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>44167</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>44302.5521875</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>44551</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>44454</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>44340</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>44431.41373842592</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>44600.45703703703</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>44530</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>44284.40975694444</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>44302.54723379629</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>44725</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>45200.41958333334</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>45740.50775462963</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>45196.6208449074</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>45189.35297453704</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>44743.38194444445</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>44788.66310185185</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>44518</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>45222</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>45048.43734953704</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>44433</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>45187.44503472222</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>45211</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>45219</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>45335</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>45204</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>44879</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>45113</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>44095</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>45049</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>45606.56679398148</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>45641.73396990741</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>45190</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>45007.52546296296</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>44418.40890046296</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>45691.38957175926</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>45636.63569444444</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>44690.6797337963</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>44739.37986111111</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>44524</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>44078</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>45392.57234953704</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>45392.58719907407</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>45415</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>45211</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>45719</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>45348.45074074074</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>45069</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14980,7 +14980,7 @@
         <v>45069</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>45397.44292824074</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15094,7 +15094,7 @@
         <v>45164.64133101852</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15151,7 +15151,7 @@
         <v>45068.41424768518</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>45719</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>45078.59818287037</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>45755.52962962963</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>45111.65074074074</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>45411.45418981482</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>45772.39434027778</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         <v>45049.61376157407</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15617,7 +15617,7 @@
         <v>45211</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>44315</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>45727.45439814815</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>44771.43327546296</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         <v>45126.36510416667</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>44698.34013888889</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>45317.44657407407</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>45440</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>45422.39476851852</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>45084</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>45373.48118055556</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16249,7 +16249,7 @@
         <v>44236.8744212963</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>45117</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>44382</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16420,7 +16420,7 @@
         <v>45229.67283564815</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>45099.49768518518</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>45385.48972222222</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>45204</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>45296</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>44593.62643518519</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45335.67450231482</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>44816.64091435185</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>44228</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>44608</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
         <v>45369.42106481481</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>45273.62960648148</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>45349.85878472222</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>45204</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>45595.51280092593</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>45376.6791087963</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>45107.60460648148</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>45433.48228009259</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         <v>44210</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17518,7 +17518,7 @@
         <v>45579.47649305555</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>45126.47204861111</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>44236.88402777778</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>45716.34835648148</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>45743.46313657407</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         <v>45237.5672337963</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45461.49600694444</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17917,7 +17917,7 @@
         <v>45740.51246527778</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>44759.39475694444</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>44861</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>45317.44828703703</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>44326.32891203704</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18202,7 +18202,7 @@
         <v>44326.34681712963</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>44531.67679398148</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>44504.38146990741</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>45103.68170138889</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>45474.4828587963</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>45104</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>45341.38545138889</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>44347.43795138889</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>45400.91444444445</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45665.4533912037</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>44907.44033564815</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>45126.47646990741</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>45202.46894675926</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>45740.36450231481</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>45700</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>45281</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>44449</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>45155</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         <v>45474.61877314815</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>45211.67291666667</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>45211</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>44159</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>45733.69460648148</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>44897.65846064815</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>45692.20631944444</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>45716.35474537037</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>45716.39373842593</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>45539.28254629629</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>44071</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>45126.47756944445</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>44959</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>44977.37475694445</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>45327.39255787037</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>45161.329375</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>45323.75855324074</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>44088</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>45273.62567129629</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>44519</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20383,7 +20383,7 @@
         <v>45126.38699074074</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>44728.83686342592</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20497,7 +20497,7 @@
         <v>45561</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>45477.50987268519</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>45093.61918981482</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>45514.38017361111</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20730,7 +20730,7 @@
         <v>45574.45165509259</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20787,7 +20787,7 @@
         <v>44951</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20844,7 +20844,7 @@
         <v>45771</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>44203.61291666667</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>45161</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>44519</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21077,7 +21077,7 @@
         <v>44852.57822916667</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>45121</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21191,7 +21191,7 @@
         <v>45341.37961805556</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>44530.5225462963</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>44979.50762731482</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         <v>44953</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21419,7 +21419,7 @@
         <v>45323.40695601852</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21476,7 +21476,7 @@
         <v>44953</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>44572</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         <v>45531.38554398148</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21647,7 +21647,7 @@
         <v>45600.65333333334</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>44400.37826388889</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>44223</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>44593.76921296296</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>45551</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>44404</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>45523.52064814815</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22046,7 +22046,7 @@
         <v>45750.91766203703</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22103,7 +22103,7 @@
         <v>45189.50841435185</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>45189.50895833333</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>45632</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45215</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>44949.42457175926</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45769.35443287037</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>45684.66949074074</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45624.64013888889</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>44550.40824074074</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>45777.58511574074</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>45099</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>45070.62878472222</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>45534.66148148148</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>45126.31585648148</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>45777.37217592593</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>45777.3700462963</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>45484.49533564815</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>45777.51607638889</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>44896.4815625</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>45351.58540509259</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>45779.45815972222</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>45779.46054398148</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>44900.36804398148</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>45537</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>45782.455</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>45562.50462962963</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>45003.90380787037</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>44984.39417824074</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>45019.67677083334</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>44980</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>44271</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23870,7 +23870,7 @@
         <v>45475.36099537037</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>44840</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>45783.6937962963</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>45783.68928240741</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>45107</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>45783.69173611111</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>45317.45069444444</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>45475.46671296296</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>45415.60552083333</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>45638</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45610.70957175926</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>45582</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>44893.57989583333</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24616,7 +24616,7 @@
         <v>45587.54915509259</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24673,7 +24673,7 @@
         <v>45132</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24730,7 +24730,7 @@
         <v>44683</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>45565.4407175926</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>45445.3777662037</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>44600.50372685185</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24958,7 +24958,7 @@
         <v>45548</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>45554</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>44895</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>44056</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>45349.64855324074</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25248,7 +25248,7 @@
         <v>44995</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25305,7 +25305,7 @@
         <v>45037.64929398148</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25362,7 +25362,7 @@
         <v>45155</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25419,7 +25419,7 @@
         <v>44897.66574074074</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>44982.67675925926</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25533,7 +25533,7 @@
         <v>45609.51984953704</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>45688</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>44949</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>45484.35097222222</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>45349.90940972222</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>45386.35418981482</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>44993</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25932,7 +25932,7 @@
         <v>45007.53736111111</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25989,7 +25989,7 @@
         <v>45433</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26046,7 +26046,7 @@
         <v>45775.59086805556</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26103,7 +26103,7 @@
         <v>45400.68645833333</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26160,7 +26160,7 @@
         <v>44453</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26217,7 +26217,7 @@
         <v>45566.63414351852</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26274,7 +26274,7 @@
         <v>45789.54855324074</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26331,7 +26331,7 @@
         <v>44580.64971064815</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26388,7 +26388,7 @@
         <v>45481.92570601852</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>45146.35854166667</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>45022.634375</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26559,7 +26559,7 @@
         <v>45022.64363425926</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>45400</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26673,7 +26673,7 @@
         <v>44839</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>44955</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>45714.62857638889</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26844,7 +26844,7 @@
         <v>45636.63883101852</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26901,7 +26901,7 @@
         <v>44494</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26958,7 +26958,7 @@
         <v>45098.91159722222</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27015,7 +27015,7 @@
         <v>45211</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>45706.44140046297</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27129,7 +27129,7 @@
         <v>45790.40994212963</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27186,7 +27186,7 @@
         <v>44445</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27243,7 +27243,7 @@
         <v>45559</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>45691.394375</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>45040</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>45709</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>45743</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>45554</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>45166</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>45166</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>45455.38807870371</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         <v>45252.41863425926</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27823,7 +27823,7 @@
         <v>45126</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27880,7 +27880,7 @@
         <v>45126</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27937,7 +27937,7 @@
         <v>45191.56679398148</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27994,7 +27994,7 @@
         <v>45126</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28051,7 +28051,7 @@
         <v>45392.58935185185</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28108,7 +28108,7 @@
         <v>44995.57965277778</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28165,7 +28165,7 @@
         <v>45205.49876157408</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28222,7 +28222,7 @@
         <v>44973.864375</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
         <v>45167.65172453703</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28341,7 +28341,7 @@
         <v>45681.58681712963</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>44594</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28455,7 +28455,7 @@
         <v>44524</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28512,7 +28512,7 @@
         <v>44978.31736111111</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28569,7 +28569,7 @@
         <v>45707</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>45763</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>45741.70216435185</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28740,7 +28740,7 @@
         <v>44953</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28797,7 +28797,7 @@
         <v>44690</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28854,7 +28854,7 @@
         <v>45795.67989583333</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28911,7 +28911,7 @@
         <v>45644.45738425926</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>45021.50722222222</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29025,7 +29025,7 @@
         <v>45021.50942129629</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>45078.5972337963</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>45078.59965277778</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>45084.66810185185</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29263,7 +29263,7 @@
         <v>45835.51372685185</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>45048.435</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>45727.64369212963</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>45072</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>45622.56673611111</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>45159.4650925926</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>45238</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>45573.3758912037</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>44978.32152777778</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>45769.60783564814</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>45182</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>44299</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>44222</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>45225.62575231482</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>44748.54626157408</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>45062.65315972222</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>45327.37474537037</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>45063</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30294,7 +30294,7 @@
         <v>45797.45761574074</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>45191.58287037037</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30408,7 +30408,7 @@
         <v>44783.34944444444</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30465,7 +30465,7 @@
         <v>45621</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>45095</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>44777</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>44960</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>45091</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>44652</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>44665.90422453704</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>45362.96539351852</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30921,7 +30921,7 @@
         <v>45797.44099537037</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30978,7 +30978,7 @@
         <v>45230</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31035,7 +31035,7 @@
         <v>45009.46947916667</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31092,7 +31092,7 @@
         <v>45009</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>45800.58695601852</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>45800.5805787037</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>45841.36670138889</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>44376.82413194444</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31377,7 +31377,7 @@
         <v>45422.47181712963</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>45559.60966435185</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31491,7 +31491,7 @@
         <v>45841.44533564815</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31548,7 +31548,7 @@
         <v>45537</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>45232</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31662,7 +31662,7 @@
         <v>45084</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31719,7 +31719,7 @@
         <v>45355.42155092592</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31776,7 +31776,7 @@
         <v>44700.61766203704</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>44977</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31890,7 +31890,7 @@
         <v>45230.63987268518</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31947,7 +31947,7 @@
         <v>45182.57702546296</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>45776</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>45776</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32118,7 +32118,7 @@
         <v>45799.55665509259</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32175,7 +32175,7 @@
         <v>45665.45535879629</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>45841.44762731482</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>45841.65936342593</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44965.4890162037</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>45099.4612037037</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>45629.44709490741</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32522,7 +32522,7 @@
         <v>45845</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>44852.5103125</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>45258</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32693,7 +32693,7 @@
         <v>45392.5746412037</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>44699.83489583333</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32807,7 +32807,7 @@
         <v>45803.56060185185</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>45574.38966435185</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32921,7 +32921,7 @@
         <v>45009.36045138889</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>45009.40710648148</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>45107</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33092,7 +33092,7 @@
         <v>45148.51032407407</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33149,7 +33149,7 @@
         <v>44922.58392361111</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33206,7 +33206,7 @@
         <v>45846</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33263,7 +33263,7 @@
         <v>45804.56436342592</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>45804.35590277778</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33377,7 +33377,7 @@
         <v>44958</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33434,7 +33434,7 @@
         <v>45531.50122685185</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33491,7 +33491,7 @@
         <v>45126</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>45434.59488425926</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33605,7 +33605,7 @@
         <v>45845.41</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33662,7 +33662,7 @@
         <v>45805</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33719,7 +33719,7 @@
         <v>45805</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
         <v>44743.42150462963</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33833,7 +33833,7 @@
         <v>44619</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33890,7 +33890,7 @@
         <v>45092</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33947,7 +33947,7 @@
         <v>45092</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34004,7 +34004,7 @@
         <v>45408</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34061,7 +34061,7 @@
         <v>45229.52315972222</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34118,7 +34118,7 @@
         <v>45394</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>45515.76115740741</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34232,7 +34232,7 @@
         <v>45852.58133101852</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>45673.67064814815</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34346,7 +34346,7 @@
         <v>44728.36712962963</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34403,7 +34403,7 @@
         <v>44473</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
         <v>45851.91469907408</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34517,7 +34517,7 @@
         <v>44235</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>45079</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>45188</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34693,7 +34693,7 @@
         <v>45188</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34755,7 +34755,7 @@
         <v>45400.62210648148</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34812,7 +34812,7 @@
         <v>45645.58637731482</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>45851.91112268518</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>45107.47519675926</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34983,7 +34983,7 @@
         <v>45614.54209490741</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35040,7 +35040,7 @@
         <v>44673.38012731481</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35097,7 +35097,7 @@
         <v>44273</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35154,7 +35154,7 @@
         <v>45113.63261574074</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35211,7 +35211,7 @@
         <v>45852.5841087963</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35268,7 +35268,7 @@
         <v>45596.75166666666</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>45164.64883101852</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>44749.78425925926</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>45849.46575231481</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>44726</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>45102</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35610,7 +35610,7 @@
         <v>45615</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35667,7 +35667,7 @@
         <v>45707</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35724,7 +35724,7 @@
         <v>44802.69710648148</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35781,7 +35781,7 @@
         <v>45852</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35838,7 +35838,7 @@
         <v>45102</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35895,7 +35895,7 @@
         <v>45401.43559027778</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35952,7 +35952,7 @@
         <v>44729.41611111111</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36009,7 +36009,7 @@
         <v>45722</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>45258.50520833334</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>45258</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36180,7 +36180,7 @@
         <v>45736.56527777778</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>45735.47873842593</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36294,7 +36294,7 @@
         <v>45856.47141203703</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>45855.72674768518</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36408,7 +36408,7 @@
         <v>44781</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36465,7 +36465,7 @@
         <v>45148.50620370371</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>45475.36554398148</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36579,7 +36579,7 @@
         <v>45716.5465625</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36636,7 +36636,7 @@
         <v>45813.45756944444</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36693,7 +36693,7 @@
         <v>44384</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36755,7 +36755,7 @@
         <v>45775.59498842592</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36812,7 +36812,7 @@
         <v>45818</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36869,7 +36869,7 @@
         <v>45818</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36926,7 +36926,7 @@
         <v>45757.63991898148</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36983,7 +36983,7 @@
         <v>44799.28053240741</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37040,7 +37040,7 @@
         <v>45772.39091435185</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37097,7 +37097,7 @@
         <v>45772.39609953704</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37154,7 +37154,7 @@
         <v>45818</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37211,7 +37211,7 @@
         <v>45726.59443287037</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37268,7 +37268,7 @@
         <v>44984.56648148148</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37325,7 +37325,7 @@
         <v>44761.65730324074</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37382,7 +37382,7 @@
         <v>44827</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37439,7 +37439,7 @@
         <v>45301</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37496,7 +37496,7 @@
         <v>45113.64193287037</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37553,7 +37553,7 @@
         <v>45818</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>45727.45094907407</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>45309.61168981482</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37724,7 +37724,7 @@
         <v>45742.80981481481</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>45126.475625</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>44683.43862268519</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>45861.33920138889</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37952,7 +37952,7 @@
         <v>45819.69038194444</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38009,7 +38009,7 @@
         <v>45307.37699074074</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38066,7 +38066,7 @@
         <v>44349.62881944444</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>45716.34990740741</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>45190</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>45722</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>45310.58383101852</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>45477.69497685185</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38413,7 +38413,7 @@
         <v>45445.39274305556</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38470,7 +38470,7 @@
         <v>44851.49424768519</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38527,7 +38527,7 @@
         <v>45089.38663194444</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>45021.67435185185</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>45825.73362268518</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38698,7 +38698,7 @@
         <v>45826.36164351852</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38755,7 +38755,7 @@
         <v>45826.73186342593</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38812,7 +38812,7 @@
         <v>45826.35939814815</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38869,7 +38869,7 @@
         <v>45826.3639699074</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>45826.36921296296</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38983,7 +38983,7 @@
         <v>45067</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39040,7 +39040,7 @@
         <v>44893.48324074074</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39097,7 +39097,7 @@
         <v>45637.57834490741</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39154,7 +39154,7 @@
         <v>44278.36359953704</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39211,7 +39211,7 @@
         <v>45825.44528935185</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39268,7 +39268,7 @@
         <v>45867.57765046296</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39325,7 +39325,7 @@
         <v>45749.44238425926</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39382,7 +39382,7 @@
         <v>45826.35645833334</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39439,7 +39439,7 @@
         <v>45825.4341087963</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39496,7 +39496,7 @@
         <v>45615</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39553,7 +39553,7 @@
         <v>45716</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39610,7 +39610,7 @@
         <v>45716</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39667,7 +39667,7 @@
         <v>45028</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39724,7 +39724,7 @@
         <v>45159.46884259259</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>45772.39268518519</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39838,7 +39838,7 @@
         <v>44769.56326388889</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>45551.56715277778</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39957,7 +39957,7 @@
         <v>45832.38621527778</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40014,7 +40014,7 @@
         <v>45187.47203703703</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>45832.7072800926</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40128,7 +40128,7 @@
         <v>45401.4321412037</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40185,7 +40185,7 @@
         <v>44851.4281712963</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40242,7 +40242,7 @@
         <v>45196</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40299,7 +40299,7 @@
         <v>45863</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>45832.40292824074</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>45857</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>45392.58570601852</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>44897.54603009259</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>45323.39561342593</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40641,7 +40641,7 @@
         <v>44487.60532407407</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40698,7 +40698,7 @@
         <v>45323</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40755,7 +40755,7 @@
         <v>45524.50288194444</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>45637.58159722222</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40869,7 +40869,7 @@
         <v>44424</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40926,7 +40926,7 @@
         <v>45466.85056712963</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40983,7 +40983,7 @@
         <v>45327.39550925926</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>44488</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41102,7 +41102,7 @@
         <v>45296</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41159,7 +41159,7 @@
         <v>45743</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41216,7 +41216,7 @@
         <v>44235</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>44993.56126157408</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         <v>44424</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>44143</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>44530.53258101852</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41506,7 +41506,7 @@
         <v>44586</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>44278</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41620,7 +41620,7 @@
         <v>44416</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>44447</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>44589.42831018518</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>44405.3347337963</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>45524.58461805555</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>44507</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44893.78201388889</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>44938.51150462963</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>44979.50945601852</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>45606.57038194445</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>45370.74839120371</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>45091.60043981481</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>45149.35745370371</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42361,7 +42361,7 @@
         <v>45191.37449074074</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42418,7 +42418,7 @@
         <v>44239</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>45155</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>45251.67181712963</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>44930.5281712963</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42646,7 +42646,7 @@
         <v>45181.58443287037</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>44728.36835648148</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>45425.51765046296</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>45036.45335648148</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>44834.45706018519</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>45051</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>45051.4380787037</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>45590.56064814814</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>44808.80826388889</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>44126.66101851852</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>44944</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43273,7 +43273,7 @@
         <v>45048</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>44487</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43392,7 +43392,7 @@
         <v>45514.3787037037</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43449,7 +43449,7 @@
         <v>45514.3809375</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43506,7 +43506,7 @@
         <v>45514.38158564815</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43563,7 +43563,7 @@
         <v>45625</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>45076.58376157407</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43682,7 +43682,7 @@
         <v>45392.57063657408</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
         <v>45217</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>45688</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43853,7 +43853,7 @@
         <v>44455</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43915,7 +43915,7 @@
         <v>45740.50475694444</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43972,7 +43972,7 @@
         <v>45117</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44029,7 +44029,7 @@
         <v>45180</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44086,7 +44086,7 @@
         <v>45668.41509259259</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44143,7 +44143,7 @@
         <v>45714</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44200,7 +44200,7 @@
         <v>44239</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44257,7 +44257,7 @@
         <v>44145</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>44054</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44371,7 +44371,7 @@
         <v>44207.35459490741</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>45757.64254629629</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44485,7 +44485,7 @@
         <v>45349.81209490741</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44542,7 +44542,7 @@
         <v>45349.86459490741</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>45641.74149305555</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44656,7 +44656,7 @@
         <v>44791.33793981482</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44713,7 +44713,7 @@
         <v>45310.58832175926</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>44911</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>45728</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44884,7 +44884,7 @@
         <v>45394.41221064814</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>44900</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>

--- a/Översikt EMMABODA.xlsx
+++ b/Översikt EMMABODA.xlsx
@@ -567,7 +567,7 @@
         <v>44314</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         <v>45377.5588425926</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45369</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45818</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>44811</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>44238</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44445</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44570.72098379629</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45161.33116898148</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>44762</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>44120</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>44984.36140046296</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>45229.67172453704</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>44495</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>44966.54540509259</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>44488</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45335</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45068.42262731482</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>44405.32738425926</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>44140</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>44089</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>44082</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>44120.38783564815</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>44459.43425925926</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>44105</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>44379.56671296297</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>44530.4546875</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>44496.52702546296</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44441.48626157407</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>44488</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>44764.45645833333</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>44405.31638888889</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>44530.4562037037</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>44405.31894675926</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44405</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44496.5110300926</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44120.39879629629</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>44405.32319444444</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44228</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>44454.86018518519</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>44117.6835300926</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>44264.36884259259</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>44454</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>44529</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>44251</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>44490</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44431</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>44110</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>44601.34255787037</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>44211</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>44600</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>44383.5654050926</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>44097</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>44251</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>44507</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>44507.56921296296</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>44507</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>44507</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>44280.65521990741</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>44297</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>44416</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44416</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44442</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>44240</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>44728.83878472223</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>44599.69461805555</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>44238</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>44211</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>44691</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>44628.35012731481</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>44326.44194444444</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>44504.38268518518</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>44387</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>44379</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>44383.6131712963</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>44515.44268518518</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>44851.40596064815</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>44071</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>44860.88715277778</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>44070</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>44239</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>44082</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>44118</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>44462.69965277778</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>44240.59631944444</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>44648.3578587963</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>44523</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>44278</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>44628</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44788.65715277778</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>44347.43119212963</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>44416</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>44382.6675925926</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>44361.39021990741</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>44347.44501157408</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>44405</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>44062</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>44627.34532407407</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>44392.4420949074</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>44075</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44071</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>44109</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44112</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>44462</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>44240.57777777778</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>44148</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>44498</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>44120</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>44768.83986111111</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44851.49548611111</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>44529.29797453704</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>44249</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>44172</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>44277</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>44320</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>44208</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>44208</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>44385</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>44347.43444444444</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>44813</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>44809.43158564815</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>44771</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>44202</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>44202</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>44412</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>44587.42887731481</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44433</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
         <v>44251</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>44496</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>44466.39774305555</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>44507</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44507</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>44487</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>44405</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>44405</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>44383.61637731481</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>44147</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>44416</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44628.36534722222</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>44652</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44600</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>44421</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>44120</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>44600.45505787037</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>44110</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44501</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>44293</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>44148</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         <v>44148</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>44852.48653935185</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>44334.61043981482</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>44847.55930555556</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>44295</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>44148</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>44839.33949074074</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>44743.42285879629</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>44382.66943287037</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>44180</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>44488</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>44722.49396990741</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>44083</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>44223</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>44532.70575231482</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>44120.39627314815</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>44452.30709490741</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>44210.32178240741</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>44076</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>44238</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>44083</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>44615</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>44385</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>44412</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>44655.9318287037</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>44470.31766203704</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>44622.48368055555</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44593.62412037037</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>44652</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44524.72388888889</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>44699.83193287037</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>44712.48467592592</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>44162.37409722222</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>44589.43354166667</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>44383.559375</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>44383.61515046296</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>44820</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>44706</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>44110</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>44302.5521875</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>44167</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>44551</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>44340</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>44431.41373842592</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>44600.45703703703</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>44454</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>44284.40975694444</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>44302.54723379629</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>44725</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>44743.38194444445</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>44600.45854166667</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>44074</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>44530</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>44116.37994212963</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>44788.66310185185</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>44256</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>45719</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12890,7 +12890,7 @@
         <v>45048.43734953704</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>45187.44503472222</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>45219</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>45539.28254629629</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>45078.59818287037</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13180,7 +13180,7 @@
         <v>45335</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>45126.47756944445</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         <v>44959</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>45411.45418981482</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>45204</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13470,7 +13470,7 @@
         <v>44977.37475694445</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45327.39255787037</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>44315</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>44841.3953125</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>45561</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>44771.43327546296</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>45190</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>45440</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>45422.39476851852</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45126.38699074074</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         <v>45574.45165509259</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>44728.83686342592</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>44236.8744212963</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14226,7 +14226,7 @@
         <v>45093.61918981482</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>44382</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>45229.67283564815</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>45385.48972222222</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>44739.37986111111</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>44979.50762731482</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>44078</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>45771</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>44203.61291666667</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>45211</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>45719</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>45348.45074074074</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>45296</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>45069</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>45069</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>44852.57822916667</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>45397.44292824074</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>45121</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>45341.37961805556</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>45551</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>45523.52064814815</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>45215</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>44949.42457175926</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>45684.66949074074</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>44953</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>45323.40695601852</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>44953</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>45624.64013888889</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>44572</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>45777.58511574074</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>45534.66148148148</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>45777.37217592593</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>45777.3700462963</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>45531.38554398148</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45600.65333333334</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>45484.49533564815</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>45777.51607638889</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>44223</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>45351.58540509259</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>44593.76921296296</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>45779.45815972222</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>45779.46054398148</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>45750.91766203703</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>45769.35443287037</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>45782.455</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>45126.31585648148</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>45003.90380787037</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>44984.39417824074</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>45019.67677083334</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17019,7 +17019,7 @@
         <v>44980</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17076,7 +17076,7 @@
         <v>44271</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>45783.6937962963</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>45783.68928240741</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>45107</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>45783.69173611111</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>45317.45069444444</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>44840</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17480,7 +17480,7 @@
         <v>45415.60552083333</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>45638</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>45475.46671296296</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>45610.70957175926</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>45582</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>45565.4407175926</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>45132</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>45445.3777662037</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>45548</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>44600.50372685185</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>44895</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18107,7 +18107,7 @@
         <v>45037.64929398148</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>45609.51984953704</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45688</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>44982.67675925926</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>45484.35097222222</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18392,7 +18392,7 @@
         <v>45386.35418981482</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>45775.59086805556</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>44453</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>45566.63414351852</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18620,7 +18620,7 @@
         <v>45789.54855324074</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>45481.92570601852</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>44993</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18791,7 +18791,7 @@
         <v>45433</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>45400</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>45146.35854166667</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>45790.40994212963</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19019,7 +19019,7 @@
         <v>45714.62857638889</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>44494</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>45455.38807870371</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>45559</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>45376.6791087963</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>45743</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>45795.67989583333</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>45126.47204861111</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>45126</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>45126</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>45191.56679398148</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>45126</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>45205.49876157408</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45167.65172453703</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>45797.45761574074</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19879,7 +19879,7 @@
         <v>45681.58681712963</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19936,7 +19936,7 @@
         <v>45797.44099537037</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>45800.58695601852</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20050,7 +20050,7 @@
         <v>45800.5805787037</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>45537</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>45741.70216435185</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>44977</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>45644.45738425926</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>45799.55665509259</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>45665.45535879629</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>45078.5972337963</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>45078.59965277778</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>45084.66810185185</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>45845</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>45727.64369212963</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20744,7 +20744,7 @@
         <v>45072</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20801,7 +20801,7 @@
         <v>45622.56673611111</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>45159.4650925926</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>45573.3758912037</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>45803.56060185185</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>44299</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>45225.62575231482</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>45846</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>45804.56436342592</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>45804.35590277778</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>44958</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>45327.37474537037</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>45845.41</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>45063</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>44783.34944444444</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>45621</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21661,7 +21661,7 @@
         <v>45461.49600694444</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>45091</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>44861</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>44652</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>44665.90422453704</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21946,7 +21946,7 @@
         <v>44326.32891203704</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>44326.34681712963</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         <v>45230</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>44376.82413194444</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         <v>44347.43795138889</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>45852.58133101852</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>45232</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>45400.91444444445</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22402,7 +22402,7 @@
         <v>44907.44033564815</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>45474.61877314815</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>45851.91469907408</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>45182.57702546296</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>44071</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>45392.5746412037</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44699.83489583333</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>45161.329375</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>45323.75855324074</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>44088</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22982,7 +22982,7 @@
         <v>45148.51032407407</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>45273.62567129629</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45851.91112268518</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>45531.50122685185</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>45126</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23272,7 +23272,7 @@
         <v>45434.59488425926</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>45477.50987268519</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23386,7 +23386,7 @@
         <v>45852.5841087963</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>45514.38017361111</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23500,7 +23500,7 @@
         <v>44619</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23557,7 +23557,7 @@
         <v>45849.46575231481</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>44951</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23671,7 +23671,7 @@
         <v>45852</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>45161</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>45408</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23847,7 +23847,7 @@
         <v>44519</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         <v>45394</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>44530.5225462963</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>44728.36712962963</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>44400.37826388889</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>45856.47141203703</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>44404</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24246,7 +24246,7 @@
         <v>45855.72674768518</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24303,7 +24303,7 @@
         <v>45189.50841435185</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>45189.50895833333</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24417,7 +24417,7 @@
         <v>45632</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>44550.40824074074</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>45099</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>45070.62878472222</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>45813.45756944444</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>45188</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24764,7 +24764,7 @@
         <v>45188</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24826,7 +24826,7 @@
         <v>44896.4815625</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>44900.36804398148</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24940,7 +24940,7 @@
         <v>45537</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>45400.62210648148</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>45562.50462962963</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>45818</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>45818</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>45818</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>45475.36099537037</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>45107.47519675926</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>45818</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>44673.38012731481</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44273</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44893.57989583333</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>45587.54915509259</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44683</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>45164.64883101852</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44749.78425925926</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>44726</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>45707</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>44802.69710648148</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45861.33920138889</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>45819.69038194444</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>45401.43559027778</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>45258.50520833334</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>45258</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>45736.56527777778</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>45735.47873842593</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>45554</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>45349.64855324074</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>44995</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         <v>45825.73362268518</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26655,7 +26655,7 @@
         <v>45826.36164351852</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         <v>45826.73186342593</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>45826.35939814815</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>45826.3639699074</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26883,7 +26883,7 @@
         <v>45155</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26940,7 +26940,7 @@
         <v>45826.36921296296</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26997,7 +26997,7 @@
         <v>44897.66574074074</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>45825.44528935185</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>45867.57765046296</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>45475.36554398148</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>45716.5465625</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>44949</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>45826.35645833334</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>45825.4341087963</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>44384</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27515,7 +27515,7 @@
         <v>45349.90940972222</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>45775.59498842592</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27629,7 +27629,7 @@
         <v>45007.53736111111</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27686,7 +27686,7 @@
         <v>45615</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>45400.68645833333</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>45757.63991898148</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>44799.28053240741</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>45772.39091435185</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>45772.39609953704</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>44580.64971064815</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>44827</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>45301</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>45022.634375</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>45022.64363425926</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>45727.45094907407</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>45309.61168981482</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28427,7 +28427,7 @@
         <v>45832.38621527778</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>44839</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28541,7 +28541,7 @@
         <v>44955</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>45832.7072800926</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28655,7 +28655,7 @@
         <v>45126.475625</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28712,7 +28712,7 @@
         <v>45863</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28769,7 +28769,7 @@
         <v>45307.37699074074</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>45832.40292824074</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>45857</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>45716.34990740741</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>45636.63883101852</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>45190</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45098.91159722222</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>45211</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>45310.58383101852</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>45477.69497685185</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29344,7 +29344,7 @@
         <v>45706.44140046297</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29401,7 +29401,7 @@
         <v>44851.49424768519</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29458,7 +29458,7 @@
         <v>44445</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>45089.38663194444</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29572,7 +29572,7 @@
         <v>44893.48324074074</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29629,7 +29629,7 @@
         <v>45691.394375</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>45040</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>45159.46884259259</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>44769.56326388889</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>45551.56715277778</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>45709</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>45187.47203703703</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>45401.4321412037</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>44851.4281712963</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>45835.51372685185</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>45196</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>45392.58570601852</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>45554</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>45166</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>45166</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>45881.41793981481</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>45252.41863425926</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>44897.54603009259</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>45392.58935185185</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>44995.57965277778</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>44973.864375</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>45323.39561342593</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>45881.37207175926</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>44487.60532407407</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>44594</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>45323</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>44524</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>45524.50288194444</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>44978.31736111111</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
         <v>45707</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31354,7 +31354,7 @@
         <v>45763</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>44953</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>44690</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>45021.50722222222</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>45021.50942129629</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31639,7 +31639,7 @@
         <v>45637.58159722222</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>45841.44533564815</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>45841.44762731482</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         <v>44424</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>45466.85056712963</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>45776</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>45776</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>45805</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>45805</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>45327.39550925926</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>44488</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>45296</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>45048.435</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32385,7 +32385,7 @@
         <v>45884.31863425926</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>45841.65936342593</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>45743</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32556,7 +32556,7 @@
         <v>44235</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>45238</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>45841.36670138889</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>44978.32152777778</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>45769.60783564814</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>45182</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>44993.56126157408</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>44222</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33012,7 +33012,7 @@
         <v>44424</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33069,7 +33069,7 @@
         <v>44143</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>44748.54626157408</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>45062.65315972222</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33245,7 +33245,7 @@
         <v>44530.53258101852</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33302,7 +33302,7 @@
         <v>44586</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33359,7 +33359,7 @@
         <v>45191.58287037037</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33416,7 +33416,7 @@
         <v>44278</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33473,7 +33473,7 @@
         <v>45095</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>44416</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33587,7 +33587,7 @@
         <v>44447</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>44777</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>44589.42831018518</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>44960</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>44405.3347337963</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33872,7 +33872,7 @@
         <v>45362.96539351852</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>45524.58461805555</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>45009.46947916667</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>45009</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34100,7 +34100,7 @@
         <v>44507</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34157,7 +34157,7 @@
         <v>45422.47181712963</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>45559.60966435185</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>45084</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>45355.42155092592</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>44893.78201388889</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>44700.61766203704</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34499,7 +34499,7 @@
         <v>44938.51150462963</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>45230.63987268518</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>44979.50945601852</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>44965.4890162037</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>45099.4612037037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>45606.57038194445</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>45629.44709490741</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34903,7 +34903,7 @@
         <v>44852.5103125</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>45258</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>45574.38966435185</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35074,7 +35074,7 @@
         <v>45370.74839120371</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35131,7 +35131,7 @@
         <v>45009.36045138889</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>45009.40710648148</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35245,7 +35245,7 @@
         <v>45107</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35302,7 +35302,7 @@
         <v>45091.60043981481</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>45149.35745370371</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>45191.37449074074</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35473,7 +35473,7 @@
         <v>44922.58392361111</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>44743.42150462963</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35587,7 +35587,7 @@
         <v>44239</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>45155</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>45251.67181712963</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>44930.5281712963</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>45092</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>45092</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35929,7 +35929,7 @@
         <v>45181.58443287037</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35986,7 +35986,7 @@
         <v>45229.52315972222</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36043,7 +36043,7 @@
         <v>44728.36835648148</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>45515.76115740741</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>45425.51765046296</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         <v>45036.45335648148</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36271,7 +36271,7 @@
         <v>44834.45706018519</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>45673.67064814815</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36385,7 +36385,7 @@
         <v>44473</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36442,7 +36442,7 @@
         <v>44235</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36499,7 +36499,7 @@
         <v>45051</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36556,7 +36556,7 @@
         <v>45051.4380787037</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36613,7 +36613,7 @@
         <v>45079</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36670,7 +36670,7 @@
         <v>45590.56064814814</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36727,7 +36727,7 @@
         <v>44808.80826388889</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36784,7 +36784,7 @@
         <v>45645.58637731482</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36841,7 +36841,7 @@
         <v>44126.66101851852</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36898,7 +36898,7 @@
         <v>45614.54209490741</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36955,7 +36955,7 @@
         <v>44944</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37012,7 +37012,7 @@
         <v>45048</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>44487</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>45113.63261574074</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>45514.3787037037</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>45514.3809375</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>45514.38158564815</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37359,7 +37359,7 @@
         <v>45596.75166666666</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37416,7 +37416,7 @@
         <v>45625</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37478,7 +37478,7 @@
         <v>45102</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         <v>45615</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37592,7 +37592,7 @@
         <v>45076.58376157407</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37649,7 +37649,7 @@
         <v>45392.57063657408</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37706,7 +37706,7 @@
         <v>45217</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37763,7 +37763,7 @@
         <v>45102</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37820,7 +37820,7 @@
         <v>44729.41611111111</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>45688</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37934,7 +37934,7 @@
         <v>44455</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37996,7 +37996,7 @@
         <v>45722</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>45740.50475694444</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>45117</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>45180</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>45668.41509259259</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>45714</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>44239</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>44145</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>44781</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38509,7 +38509,7 @@
         <v>45148.50620370371</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38566,7 +38566,7 @@
         <v>44207.35459490741</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38623,7 +38623,7 @@
         <v>45757.64254629629</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38680,7 +38680,7 @@
         <v>45349.81209490741</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>45349.86459490741</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>45641.74149305555</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38851,7 +38851,7 @@
         <v>45726.59443287037</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38908,7 +38908,7 @@
         <v>44984.56648148148</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38965,7 +38965,7 @@
         <v>44761.65730324074</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>45113.64193287037</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>45742.80981481481</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39136,7 +39136,7 @@
         <v>44791.33793981482</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39193,7 +39193,7 @@
         <v>44683.43862268519</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39250,7 +39250,7 @@
         <v>45310.58832175926</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>44911</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39364,7 +39364,7 @@
         <v>45728</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39421,7 +39421,7 @@
         <v>45394.41221064814</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39478,7 +39478,7 @@
         <v>44349.62881944444</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         <v>45722</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39592,7 +39592,7 @@
         <v>44900</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>45445.39274305556</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>45021.67435185185</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>45189.35297453704</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>45067</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>45637.57834490741</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>44278.36359953704</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>45749.44238425926</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>45716</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>45716</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>45113</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>45028</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
         <v>45606.56679398148</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>45641.73396990741</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>45007.52546296296</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>45636.63569444444</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>45772.39268518519</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>45392.57234953704</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>45392.58719907407</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40675,7 +40675,7 @@
         <v>45200.41958333334</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40732,7 +40732,7 @@
         <v>45740.50775462963</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>45196.6208449074</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         <v>45164.64133101852</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40903,7 +40903,7 @@
         <v>44518</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40960,7 +40960,7 @@
         <v>45222</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>44433</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41074,7 +41074,7 @@
         <v>45211</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>44879</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>44095</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41245,7 +41245,7 @@
         <v>45049</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>45211</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41359,7 +41359,7 @@
         <v>44418.40890046296</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41416,7 +41416,7 @@
         <v>45126.36510416667</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41473,7 +41473,7 @@
         <v>45691.38957175926</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>44698.34013888889</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>44690.6797337963</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>45317.44657407407</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>44524</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>45415</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>45373.48118055556</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41872,7 +41872,7 @@
         <v>45068.41424768518</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45755.52962962963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41991,7 +41991,7 @@
         <v>45111.65074074074</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>45204</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>45772.39434027778</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42167,7 +42167,7 @@
         <v>45049.61376157407</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>45335.67450231482</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42281,7 +42281,7 @@
         <v>45727.45439814815</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42338,7 +42338,7 @@
         <v>44228</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42395,7 +42395,7 @@
         <v>45369.42106481481</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
         <v>45273.62960648148</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45084</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45204</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42633,7 +42633,7 @@
         <v>45595.51280092593</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>45433.48228009259</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>45117</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45579.47649305555</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>45099.49768518518</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>45716.34835648148</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>45237.5672337963</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>44593.62643518519</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>44531.67679398148</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>44504.38146990741</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43203,7 +43203,7 @@
         <v>45103.68170138889</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>44816.64091435185</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>45474.4828587963</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>44608</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43431,7 +43431,7 @@
         <v>45341.38545138889</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43488,7 +43488,7 @@
         <v>45665.4533912037</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43545,7 +43545,7 @@
         <v>45126.47646990741</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43602,7 +43602,7 @@
         <v>45349.85878472222</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43659,7 +43659,7 @@
         <v>45202.46894675926</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43716,7 +43716,7 @@
         <v>45740.36450231481</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>45700</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43830,7 +43830,7 @@
         <v>45281</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43887,7 +43887,7 @@
         <v>45107.60460648148</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43944,7 +43944,7 @@
         <v>44449</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44001,7 +44001,7 @@
         <v>45155</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44058,7 +44058,7 @@
         <v>44210</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44115,7 +44115,7 @@
         <v>44236.88402777778</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44172,7 +44172,7 @@
         <v>44897.65846064815</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44229,7 +44229,7 @@
         <v>45743.46313657407</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44286,7 +44286,7 @@
         <v>45692.20631944444</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>45716.35474537037</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44400,7 +44400,7 @@
         <v>45716.39373842593</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44457,7 +44457,7 @@
         <v>45740.51246527778</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>44759.39475694444</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44571,7 +44571,7 @@
         <v>45317.44828703703</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44628,7 +44628,7 @@
         <v>45104</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>45211.67291666667</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44742,7 +44742,7 @@
         <v>45211</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44799,7 +44799,7 @@
         <v>44159</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44856,7 +44856,7 @@
         <v>45733.69460648148</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>44519</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>

--- a/Översikt EMMABODA.xlsx
+++ b/Översikt EMMABODA.xlsx
@@ -567,7 +567,7 @@
         <v>44314</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         <v>45377.5588425926</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45369</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45818</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>44811</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>44238</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44445</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44570.72098379629</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45161.33116898148</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>44762</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>44120</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>44984.36140046296</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>45229.67172453704</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>44495</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>44966.54540509259</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>44488</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45335</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45068.42262731482</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>44405.32738425926</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>44140</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>44089</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>44082</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>44120.38783564815</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>44459.43425925926</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>44105</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>44379.56671296297</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>44530.4546875</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>44496.52702546296</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44441.48626157407</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>44488</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>44764.45645833333</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>44405.31638888889</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>44530.4562037037</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>44405.31894675926</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44405</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44496.5110300926</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>44120.39879629629</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>44405.32319444444</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44228</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>44454.86018518519</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>44117.6835300926</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>44264.36884259259</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>44454</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>44529</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>44251</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>44490</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44431</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>44110</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>44601.34255787037</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>44211</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>44600</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>44383.5654050926</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>44097</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>44251</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>44507</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>44507.56921296296</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>44507</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>44507</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>44280.65521990741</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>44297</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>44416</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44416</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44442</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>44240</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>44728.83878472223</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>44599.69461805555</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>44238</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>44211</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>44691</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>44628.35012731481</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>44326.44194444444</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>44504.38268518518</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>44387</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>44379</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>44383.6131712963</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>44515.44268518518</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>44851.40596064815</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>44071</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>44860.88715277778</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>44070</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>44239</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>44082</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>44118</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>44462.69965277778</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>44240.59631944444</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>44648.3578587963</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>44523</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>44278</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>44628</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44788.65715277778</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>44347.43119212963</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>44416</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>44382.6675925926</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>44361.39021990741</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>44347.44501157408</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>44405</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>44062</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>44627.34532407407</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>44392.4420949074</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>44075</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44071</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>44109</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44112</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>44462</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>44240.57777777778</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>44148</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>44498</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>44120</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>44768.83986111111</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44851.49548611111</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>44529.29797453704</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>44249</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>44172</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>44277</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>44320</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>44208</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>44208</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>44385</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>44347.43444444444</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>44813</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>44809.43158564815</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>44771</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>44202</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>44202</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>44412</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>44587.42887731481</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44433</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
         <v>44251</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>44496</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>44466.39774305555</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>44507</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44507</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>44487</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>44405</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>44405</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>44383.61637731481</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>44147</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>44416</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44628.36534722222</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>44652</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44600</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>44421</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>44120</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>44600.45505787037</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>44110</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44501</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>44293</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>44148</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         <v>44148</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>44852.48653935185</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>44334.61043981482</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>44847.55930555556</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>44295</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>44148</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>44839.33949074074</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>44743.42285879629</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>44382.66943287037</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>44180</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>44488</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>44722.49396990741</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>44083</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>44223</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>44532.70575231482</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>44120.39627314815</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>44452.30709490741</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>44210.32178240741</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>44076</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>44238</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>44083</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>44615</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>44385</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>44412</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>44655.9318287037</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>44470.31766203704</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>44622.48368055555</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44593.62412037037</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>44652</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44524.72388888889</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>44699.83193287037</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>44712.48467592592</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>44162.37409722222</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>44589.43354166667</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>44383.559375</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>44383.61515046296</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>44820</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>44706</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>44110</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>44302.5521875</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>44167</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>44551</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>44340</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>44431.41373842592</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>44600.45703703703</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>44454</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>44284.40975694444</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>44302.54723379629</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>44725</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>44743.38194444445</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>44600.45854166667</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>44074</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>44530</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>44116.37994212963</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>44788.66310185185</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>44256</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>45719</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12890,7 +12890,7 @@
         <v>45048.43734953704</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>45187.44503472222</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>45219</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>45539.28254629629</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>45078.59818287037</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13180,7 +13180,7 @@
         <v>45335</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>45126.47756944445</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         <v>44959</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>45411.45418981482</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>45204</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13470,7 +13470,7 @@
         <v>44977.37475694445</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45327.39255787037</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>44315</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>44841.3953125</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>45561</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>44771.43327546296</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>45190</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>45440</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>45422.39476851852</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45126.38699074074</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         <v>45574.45165509259</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>44728.83686342592</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>44236.8744212963</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14226,7 +14226,7 @@
         <v>45093.61918981482</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>44382</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>45229.67283564815</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>45385.48972222222</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>44739.37986111111</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>44979.50762731482</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>44078</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>45771</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>44203.61291666667</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>45211</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>45719</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>45348.45074074074</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>45296</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>45069</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>45069</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>44852.57822916667</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>45397.44292824074</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>45121</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>45341.37961805556</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>45551</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>45523.52064814815</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>45215</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>44949.42457175926</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>45684.66949074074</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>44953</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>45323.40695601852</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>44953</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>45624.64013888889</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>44572</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>45777.58511574074</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>45534.66148148148</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>45777.37217592593</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>45777.3700462963</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>45531.38554398148</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45600.65333333334</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>45484.49533564815</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>45777.51607638889</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>44223</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>45351.58540509259</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>44593.76921296296</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>45779.45815972222</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>45779.46054398148</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>45750.91766203703</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>45769.35443287037</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>45782.455</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>45126.31585648148</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>45003.90380787037</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>44984.39417824074</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>45019.67677083334</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17019,7 +17019,7 @@
         <v>44980</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17076,7 +17076,7 @@
         <v>44271</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>45783.6937962963</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>45783.68928240741</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>45107</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>45783.69173611111</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>45317.45069444444</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>44840</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17480,7 +17480,7 @@
         <v>45415.60552083333</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>45638</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>45475.46671296296</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>45610.70957175926</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>45582</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>45565.4407175926</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>45132</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>45445.3777662037</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>45548</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>44600.50372685185</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>44895</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18107,7 +18107,7 @@
         <v>45037.64929398148</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>45609.51984953704</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45688</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>44982.67675925926</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>45484.35097222222</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18392,7 +18392,7 @@
         <v>45386.35418981482</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>45775.59086805556</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>44453</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>45566.63414351852</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18620,7 +18620,7 @@
         <v>45789.54855324074</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>45481.92570601852</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>44993</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18791,7 +18791,7 @@
         <v>45433</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>45400</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>45146.35854166667</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>45790.40994212963</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19019,7 +19019,7 @@
         <v>45714.62857638889</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>44494</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>45455.38807870371</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>45559</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>45376.6791087963</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>45743</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>45795.67989583333</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>45126.47204861111</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>45126</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>45126</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>45191.56679398148</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>45126</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>45205.49876157408</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45167.65172453703</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>45797.45761574074</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19879,7 +19879,7 @@
         <v>45681.58681712963</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19936,7 +19936,7 @@
         <v>45797.44099537037</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>45800.58695601852</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20050,7 +20050,7 @@
         <v>45800.5805787037</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>45537</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>45741.70216435185</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>44977</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>45644.45738425926</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>45799.55665509259</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>45665.45535879629</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>45078.5972337963</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>45078.59965277778</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>45084.66810185185</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>45845</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>45727.64369212963</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20744,7 +20744,7 @@
         <v>45072</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20801,7 +20801,7 @@
         <v>45622.56673611111</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>45159.4650925926</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>45573.3758912037</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>45803.56060185185</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>44299</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>45225.62575231482</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>45846</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>45804.56436342592</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>45804.35590277778</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>44958</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>45327.37474537037</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>45845.41</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>45063</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>44783.34944444444</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>45621</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21661,7 +21661,7 @@
         <v>45461.49600694444</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>45091</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>44861</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>44652</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>44665.90422453704</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21946,7 +21946,7 @@
         <v>44326.32891203704</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>44326.34681712963</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         <v>45230</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>44376.82413194444</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         <v>44347.43795138889</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>45852.58133101852</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>45232</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>45400.91444444445</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22402,7 +22402,7 @@
         <v>44907.44033564815</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>45474.61877314815</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>45851.91469907408</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>45182.57702546296</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>44071</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>45392.5746412037</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44699.83489583333</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>45161.329375</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         <v>45323.75855324074</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>44088</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22982,7 +22982,7 @@
         <v>45148.51032407407</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>45273.62567129629</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45851.91112268518</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>45531.50122685185</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>45126</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23272,7 +23272,7 @@
         <v>45434.59488425926</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>45477.50987268519</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23386,7 +23386,7 @@
         <v>45852.5841087963</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>45514.38017361111</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23500,7 +23500,7 @@
         <v>44619</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23557,7 +23557,7 @@
         <v>45849.46575231481</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>44951</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23671,7 +23671,7 @@
         <v>45852</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>45161</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>45408</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23847,7 +23847,7 @@
         <v>44519</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         <v>45394</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>44530.5225462963</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>44728.36712962963</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>44400.37826388889</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>45856.47141203703</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>44404</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24246,7 +24246,7 @@
         <v>45855.72674768518</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24303,7 +24303,7 @@
         <v>45189.50841435185</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>45189.50895833333</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24417,7 +24417,7 @@
         <v>45632</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>44550.40824074074</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>45099</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>45070.62878472222</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>45813.45756944444</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>45188</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24764,7 +24764,7 @@
         <v>45188</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24826,7 +24826,7 @@
         <v>44896.4815625</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>44900.36804398148</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24940,7 +24940,7 @@
         <v>45537</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>45400.62210648148</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>45562.50462962963</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>45818</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>45818</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>45818</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>45475.36099537037</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>45107.47519675926</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>45818</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>44673.38012731481</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44273</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44893.57989583333</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>45587.54915509259</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44683</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>45164.64883101852</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44749.78425925926</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>44726</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>45707</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>44802.69710648148</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45861.33920138889</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>45819.69038194444</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>45401.43559027778</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>45258.50520833334</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>45258</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>45736.56527777778</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>45735.47873842593</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>45554</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>45349.64855324074</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>44995</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         <v>45825.73362268518</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26655,7 +26655,7 @@
         <v>45826.36164351852</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         <v>45826.73186342593</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>45826.35939814815</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>45826.3639699074</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26883,7 +26883,7 @@
         <v>45155</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26940,7 +26940,7 @@
         <v>45826.36921296296</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26997,7 +26997,7 @@
         <v>44897.66574074074</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>45825.44528935185</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>45867.57765046296</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>45475.36554398148</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>45716.5465625</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>44949</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>45826.35645833334</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>45825.4341087963</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>44384</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27515,7 +27515,7 @@
         <v>45349.90940972222</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>45775.59498842592</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27629,7 +27629,7 @@
         <v>45007.53736111111</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27686,7 +27686,7 @@
         <v>45615</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>45400.68645833333</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>45757.63991898148</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>44799.28053240741</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>45772.39091435185</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>45772.39609953704</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>44580.64971064815</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>44827</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>45301</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>45022.634375</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>45022.64363425926</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>45727.45094907407</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>45309.61168981482</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28427,7 +28427,7 @@
         <v>45832.38621527778</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>44839</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28541,7 +28541,7 @@
         <v>44955</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>45832.7072800926</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28655,7 +28655,7 @@
         <v>45126.475625</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28712,7 +28712,7 @@
         <v>45863</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28769,7 +28769,7 @@
         <v>45307.37699074074</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>45832.40292824074</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>45857</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>45716.34990740741</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>45636.63883101852</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>45190</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45098.91159722222</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29168,7 +29168,7 @@
         <v>45211</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>45310.58383101852</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>45477.69497685185</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29344,7 +29344,7 @@
         <v>45706.44140046297</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29401,7 +29401,7 @@
         <v>44851.49424768519</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29458,7 +29458,7 @@
         <v>44445</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>45089.38663194444</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29572,7 +29572,7 @@
         <v>44893.48324074074</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29629,7 +29629,7 @@
         <v>45691.394375</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>45040</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>45159.46884259259</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>44769.56326388889</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>45551.56715277778</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>45709</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>45187.47203703703</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>45401.4321412037</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>44851.4281712963</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>45835.51372685185</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>45196</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>45392.58570601852</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>45554</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>45166</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>45166</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>45881.41793981481</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>45252.41863425926</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>44897.54603009259</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>45392.58935185185</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>44995.57965277778</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30779,7 +30779,7 @@
         <v>44973.864375</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>45323.39561342593</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>45881.37207175926</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>44487.60532407407</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>44594</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>45323</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>44524</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>45524.50288194444</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>44978.31736111111</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
         <v>45707</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31354,7 +31354,7 @@
         <v>45763</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>44953</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>44690</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>45021.50722222222</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>45021.50942129629</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31639,7 +31639,7 @@
         <v>45637.58159722222</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>45841.44533564815</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>45841.44762731482</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         <v>44424</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>45466.85056712963</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>45776</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>45776</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>45805</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>45805</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>45327.39550925926</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>44488</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>45296</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>45048.435</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32385,7 +32385,7 @@
         <v>45884.31863425926</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>45841.65936342593</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32499,7 +32499,7 @@
         <v>45743</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32556,7 +32556,7 @@
         <v>44235</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>45238</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>45841.36670138889</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>44978.32152777778</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>45769.60783564814</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>45182</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>44993.56126157408</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>44222</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33012,7 +33012,7 @@
         <v>44424</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33069,7 +33069,7 @@
         <v>44143</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>44748.54626157408</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>45062.65315972222</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33245,7 +33245,7 @@
         <v>44530.53258101852</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33302,7 +33302,7 @@
         <v>44586</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33359,7 +33359,7 @@
         <v>45191.58287037037</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33416,7 +33416,7 @@
         <v>44278</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33473,7 +33473,7 @@
         <v>45095</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>44416</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33587,7 +33587,7 @@
         <v>44447</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>44777</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>44589.42831018518</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>44960</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>44405.3347337963</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33872,7 +33872,7 @@
         <v>45362.96539351852</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>45524.58461805555</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>45009.46947916667</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>45009</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34100,7 +34100,7 @@
         <v>44507</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34157,7 +34157,7 @@
         <v>45422.47181712963</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>45559.60966435185</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>45084</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>45355.42155092592</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>44893.78201388889</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>44700.61766203704</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34499,7 +34499,7 @@
         <v>44938.51150462963</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>45230.63987268518</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>44979.50945601852</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>44965.4890162037</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>45099.4612037037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>45606.57038194445</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>45629.44709490741</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34903,7 +34903,7 @@
         <v>44852.5103125</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>45258</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>45574.38966435185</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35074,7 +35074,7 @@
         <v>45370.74839120371</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35131,7 +35131,7 @@
         <v>45009.36045138889</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>45009.40710648148</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35245,7 +35245,7 @@
         <v>45107</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35302,7 +35302,7 @@
         <v>45091.60043981481</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>45149.35745370371</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>45191.37449074074</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35473,7 +35473,7 @@
         <v>44922.58392361111</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>44743.42150462963</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35587,7 +35587,7 @@
         <v>44239</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>45155</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>45251.67181712963</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>44930.5281712963</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>45092</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>45092</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35929,7 +35929,7 @@
         <v>45181.58443287037</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35986,7 +35986,7 @@
         <v>45229.52315972222</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36043,7 +36043,7 @@
         <v>44728.36835648148</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>45515.76115740741</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>45425.51765046296</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         <v>45036.45335648148</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36271,7 +36271,7 @@
         <v>44834.45706018519</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>45673.67064814815</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36385,7 +36385,7 @@
         <v>44473</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36442,7 +36442,7 @@
         <v>44235</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36499,7 +36499,7 @@
         <v>45051</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36556,7 +36556,7 @@
         <v>45051.4380787037</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36613,7 +36613,7 @@
         <v>45079</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36670,7 +36670,7 @@
         <v>45590.56064814814</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36727,7 +36727,7 @@
         <v>44808.80826388889</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36784,7 +36784,7 @@
         <v>45645.58637731482</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36841,7 +36841,7 @@
         <v>44126.66101851852</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36898,7 +36898,7 @@
         <v>45614.54209490741</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36955,7 +36955,7 @@
         <v>44944</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37012,7 +37012,7 @@
         <v>45048</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>44487</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>45113.63261574074</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>45514.3787037037</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>45514.3809375</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>45514.38158564815</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37359,7 +37359,7 @@
         <v>45596.75166666666</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37416,7 +37416,7 @@
         <v>45625</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37478,7 +37478,7 @@
         <v>45102</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         <v>45615</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37592,7 +37592,7 @@
         <v>45076.58376157407</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37649,7 +37649,7 @@
         <v>45392.57063657408</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37706,7 +37706,7 @@
         <v>45217</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37763,7 +37763,7 @@
         <v>45102</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37820,7 +37820,7 @@
         <v>44729.41611111111</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>45688</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37934,7 +37934,7 @@
         <v>44455</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37996,7 +37996,7 @@
         <v>45722</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>45740.50475694444</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>45117</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>45180</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>45668.41509259259</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>45714</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>44239</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>44145</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>44781</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38509,7 +38509,7 @@
         <v>45148.50620370371</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38566,7 +38566,7 @@
         <v>44207.35459490741</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38623,7 +38623,7 @@
         <v>45757.64254629629</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38680,7 +38680,7 @@
         <v>45349.81209490741</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>45349.86459490741</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>45641.74149305555</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38851,7 +38851,7 @@
         <v>45726.59443287037</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38908,7 +38908,7 @@
         <v>44984.56648148148</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38965,7 +38965,7 @@
         <v>44761.65730324074</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>45113.64193287037</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>45742.80981481481</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39136,7 +39136,7 @@
         <v>44791.33793981482</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39193,7 +39193,7 @@
         <v>44683.43862268519</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39250,7 +39250,7 @@
         <v>45310.58832175926</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39307,7 +39307,7 @@
         <v>44911</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39364,7 +39364,7 @@
         <v>45728</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39421,7 +39421,7 @@
         <v>45394.41221064814</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39478,7 +39478,7 @@
         <v>44349.62881944444</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         <v>45722</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39592,7 +39592,7 @@
         <v>44900</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>45445.39274305556</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>45021.67435185185</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>45189.35297453704</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39820,7 +39820,7 @@
         <v>45067</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>45637.57834490741</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>44278.36359953704</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>45749.44238425926</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>45716</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>45716</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>45113</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>45028</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40276,7 +40276,7 @@
         <v>45606.56679398148</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>45641.73396990741</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40390,7 +40390,7 @@
         <v>45007.52546296296</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>45636.63569444444</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>45772.39268518519</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>45392.57234953704</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>45392.58719907407</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40675,7 +40675,7 @@
         <v>45200.41958333334</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40732,7 +40732,7 @@
         <v>45740.50775462963</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40789,7 +40789,7 @@
         <v>45196.6208449074</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         <v>45164.64133101852</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40903,7 +40903,7 @@
         <v>44518</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40960,7 +40960,7 @@
         <v>45222</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>44433</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41074,7 +41074,7 @@
         <v>45211</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>44879</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>44095</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41245,7 +41245,7 @@
         <v>45049</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>45211</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41359,7 +41359,7 @@
         <v>44418.40890046296</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41416,7 +41416,7 @@
         <v>45126.36510416667</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41473,7 +41473,7 @@
         <v>45691.38957175926</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>44698.34013888889</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>44690.6797337963</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>45317.44657407407</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>44524</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>45415</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>45373.48118055556</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41872,7 +41872,7 @@
         <v>45068.41424768518</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45755.52962962963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41991,7 +41991,7 @@
         <v>45111.65074074074</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>45204</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>45772.39434027778</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42167,7 +42167,7 @@
         <v>45049.61376157407</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42224,7 +42224,7 @@
         <v>45335.67450231482</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42281,7 +42281,7 @@
         <v>45727.45439814815</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42338,7 +42338,7 @@
         <v>44228</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42395,7 +42395,7 @@
         <v>45369.42106481481</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
         <v>45273.62960648148</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45084</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45204</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42633,7 +42633,7 @@
         <v>45595.51280092593</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>45433.48228009259</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>45117</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45579.47649305555</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>45099.49768518518</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>45716.34835648148</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>45237.5672337963</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>44593.62643518519</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>44531.67679398148</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>44504.38146990741</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43203,7 +43203,7 @@
         <v>45103.68170138889</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>44816.64091435185</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>45474.4828587963</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>44608</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43431,7 +43431,7 @@
         <v>45341.38545138889</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43488,7 +43488,7 @@
         <v>45665.4533912037</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43545,7 +43545,7 @@
         <v>45126.47646990741</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43602,7 +43602,7 @@
         <v>45349.85878472222</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43659,7 +43659,7 @@
         <v>45202.46894675926</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43716,7 +43716,7 @@
         <v>45740.36450231481</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>45700</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43830,7 +43830,7 @@
         <v>45281</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43887,7 +43887,7 @@
         <v>45107.60460648148</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43944,7 +43944,7 @@
         <v>44449</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44001,7 +44001,7 @@
         <v>45155</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44058,7 +44058,7 @@
         <v>44210</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44115,7 +44115,7 @@
         <v>44236.88402777778</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44172,7 +44172,7 @@
         <v>44897.65846064815</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44229,7 +44229,7 @@
         <v>45743.46313657407</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44286,7 +44286,7 @@
         <v>45692.20631944444</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>45716.35474537037</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44400,7 +44400,7 @@
         <v>45716.39373842593</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44457,7 +44457,7 @@
         <v>45740.51246527778</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>44759.39475694444</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44571,7 +44571,7 @@
         <v>45317.44828703703</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44628,7 +44628,7 @@
         <v>45104</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>45211.67291666667</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44742,7 +44742,7 @@
         <v>45211</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44799,7 +44799,7 @@
         <v>44159</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44856,7 +44856,7 @@
         <v>45733.69460648148</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>44519</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>

--- a/Översikt EMMABODA.xlsx
+++ b/Översikt EMMABODA.xlsx
@@ -567,7 +567,7 @@
         <v>44314</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         <v>45377.5588425926</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45369</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>44811</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>45818</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>44238</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44762</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44445</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45161.33116898148</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>45068.42262731482</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>44488</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>44966.54540509259</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>44120</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>44570.72098379629</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>44984.36140046296</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>45229.67172453704</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>44495</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>45335</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>44405.32738425926</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>44140</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>44089</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>44082</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>44120.38783564815</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>44459.43425925926</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>44105</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>44379.56671296297</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>44530.4546875</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>44496.52702546296</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44441.48626157407</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>44488</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>44530.4562037037</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>44764.45645833333</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>44120.39879629629</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>44496.5110300926</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>44405.31638888889</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>44405.32319444444</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>44405.31894675926</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>44405</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44228</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>44454.86018518519</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>44117.6835300926</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>44264.36884259259</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>44454</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>44251</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>44529</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>44490</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44211</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>44110</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>44431</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>44601.34255787037</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>44600</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>44383.5654050926</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>44097</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>44280.65521990741</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>44251</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>44507</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>44507.56921296296</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>44507</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>44507</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>44297</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>44416</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44416</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44442</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>44238</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>44240</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>44211</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>44599.69461805555</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>44691</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>44728.83878472223</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>44628.35012731481</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>44326.44194444444</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>44504.38268518518</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>44379</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>44387</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>44383.6131712963</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>44515.44268518518</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>44851.40596064815</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>44071</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>44070</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>44239</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>44082</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>44118</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>44240.59631944444</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>44523</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>44648.3578587963</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>44462.69965277778</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>44278</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>44628</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>44788.65715277778</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44347.43119212963</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>44416</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>44382.6675925926</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>44361.39021990741</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>44347.44501157408</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>44405</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>44627.34532407407</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>44392.4420949074</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>44075</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>44109</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>44112</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44462</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>44240.57777777778</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44860.88715277778</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>44071</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>44148</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>44498</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>44120</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>44768.83986111111</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>44851.49548611111</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44529.29797453704</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>44249</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>44172</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>44277</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>44320</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>44208</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>44208</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>44385</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>44347.43444444444</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>44813</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>44809.43158564815</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>44771</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>44202</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>44202</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>44412</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>44587.42887731481</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>44433</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44251</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
         <v>44496</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>44466.39774305555</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>44507</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>44507</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44487</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>44405</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>44405</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>44383.61637731481</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>44416</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>44147</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>44628.36534722222</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44600</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>44652</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44120</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>44421</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>44074</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>44600.45854166667</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>44501</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44116.37994212963</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>44600.45505787037</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>44110</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         <v>44256</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>44293</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44148</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>44148</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>44852.48653935185</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>44841.3953125</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>44847.55930555556</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>44295</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>44148</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>44743.42285879629</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>44839.33949074074</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>44382.66943287037</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>44180</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>44488</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>44722.49396990741</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>44223</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>44452.30709490741</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>44210.32178240741</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>44238</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>44532.70575231482</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>44083</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>44120.39627314815</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>44076</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>44083</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>44385</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>44412</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>44655.9318287037</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44470.31766203704</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>44593.62412037037</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44652</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>44615</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>44699.83193287037</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>44589.43354166667</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>44162.37409722222</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>44622.48368055555</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>44820</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>44706</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44524.72388888889</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>44110</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44712.48467592592</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>44167</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>44454</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>44551</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>44340</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>44431.41373842592</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>44383.559375</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>44383.61515046296</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>44530</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>44600.45703703703</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>44788.66310185185</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>44980</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>45078.5972337963</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>45078.59965277778</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>44302.5521875</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>44725</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>45217</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>45397.44292824074</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>45775.59498842592</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>44726</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>45742.80981481481</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>45740.36450231481</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>44284.40975694444</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>44302.54723379629</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>45425.51765046296</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>45401.43559027778</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>45763</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>44743.38194444445</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>44951</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>44524</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>44728.83686342592</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>45117</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>45445.39274305556</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>45182.57702546296</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>44690.6797337963</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>45079</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>44816.64091435185</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>45211.67291666667</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14045,7 +14045,7 @@
         <v>45691.394375</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>44840</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>45595.51280092593</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44382</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>45673.67064814815</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>44953</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>45089.38663194444</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>45251.67181712963</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>45691.38957175926</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>45714.62857638889</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>45099.49768518518</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>44897.66574074074</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>45204</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>45561</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>45273.62567129629</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>45349.85878472222</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14977,7 +14977,7 @@
         <v>44827</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>45411.45418981482</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15091,7 +15091,7 @@
         <v>45392.57234953704</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>45392.58719907407</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>44433</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
         <v>45700</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15319,7 +15319,7 @@
         <v>45258</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>44487.60532407407</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>45590.56064814814</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>45092</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>45092</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>45040</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>45727.45094907407</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>45349.81209490741</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>45296</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>44376.82413194444</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>45310.58383101852</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>45191.37449074074</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>45126.31585648148</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>44550.40824074074</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>45750.91766203703</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>45740.51246527778</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>45076.58376157407</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>45573.3758912037</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>44384</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>45606.56679398148</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>45385.48972222222</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>45392.58935185185</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>44278.36359953704</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>45716.34835648148</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>45515.76115740741</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>45743</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>45099</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>44993.56126157408</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>44728.36835648148</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>45022.634375</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>45022.64363425926</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>45574.45165509259</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>45187.47203703703</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>45258.50520833334</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>45258</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>45600.65333333334</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>45637.58159722222</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>44930.5281712963</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>45400.62210648148</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>44698.34013888889</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>45159.46884259259</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>45219</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>45028</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>45554</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
         <v>45551.56715277778</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>45307.37699074074</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>45392.57063657408</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>45317.44657407407</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>45187.44503472222</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>44748.54626157408</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>44652</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         <v>45237.5672337963</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18298,7 +18298,7 @@
         <v>45531.50122685185</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18355,7 +18355,7 @@
         <v>44900.36804398148</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18412,7 +18412,7 @@
         <v>45196</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18469,7 +18469,7 @@
         <v>44586</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18526,7 +18526,7 @@
         <v>44095</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>45049</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>44699.83489583333</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>45615</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>45161</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>45180</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
         <v>45400.91444444445</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>44418.40890046296</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>45716.5465625</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>45117</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19101,7 +19101,7 @@
         <v>45048.43734953704</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>45229.67283564815</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19215,7 +19215,7 @@
         <v>45230.63987268518</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>45099.4612037037</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19334,7 +19334,7 @@
         <v>45188</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>45769.60783564814</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         <v>45714</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>44769.56326388889</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>44572</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
         <v>45392.58570601852</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>44488</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19743,7 +19743,7 @@
         <v>45727.45439814815</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19800,7 +19800,7 @@
         <v>45019.67677083334</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>44973.864375</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>45769.35443287037</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19976,7 +19976,7 @@
         <v>45474.61877314815</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>45709</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>45341.38545138889</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>44897.54603009259</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>44235</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>45078.59818287037</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>45722</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>44519</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>45722</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>45238</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>45394</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>45614.54209490741</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>44455</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>45230</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         <v>44977.37475694445</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>44955</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>45587.54915509259</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20955,7 +20955,7 @@
         <v>45048.435</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>45559.60966435185</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45749.44238425926</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>45301</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>45351.58540509259</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>45309.61168981482</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>45534.66148148148</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>45215</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>45551</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>45777.51607638889</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>45777.3700462963</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>45777.37217592593</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21639,7 +21639,7 @@
         <v>44400.37826388889</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>45523.52064814815</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
         <v>45211</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>45211</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>44683.43862268519</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21924,7 +21924,7 @@
         <v>44949.42457175926</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21981,7 +21981,7 @@
         <v>45757.63991898148</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>45684.66949074074</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>45624.64013888889</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>45484.49533564815</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
         <v>45692.20631944444</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>45757.64254629629</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>45665.4533912037</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>45779.45815972222</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>45779.46054398148</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>45783.68928240741</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22551,7 +22551,7 @@
         <v>45772.39091435185</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22608,7 +22608,7 @@
         <v>45772.39609953704</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22665,7 +22665,7 @@
         <v>44978.31736111111</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22722,7 +22722,7 @@
         <v>44978.32152777778</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22779,7 +22779,7 @@
         <v>45783.69173611111</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22836,7 +22836,7 @@
         <v>45622.56673611111</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22893,7 +22893,7 @@
         <v>45782.455</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>45148.50620370371</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>45164.64883101852</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>45166</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>45166</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>45107</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23235,7 +23235,7 @@
         <v>45445.3777662037</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>45093.61918981482</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23349,7 +23349,7 @@
         <v>45317.45069444444</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>44896.4815625</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23463,7 +23463,7 @@
         <v>44965.4890162037</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         <v>45475.36554398148</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         <v>45548</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23634,7 +23634,7 @@
         <v>44739.37986111111</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>45415.60552083333</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>45638</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>45394.41221064814</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>45606.57038194445</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23919,7 +23919,7 @@
         <v>44743.42150462963</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>44749.78425925926</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>45565.4407175926</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24090,7 +24090,7 @@
         <v>44949</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>45327.39550925926</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
         <v>45386.35418981482</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>45327.37474537037</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>45355.42155092592</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>45188</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>45422.39476851852</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>45775.59086805556</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>44895</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>45789.54855324074</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>44453</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>45481.92570601852</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>44145</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>45369.42106481481</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>44982.67675925926</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>44228</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25007,7 +25007,7 @@
         <v>45566.63414351852</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         <v>45582</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>45609.51984953704</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>45559</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>44834.45706018519</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>45484.35097222222</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>44273</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>44447</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>45688</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>45610.70957175926</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>44791.33793981482</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>45771</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>45182</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>45400</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>45433.48228009259</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25867,7 +25867,7 @@
         <v>45790.40994212963</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25924,7 +25924,7 @@
         <v>45107.47519675926</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>45007.52546296296</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45007.53736111111</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26095,7 +26095,7 @@
         <v>45706.44140046297</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26152,7 +26152,7 @@
         <v>44207.35459490741</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45148.51032407407</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>45084.66810185185</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>45741.70216435185</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>45455.38807870371</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>45537</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26494,7 +26494,7 @@
         <v>44783.34944444444</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26551,7 +26551,7 @@
         <v>45349.86459490741</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>45281</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26665,7 +26665,7 @@
         <v>45795.67989583333</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26722,7 +26722,7 @@
         <v>45211</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>45021.67435185185</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>45797.45761574074</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>44530.5225462963</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>45189.50841435185</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>44487</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>44938.51150462963</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         <v>44593.76921296296</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45539.28254629629</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>45021.50942129629</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>44851.49424768519</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27354,7 +27354,7 @@
         <v>44960</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>45797.44099537037</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>44600.50372685185</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>45415</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27582,7 +27582,7 @@
         <v>45665.45535879629</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>44494</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>44977</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>45537</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>45799.55665509259</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>45475.36099537037</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>45323</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>44771.43327546296</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>45740.50475694444</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>44424</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>45475.46671296296</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>45735.47873842593</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>44893.48324074074</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>45155</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>45037.64929398148</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>44690</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>44416</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>44405.3347337963</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44518</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>45641.74149305555</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>44593.62643518519</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>44728.36712962963</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>45009.36045138889</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>45009.40710648148</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>45009.46947916667</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>45009</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>44504.38146990741</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>44911</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>45126</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>45126</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>45159.4650925926</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44958</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>45803.56060185185</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>45800.58695601852</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>45800.5805787037</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>45514.3787037037</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>45514.3809375</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>45514.38158564815</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29748,7 +29748,7 @@
         <v>45202.46894675926</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>44799.28053240741</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>45155</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>45225.62575231482</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>45063</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>44424</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30095,7 +30095,7 @@
         <v>45804.56436342592</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30152,7 +30152,7 @@
         <v>45804.35590277778</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30209,7 +30209,7 @@
         <v>44879</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30266,7 +30266,7 @@
         <v>44088</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>44893.78201388889</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>45852</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>44852.5103125</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>45190</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>45433</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>45067</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>45440</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>45126</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>45126.36510416667</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>45126.47646990741</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>44953</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>45107</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>44729.41611111111</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>45155</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>45852.58133101852</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>45851.91469907408</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>45851.91112268518</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
         <v>44984.39417824074</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31354,7 +31354,7 @@
         <v>45852.5841087963</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>44953</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>45362.96539351852</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>44507</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>44665.90422453704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31639,7 +31639,7 @@
         <v>44473</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>44347.43795138889</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>45189.35297453704</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         <v>45855.72674768518</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>45048</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>45191.56679398148</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>44700.61766203704</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>44619</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>45813.45756944444</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>45434.59488425926</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>45036.45335648148</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32266,7 +32266,7 @@
         <v>45743</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>45296</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32380,7 +32380,7 @@
         <v>44530.53258101852</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>44907.44033564815</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>44777</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32551,7 +32551,7 @@
         <v>45644.45738425926</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>45181.58443287037</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>45273.62960648148</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>44222</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>44143</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32846,7 +32846,7 @@
         <v>44223</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>45211</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         <v>45856.47141203703</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>45211</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>45818</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>45818</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>45636.63883101852</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33245,7 +33245,7 @@
         <v>45861.33920138889</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33302,7 +33302,7 @@
         <v>45164.64133101852</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33359,7 +33359,7 @@
         <v>45818</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33416,7 +33416,7 @@
         <v>45229.52315972222</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33473,7 +33473,7 @@
         <v>45132</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>45084</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33587,7 +33587,7 @@
         <v>45190</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>44993</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>45819.69038194444</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>45719</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>45719</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33872,7 +33872,7 @@
         <v>45818</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>45349.64855324074</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>44519</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>44299</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34100,7 +34100,7 @@
         <v>45531.38554398148</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34157,7 +34157,7 @@
         <v>45579.47649305555</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>45126.475625</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>44861</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>45102</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>45102</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>45772.39268518519</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34499,7 +34499,7 @@
         <v>45205.49876157408</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>45474.4828587963</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>45084</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>45726.59443287037</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>44839</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>45867.57765046296</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>44404</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>45825.44528935185</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>45825.4341087963</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>45825.73362268518</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>45826.35645833334</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35126,7 +35126,7 @@
         <v>45126.47756944445</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>45317.44828703703</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35240,7 +35240,7 @@
         <v>45826.36921296296</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>45196.6208449074</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>45574.38966435185</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35411,7 +35411,7 @@
         <v>45826.73186342593</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>45204</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>45826.36164351852</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35587,7 +35587,7 @@
         <v>45232</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>45615</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>45826.35939814815</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>45826.3639699074</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>45863</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>45323.75855324074</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35934,7 +35934,7 @@
         <v>44071</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>45098.91159722222</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>45857</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36105,7 +36105,7 @@
         <v>44979.50945601852</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>45716.35474537037</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36219,7 +36219,7 @@
         <v>45716.39373842593</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36276,7 +36276,7 @@
         <v>45392.5746412037</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>45832.40292824074</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36390,7 +36390,7 @@
         <v>45832.38621527778</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>45091</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>45740.50775462963</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36561,7 +36561,7 @@
         <v>45716</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36618,7 +36618,7 @@
         <v>45716</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>45341.37961805556</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36732,7 +36732,7 @@
         <v>45832.7072800926</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36789,7 +36789,7 @@
         <v>44995.57965277778</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36846,7 +36846,7 @@
         <v>45003.90380787037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         <v>44315</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>45477.50987268519</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37017,7 +37017,7 @@
         <v>44995</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37074,7 +37074,7 @@
         <v>45835.51372685185</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>45121</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>45191.58287037037</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>44326.32891203704</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>44326.34681712963</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37359,7 +37359,7 @@
         <v>45126</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37416,7 +37416,7 @@
         <v>45514.38017361111</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>45146.35854166667</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37530,7 +37530,7 @@
         <v>44979.50762731482</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37587,7 +37587,7 @@
         <v>45113.63261574074</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37644,7 +37644,7 @@
         <v>45113.64193287037</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37701,7 +37701,7 @@
         <v>45477.69497685185</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37763,7 +37763,7 @@
         <v>44126.66101851852</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37820,7 +37820,7 @@
         <v>45167.65172453703</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>45637.57834490741</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37934,7 +37934,7 @@
         <v>44271</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>45524.50288194444</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38048,7 +38048,7 @@
         <v>44959</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38105,7 +38105,7 @@
         <v>45068.41424768518</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>45707</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>44851.4281712963</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>44608</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>45095</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>45069</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>45069</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38509,7 +38509,7 @@
         <v>45401.4321412037</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38566,7 +38566,7 @@
         <v>45524.58461805555</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38623,7 +38623,7 @@
         <v>44580.64971064815</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38680,7 +38680,7 @@
         <v>45348.45074074074</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>45107.60460648148</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>45373.48118055556</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38851,7 +38851,7 @@
         <v>45408</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38908,7 +38908,7 @@
         <v>45645.58637731482</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38965,7 +38965,7 @@
         <v>45376.6791087963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>44445</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>45161.329375</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39141,7 +39141,7 @@
         <v>45636.63569444444</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39198,7 +39198,7 @@
         <v>44683</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>44984.56648148148</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39312,7 +39312,7 @@
         <v>45629.44709490741</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>45252.41863425926</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39426,7 +39426,7 @@
         <v>45881.41793981481</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39483,7 +39483,7 @@
         <v>45881.37207175926</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39540,7 +39540,7 @@
         <v>44761.65730324074</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39597,7 +39597,7 @@
         <v>45461.49600694444</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39654,7 +39654,7 @@
         <v>44802.69710648148</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39711,7 +39711,7 @@
         <v>45349.90940972222</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39768,7 +39768,7 @@
         <v>45728</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39825,7 +39825,7 @@
         <v>45422.47181712963</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39882,7 +39882,7 @@
         <v>44808.80826388889</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39939,7 +39939,7 @@
         <v>45841.36670138889</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39996,7 +39996,7 @@
         <v>45632</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40053,7 +40053,7 @@
         <v>45776</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40110,7 +40110,7 @@
         <v>45776</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40167,7 +40167,7 @@
         <v>45805</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>45805</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>45841.65936342593</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>44078</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40395,7 +40395,7 @@
         <v>44210</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>45841.44533564815</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>45841.44762731482</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>44159</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40623,7 +40623,7 @@
         <v>44449</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>45189.50895833333</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>45707</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40794,7 +40794,7 @@
         <v>44524</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40851,7 +40851,7 @@
         <v>45845.41</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40908,7 +40908,7 @@
         <v>45091.60043981481</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>45772.39434027778</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41022,7 +41022,7 @@
         <v>45049.61376157407</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41079,7 +41079,7 @@
         <v>45887.58094907407</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41136,7 +41136,7 @@
         <v>45621</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41193,7 +41193,7 @@
         <v>44531.67679398148</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>45051</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>45051.4380787037</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41364,7 +41364,7 @@
         <v>45736.56527777778</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>44897.65846064815</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41478,7 +41478,7 @@
         <v>45887.56543981482</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>45887.5702662037</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>45126.38699074074</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45126.47204861111</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45884.31863425926</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45113</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>45323.40695601852</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45887.57563657407</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>44673.38012731481</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41991,7 +41991,7 @@
         <v>44236.8744212963</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>45727.64369212963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>45596.75166666666</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>45845</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>44235</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>44893.57989583333</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>45888.33114583333</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45554</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
         <v>45681.58681712963</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42509,7 +42509,7 @@
         <v>45846</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45668.41509259259</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>45104</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42680,7 +42680,7 @@
         <v>45335</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42737,7 +42737,7 @@
         <v>45335.67450231482</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42794,7 +42794,7 @@
         <v>44759.39475694444</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42851,7 +42851,7 @@
         <v>44349.62881944444</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42908,7 +42908,7 @@
         <v>45200.41958333334</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42965,7 +42965,7 @@
         <v>45755.52962962963</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43022,7 +43022,7 @@
         <v>45070.62878472222</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43079,7 +43079,7 @@
         <v>44236.88402777778</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43136,7 +43136,7 @@
         <v>44594</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43193,7 +43193,7 @@
         <v>45222</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43250,7 +43250,7 @@
         <v>45323.39561342593</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43307,7 +43307,7 @@
         <v>44852.57822916667</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43364,7 +43364,7 @@
         <v>44944</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43421,7 +43421,7 @@
         <v>45849.46575231481</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43478,7 +43478,7 @@
         <v>45072</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43535,7 +43535,7 @@
         <v>45149.35745370371</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>45370.74839120371</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43649,7 +43649,7 @@
         <v>45400.68645833333</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>45111.65074074074</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43763,7 +43763,7 @@
         <v>45021.50722222222</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43820,7 +43820,7 @@
         <v>45310.58832175926</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43877,7 +43877,7 @@
         <v>44239</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43934,7 +43934,7 @@
         <v>45204</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43996,7 +43996,7 @@
         <v>45062.65315972222</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44053,7 +44053,7 @@
         <v>44900</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44110,7 +44110,7 @@
         <v>44922.58392361111</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44167,7 +44167,7 @@
         <v>45625</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44229,7 +44229,7 @@
         <v>44239</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44286,7 +44286,7 @@
         <v>44278</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>45562.50462962963</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44400,7 +44400,7 @@
         <v>45103.68170138889</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44457,7 +44457,7 @@
         <v>45688</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>44781</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44571,7 +44571,7 @@
         <v>45466.85056712963</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44628,7 +44628,7 @@
         <v>44589.42831018518</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>44203.61291666667</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44742,7 +44742,7 @@
         <v>45716.34990740741</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44799,7 +44799,7 @@
         <v>45327.39255787037</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>

--- a/Översikt EMMABODA.xlsx
+++ b/Översikt EMMABODA.xlsx
@@ -567,7 +567,7 @@
         <v>44314</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         <v>45377.5588425926</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45369</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>44811</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>45818</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>44238</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44762</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44445</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>45161.33116898148</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>45068.42262731482</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>44488</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>44966.54540509259</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>44120</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>44570.72098379629</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>44984.36140046296</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>45229.67172453704</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>44495</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>45335</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>44405.32738425926</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>44140</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>44089</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>44082</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>44120.38783564815</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>44459.43425925926</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>44105</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>44379.56671296297</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>44530.4546875</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>44496.52702546296</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44441.48626157407</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>44488</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>44530.4562037037</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>44764.45645833333</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>44120.39879629629</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>44496.5110300926</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>44405.31638888889</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>44405.32319444444</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>44405.31894675926</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>44405</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44228</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>44454.86018518519</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>44117.6835300926</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>44264.36884259259</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>44454</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>44251</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>44529</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>44490</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44211</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>44110</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>44431</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>44601.34255787037</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>44600</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>44383.5654050926</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>44097</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>44280.65521990741</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>44251</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>44507</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>44507.56921296296</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>44507</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>44507</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>44297</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>44416</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44416</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44442</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>44238</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>44240</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>44211</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>44599.69461805555</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>44691</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>44728.83878472223</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>44628.35012731481</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>44326.44194444444</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>44504.38268518518</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>44379</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>44387</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>44383.6131712963</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>44515.44268518518</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>44851.40596064815</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>44071</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>44070</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>44239</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>44082</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>44118</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>44240.59631944444</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>44523</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>44648.3578587963</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>44462.69965277778</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>44278</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>44628</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>44788.65715277778</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44347.43119212963</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>44416</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>44382.6675925926</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>44361.39021990741</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>44347.44501157408</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>44405</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>44627.34532407407</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>44392.4420949074</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>44075</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>44109</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>44112</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44462</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>44240.57777777778</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44860.88715277778</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>44071</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>44148</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>44498</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>44120</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>44768.83986111111</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>44851.49548611111</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44529.29797453704</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>44249</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>44172</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>44277</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>44320</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>44208</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>44208</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>44385</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>44347.43444444444</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>44813</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>44809.43158564815</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>44771</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>44202</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>44202</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>44412</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>44587.42887731481</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         <v>44433</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44251</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
         <v>44496</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>44466.39774305555</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>44507</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>44507</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44487</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>44405</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>44405</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>44383.61637731481</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>44416</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>44147</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>44628.36534722222</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44600</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>44652</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44120</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>44421</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>44074</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>44600.45854166667</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>44501</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44116.37994212963</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>44600.45505787037</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>44110</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         <v>44256</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>44293</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44148</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>44148</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>44852.48653935185</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>44841.3953125</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>44847.55930555556</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>44295</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>44148</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>44743.42285879629</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>44839.33949074074</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>44382.66943287037</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>44180</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>44488</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>44722.49396990741</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>44223</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>44452.30709490741</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>44210.32178240741</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>44238</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>44532.70575231482</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>44083</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>44120.39627314815</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>44076</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>44083</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>44385</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>44412</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>44655.9318287037</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44470.31766203704</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>44593.62412037037</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44652</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>44615</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>44699.83193287037</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>44589.43354166667</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>44162.37409722222</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>44622.48368055555</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>44820</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>44706</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44524.72388888889</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>44110</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44712.48467592592</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>44167</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>44454</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>44551</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12097,7 +12097,7 @@
         <v>44340</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>44431.41373842592</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>44383.559375</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>44383.61515046296</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>44530</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>44600.45703703703</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>44788.66310185185</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>44980</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>45078.5972337963</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>45078.59965277778</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>44302.5521875</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>44725</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>45217</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>45397.44292824074</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>45775.59498842592</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>44726</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>45742.80981481481</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>45740.36450231481</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>44284.40975694444</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>44302.54723379629</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>45425.51765046296</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>45401.43559027778</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>45763</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>44743.38194444445</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>44951</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>44524</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>44728.83686342592</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>45117</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>45445.39274305556</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>45182.57702546296</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>44690.6797337963</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>45079</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>44816.64091435185</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>45211.67291666667</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14045,7 +14045,7 @@
         <v>45691.394375</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>44840</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>45595.51280092593</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44382</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>45673.67064814815</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>44953</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>45089.38663194444</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>45251.67181712963</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>45691.38957175926</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>45714.62857638889</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>45099.49768518518</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>44897.66574074074</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>45204</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>45561</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>45273.62567129629</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>45349.85878472222</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14977,7 +14977,7 @@
         <v>44827</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>45411.45418981482</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15091,7 +15091,7 @@
         <v>45392.57234953704</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>45392.58719907407</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>44433</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
         <v>45700</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15319,7 +15319,7 @@
         <v>45258</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>44487.60532407407</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>45590.56064814814</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>45092</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>45092</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>45040</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>45727.45094907407</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>45349.81209490741</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>45296</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>44376.82413194444</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>45310.58383101852</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>45191.37449074074</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>45126.31585648148</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>44550.40824074074</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>45750.91766203703</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>45740.51246527778</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>45076.58376157407</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>45573.3758912037</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>44384</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>45606.56679398148</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>45385.48972222222</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>45392.58935185185</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>44278.36359953704</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>45716.34835648148</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>45515.76115740741</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>45743</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>45099</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>44993.56126157408</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>44728.36835648148</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>45022.634375</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>45022.64363425926</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>45574.45165509259</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>45187.47203703703</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17205,7 +17205,7 @@
         <v>45258.50520833334</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>45258</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17319,7 +17319,7 @@
         <v>45600.65333333334</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>45637.58159722222</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>44930.5281712963</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>45400.62210648148</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>44698.34013888889</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>45159.46884259259</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>45219</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>45028</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>45554</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
         <v>45551.56715277778</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>45307.37699074074</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>45392.57063657408</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>45317.44657407407</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>45187.44503472222</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>44748.54626157408</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>44652</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         <v>45237.5672337963</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18298,7 +18298,7 @@
         <v>45531.50122685185</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18355,7 +18355,7 @@
         <v>44900.36804398148</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18412,7 +18412,7 @@
         <v>45196</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18469,7 +18469,7 @@
         <v>44586</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18526,7 +18526,7 @@
         <v>44095</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>45049</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>44699.83489583333</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>45615</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>45161</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>45180</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
         <v>45400.91444444445</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>44418.40890046296</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>45716.5465625</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>45117</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19101,7 +19101,7 @@
         <v>45048.43734953704</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>45229.67283564815</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19215,7 +19215,7 @@
         <v>45230.63987268518</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>45099.4612037037</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19334,7 +19334,7 @@
         <v>45188</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>45769.60783564814</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         <v>45714</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>44769.56326388889</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>44572</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
         <v>45392.58570601852</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>44488</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19743,7 +19743,7 @@
         <v>45727.45439814815</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19800,7 +19800,7 @@
         <v>45019.67677083334</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>44973.864375</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>45769.35443287037</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19976,7 +19976,7 @@
         <v>45474.61877314815</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>45709</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>45341.38545138889</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>44897.54603009259</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>44235</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>45078.59818287037</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>45722</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>44519</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>45722</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>45238</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>45394</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>45614.54209490741</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>44455</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>45230</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         <v>44977.37475694445</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>44955</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>45587.54915509259</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20955,7 +20955,7 @@
         <v>45048.435</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21012,7 +21012,7 @@
         <v>45559.60966435185</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45749.44238425926</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>45301</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>45351.58540509259</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>45309.61168981482</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>45534.66148148148</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>45215</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>45551</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>45777.51607638889</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>45777.3700462963</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>45777.37217592593</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21639,7 +21639,7 @@
         <v>44400.37826388889</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>45523.52064814815</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
         <v>45211</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>45211</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>44683.43862268519</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21924,7 +21924,7 @@
         <v>44949.42457175926</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21981,7 +21981,7 @@
         <v>45757.63991898148</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>45684.66949074074</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>45624.64013888889</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>45484.49533564815</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
         <v>45692.20631944444</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>45757.64254629629</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>45665.4533912037</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>45779.45815972222</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>45779.46054398148</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>45783.68928240741</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22551,7 +22551,7 @@
         <v>45772.39091435185</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22608,7 +22608,7 @@
         <v>45772.39609953704</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22665,7 +22665,7 @@
         <v>44978.31736111111</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22722,7 +22722,7 @@
         <v>44978.32152777778</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22779,7 +22779,7 @@
         <v>45783.69173611111</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22836,7 +22836,7 @@
         <v>45622.56673611111</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22893,7 +22893,7 @@
         <v>45782.455</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>45148.50620370371</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>45164.64883101852</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>45166</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>45166</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>45107</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23235,7 +23235,7 @@
         <v>45445.3777662037</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>45093.61918981482</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23349,7 +23349,7 @@
         <v>45317.45069444444</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>44896.4815625</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23463,7 +23463,7 @@
         <v>44965.4890162037</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         <v>45475.36554398148</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         <v>45548</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23634,7 +23634,7 @@
         <v>44739.37986111111</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>45415.60552083333</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>45638</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>45394.41221064814</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>45606.57038194445</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23919,7 +23919,7 @@
         <v>44743.42150462963</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>44749.78425925926</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>45565.4407175926</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24090,7 +24090,7 @@
         <v>44949</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>45327.39550925926</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
         <v>45386.35418981482</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>45327.37474537037</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>45355.42155092592</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>45188</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>45422.39476851852</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>45775.59086805556</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>44895</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>45789.54855324074</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>44453</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>45481.92570601852</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>44145</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>45369.42106481481</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>44982.67675925926</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>44228</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25007,7 +25007,7 @@
         <v>45566.63414351852</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         <v>45582</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>45609.51984953704</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>45559</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>44834.45706018519</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>45484.35097222222</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>44273</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>44447</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>45688</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>45610.70957175926</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>44791.33793981482</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>45771</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>45182</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>45400</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>45433.48228009259</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25867,7 +25867,7 @@
         <v>45790.40994212963</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25924,7 +25924,7 @@
         <v>45107.47519675926</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>45007.52546296296</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45007.53736111111</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26095,7 +26095,7 @@
         <v>45706.44140046297</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26152,7 +26152,7 @@
         <v>44207.35459490741</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45148.51032407407</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>45084.66810185185</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>45741.70216435185</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>45455.38807870371</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>45537</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26494,7 +26494,7 @@
         <v>44783.34944444444</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26551,7 +26551,7 @@
         <v>45349.86459490741</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>45281</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26665,7 +26665,7 @@
         <v>45795.67989583333</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26722,7 +26722,7 @@
         <v>45211</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>45021.67435185185</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>45797.45761574074</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>44530.5225462963</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>45189.50841435185</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>44487</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>44938.51150462963</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         <v>44593.76921296296</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45539.28254629629</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>45021.50942129629</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>44851.49424768519</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27354,7 +27354,7 @@
         <v>44960</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>45797.44099537037</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>44600.50372685185</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>45415</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27582,7 +27582,7 @@
         <v>45665.45535879629</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27639,7 +27639,7 @@
         <v>44494</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>44977</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>45537</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>45799.55665509259</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>45475.36099537037</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>45323</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>44771.43327546296</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>45740.50475694444</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>44424</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>45475.46671296296</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>45735.47873842593</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>44893.48324074074</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>45155</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>45037.64929398148</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>44690</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>44416</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>44405.3347337963</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44518</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>45641.74149305555</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>44593.62643518519</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>44728.36712962963</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>45009.36045138889</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>45009.40710648148</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>45009.46947916667</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>45009</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>44504.38146990741</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>44911</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>45126</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>45126</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>45159.4650925926</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44958</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>45803.56060185185</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>45800.58695601852</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>45800.5805787037</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>45514.3787037037</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>45514.3809375</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>45514.38158564815</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29748,7 +29748,7 @@
         <v>45202.46894675926</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>44799.28053240741</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>45155</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>45225.62575231482</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>45063</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>44424</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30095,7 +30095,7 @@
         <v>45804.56436342592</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30152,7 +30152,7 @@
         <v>45804.35590277778</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30209,7 +30209,7 @@
         <v>44879</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30266,7 +30266,7 @@
         <v>44088</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>44893.78201388889</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>45852</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>44852.5103125</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>45190</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>45433</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>45067</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>45440</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>45126</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>45126.36510416667</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>45126.47646990741</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>44953</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>45107</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>44729.41611111111</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>45155</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>45852.58133101852</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>45851.91469907408</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>45851.91112268518</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
         <v>44984.39417824074</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31354,7 +31354,7 @@
         <v>45852.5841087963</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>44953</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>45362.96539351852</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>44507</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>44665.90422453704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31639,7 +31639,7 @@
         <v>44473</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>44347.43795138889</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>45189.35297453704</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         <v>45855.72674768518</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>45048</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>45191.56679398148</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>44700.61766203704</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>44619</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>45813.45756944444</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>45434.59488425926</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>45036.45335648148</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32266,7 +32266,7 @@
         <v>45743</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>45296</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32380,7 +32380,7 @@
         <v>44530.53258101852</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>44907.44033564815</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>44777</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32551,7 +32551,7 @@
         <v>45644.45738425926</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>45181.58443287037</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>45273.62960648148</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>44222</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>44143</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32846,7 +32846,7 @@
         <v>44223</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>45211</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         <v>45856.47141203703</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>45211</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>45818</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>45818</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>45636.63883101852</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33245,7 +33245,7 @@
         <v>45861.33920138889</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33302,7 +33302,7 @@
         <v>45164.64133101852</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33359,7 +33359,7 @@
         <v>45818</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33416,7 +33416,7 @@
         <v>45229.52315972222</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33473,7 +33473,7 @@
         <v>45132</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>45084</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33587,7 +33587,7 @@
         <v>45190</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>44993</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>45819.69038194444</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>45719</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>45719</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33872,7 +33872,7 @@
         <v>45818</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>45349.64855324074</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>44519</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>44299</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34100,7 +34100,7 @@
         <v>45531.38554398148</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34157,7 +34157,7 @@
         <v>45579.47649305555</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34214,7 +34214,7 @@
         <v>45126.475625</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>44861</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>45102</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>45102</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34442,7 +34442,7 @@
         <v>45772.39268518519</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34499,7 +34499,7 @@
         <v>45205.49876157408</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>45474.4828587963</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>45084</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>45726.59443287037</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>44839</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>45867.57765046296</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>44404</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>45825.44528935185</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>45825.4341087963</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>45825.73362268518</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>45826.35645833334</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35126,7 +35126,7 @@
         <v>45126.47756944445</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>45317.44828703703</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35240,7 +35240,7 @@
         <v>45826.36921296296</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>45196.6208449074</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>45574.38966435185</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35411,7 +35411,7 @@
         <v>45826.73186342593</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>45204</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>45826.36164351852</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35587,7 +35587,7 @@
         <v>45232</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>45615</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>45826.35939814815</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>45826.3639699074</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>45863</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>45323.75855324074</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35934,7 +35934,7 @@
         <v>44071</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>45098.91159722222</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>45857</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36105,7 +36105,7 @@
         <v>44979.50945601852</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>45716.35474537037</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36219,7 +36219,7 @@
         <v>45716.39373842593</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36276,7 +36276,7 @@
         <v>45392.5746412037</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>45832.40292824074</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36390,7 +36390,7 @@
         <v>45832.38621527778</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>45091</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>45740.50775462963</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36561,7 +36561,7 @@
         <v>45716</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36618,7 +36618,7 @@
         <v>45716</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>45341.37961805556</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36732,7 +36732,7 @@
         <v>45832.7072800926</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36789,7 +36789,7 @@
         <v>44995.57965277778</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36846,7 +36846,7 @@
         <v>45003.90380787037</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         <v>44315</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>45477.50987268519</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37017,7 +37017,7 @@
         <v>44995</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37074,7 +37074,7 @@
         <v>45835.51372685185</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>45121</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>45191.58287037037</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>44326.32891203704</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>44326.34681712963</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37359,7 +37359,7 @@
         <v>45126</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37416,7 +37416,7 @@
         <v>45514.38017361111</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>45146.35854166667</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37530,7 +37530,7 @@
         <v>44979.50762731482</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37587,7 +37587,7 @@
         <v>45113.63261574074</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37644,7 +37644,7 @@
         <v>45113.64193287037</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37701,7 +37701,7 @@
         <v>45477.69497685185</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37763,7 +37763,7 @@
         <v>44126.66101851852</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37820,7 +37820,7 @@
         <v>45167.65172453703</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>45637.57834490741</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37934,7 +37934,7 @@
         <v>44271</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>45524.50288194444</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38048,7 +38048,7 @@
         <v>44959</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38105,7 +38105,7 @@
         <v>45068.41424768518</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>45707</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>44851.4281712963</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>44608</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>45095</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>45069</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>45069</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38509,7 +38509,7 @@
         <v>45401.4321412037</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38566,7 +38566,7 @@
         <v>45524.58461805555</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38623,7 +38623,7 @@
         <v>44580.64971064815</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38680,7 +38680,7 @@
         <v>45348.45074074074</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>45107.60460648148</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>45373.48118055556</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38851,7 +38851,7 @@
         <v>45408</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38908,7 +38908,7 @@
         <v>45645.58637731482</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38965,7 +38965,7 @@
         <v>45376.6791087963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>44445</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>45161.329375</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39141,7 +39141,7 @@
         <v>45636.63569444444</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39198,7 +39198,7 @@
         <v>44683</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>44984.56648148148</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39312,7 +39312,7 @@
         <v>45629.44709490741</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>45252.41863425926</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39426,7 +39426,7 @@
         <v>45881.41793981481</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39483,7 +39483,7 @@
         <v>45881.37207175926</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39540,7 +39540,7 @@
         <v>44761.65730324074</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39597,7 +39597,7 @@
         <v>45461.49600694444</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39654,7 +39654,7 @@
         <v>44802.69710648148</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39711,7 +39711,7 @@
         <v>45349.90940972222</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39768,7 +39768,7 @@
         <v>45728</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39825,7 +39825,7 @@
         <v>45422.47181712963</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39882,7 +39882,7 @@
         <v>44808.80826388889</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39939,7 +39939,7 @@
         <v>45841.36670138889</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39996,7 +39996,7 @@
         <v>45632</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40053,7 +40053,7 @@
         <v>45776</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40110,7 +40110,7 @@
         <v>45776</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40167,7 +40167,7 @@
         <v>45805</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>45805</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>45841.65936342593</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>44078</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40395,7 +40395,7 @@
         <v>44210</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40452,7 +40452,7 @@
         <v>45841.44533564815</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>45841.44762731482</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>44159</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40623,7 +40623,7 @@
         <v>44449</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>45189.50895833333</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>45707</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40794,7 +40794,7 @@
         <v>44524</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40851,7 +40851,7 @@
         <v>45845.41</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40908,7 +40908,7 @@
         <v>45091.60043981481</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>45772.39434027778</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41022,7 +41022,7 @@
         <v>45049.61376157407</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41079,7 +41079,7 @@
         <v>45887.58094907407</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41136,7 +41136,7 @@
         <v>45621</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41193,7 +41193,7 @@
         <v>44531.67679398148</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>45051</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>45051.4380787037</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41364,7 +41364,7 @@
         <v>45736.56527777778</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>44897.65846064815</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41478,7 +41478,7 @@
         <v>45887.56543981482</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>45887.5702662037</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>45126.38699074074</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45126.47204861111</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45884.31863425926</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45113</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>45323.40695601852</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45887.57563657407</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>44673.38012731481</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41991,7 +41991,7 @@
         <v>44236.8744212963</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>45727.64369212963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>45596.75166666666</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>45845</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>44235</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>44893.57989583333</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>45888.33114583333</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45554</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
         <v>45681.58681712963</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42509,7 +42509,7 @@
         <v>45846</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>45668.41509259259</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>45104</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42680,7 +42680,7 @@
         <v>45335</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42737,7 +42737,7 @@
         <v>45335.67450231482</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42794,7 +42794,7 @@
         <v>44759.39475694444</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42851,7 +42851,7 @@
         <v>44349.62881944444</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42908,7 +42908,7 @@
         <v>45200.41958333334</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42965,7 +42965,7 @@
         <v>45755.52962962963</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43022,7 +43022,7 @@
         <v>45070.62878472222</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43079,7 +43079,7 @@
         <v>44236.88402777778</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43136,7 +43136,7 @@
         <v>44594</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43193,7 +43193,7 @@
         <v>45222</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43250,7 +43250,7 @@
         <v>45323.39561342593</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43307,7 +43307,7 @@
         <v>44852.57822916667</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43364,7 +43364,7 @@
         <v>44944</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43421,7 +43421,7 @@
         <v>45849.46575231481</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43478,7 +43478,7 @@
         <v>45072</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43535,7 +43535,7 @@
         <v>45149.35745370371</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>45370.74839120371</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43649,7 +43649,7 @@
         <v>45400.68645833333</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>45111.65074074074</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43763,7 +43763,7 @@
         <v>45021.50722222222</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43820,7 +43820,7 @@
         <v>45310.58832175926</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43877,7 +43877,7 @@
         <v>44239</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43934,7 +43934,7 @@
         <v>45204</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43996,7 +43996,7 @@
         <v>45062.65315972222</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44053,7 +44053,7 @@
         <v>44900</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44110,7 +44110,7 @@
         <v>44922.58392361111</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44167,7 +44167,7 @@
         <v>45625</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44229,7 +44229,7 @@
         <v>44239</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44286,7 +44286,7 @@
         <v>44278</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>45562.50462962963</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44400,7 +44400,7 @@
         <v>45103.68170138889</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44457,7 +44457,7 @@
         <v>45688</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>44781</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44571,7 +44571,7 @@
         <v>45466.85056712963</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44628,7 +44628,7 @@
         <v>44589.42831018518</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>44203.61291666667</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44742,7 +44742,7 @@
         <v>45716.34990740741</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44799,7 +44799,7 @@
         <v>45327.39255787037</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>

--- a/Översikt EMMABODA.xlsx
+++ b/Översikt EMMABODA.xlsx
@@ -567,7 +567,7 @@
         <v>44314</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         <v>45377.5588425926</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45369</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45818</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>44811</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>44238</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44445</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>45161.33116898148</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>44570.72098379629</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>44762</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>44495</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>44120</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>44984.36140046296</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>45229.67172453704</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>44966.54540509259</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>44488</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45335</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45068.42262731482</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>44405.32738425926</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>44140</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>44089</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>44082</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>44120.38783564815</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>44459.43425925926</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>44105</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>44379.56671296297</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>44530.4546875</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>44496.52702546296</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44441.48626157407</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>44488</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>44764.45645833333</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>44405.31638888889</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>44405.31894675926</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>44405</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44530.4562037037</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44120.39879629629</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>44496.5110300926</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>44405.32319444444</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44228</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>44454.86018518519</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>44117.6835300926</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>44264.36884259259</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>44454</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>44529</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>44251</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>44490</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44110</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>44211</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>44601.34255787037</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>44431</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>44600</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>44383.5654050926</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>44097</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>44280.65521990741</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>44251</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>44507</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>44507.56921296296</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>44507</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>44507</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>44297</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>44416</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44416</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44442</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>44240</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>44238</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>44599.69461805555</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>44728.83878472223</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>44211</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>44326.44194444444</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>44691</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>44628.35012731481</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>44504.38268518518</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>44387</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>44379</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>44515.44268518518</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>44383.6131712963</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>44851.40596064815</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>44860.88715277778</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>44239</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>44118</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>44082</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>44240.59631944444</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>44648.3578587963</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>44462.69965277778</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>44523</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>44278</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>44628</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>44788.65715277778</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>44347.43119212963</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>44416</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>44382.6675925926</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>44361.39021990741</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>44347.44501157408</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>44405</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>44627.34532407407</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44392.4420949074</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>44075</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>44109</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>44112</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>44462</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>44240.57777777778</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>44148</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44498</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>44120</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>44768.83986111111</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>44851.49548611111</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>44529.29797453704</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>44249</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>44172</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>44277</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>44320</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>44208</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>44208</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>44385</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>44347.43444444444</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>44813</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>44809.43158564815</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>44771</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>44202</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>44202</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>44412</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         <v>44587.42887731481</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>44433</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>44251</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>44496</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>44466.39774305555</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>44507</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>44507</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44487</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>44405</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>44405</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44383.61637731481</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>44147</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>44416</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>44652</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>44628.36534722222</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>44600</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>44421</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>44120</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>44600.45505787037</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44110</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>44501</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>44116.37994212963</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44841.3953125</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>44293</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44148</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>44148</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>44256</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>44852.48653935185</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>44295</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>44847.55930555556</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>44148</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>44839.33949074074</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>44382.66943287037</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>44743.42285879629</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>44180</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>44722.49396990741</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>44083</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>44532.70575231482</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>44488</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>44120.39627314815</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>44223</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>44452.30709490741</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>44210.32178240741</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>44238</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>44385</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>44076</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>44615</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>44412</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>44470.31766203704</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>44083</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>44622.48368055555</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>44593.62412037037</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>44652</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>44655.9318287037</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44699.83193287037</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>44162.37409722222</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44524.72388888889</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>44712.48467592592</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>44589.43354166667</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>44820</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>44706</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>44383.559375</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>44383.61515046296</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>44110</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>44302.5521875</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>44167</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>44551</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>44340</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>44431.41373842592</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>44600.45703703703</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>44284.40975694444</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>44302.54723379629</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>44454</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>44743.38194444445</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>44074</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>44725</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>44600.45854166667</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>44530</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>44739.37986111111</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>44078</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>45211</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>45719</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>44788.66310185185</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>45539.28254629629</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12890,7 +12890,7 @@
         <v>45348.45074074074</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>45069</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>45069</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>45397.44292824074</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>45048.43734953704</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>45126.47756944445</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>45187.44503472222</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>44959</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>45219</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>45335</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>45719</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>45204</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>45561</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>44977.37475694445</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>45327.39255787037</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>45078.59818287037</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>45411.45418981482</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>45190</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>45574.45165509259</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>44315</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14045,7 +14045,7 @@
         <v>44771.43327546296</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>45126.38699074074</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>44728.83686342592</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>45440</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>44979.50762731482</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>45422.39476851852</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>45093.61918981482</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>44236.8744212963</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>44382</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>45551</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>45229.67283564815</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>45385.48972222222</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>45523.52064814815</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>45771</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>45215</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>44203.61291666667</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>44949.42457175926</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15019,7 +15019,7 @@
         <v>45684.66949074074</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15076,7 +15076,7 @@
         <v>45624.64013888889</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45534.66148148148</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>45777.37217592593</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>45777.3700462963</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15304,7 +15304,7 @@
         <v>44852.57822916667</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>45121</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>45484.49533564815</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>45777.51607638889</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>45351.58540509259</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>45341.37961805556</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>45779.45815972222</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         <v>45779.46054398148</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>45296</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>45782.455</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>44953</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>45323.40695601852</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44953</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44572</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>45531.38554398148</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>45600.65333333334</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>44223</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>44593.76921296296</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>45107</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>45750.91766203703</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>45317.45069444444</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>45769.35443287037</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45415.60552083333</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>45638</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>45376.6791087963</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>45610.70957175926</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>45582</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>45565.4407175926</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>45126.31585648148</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         <v>45445.3777662037</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17014,7 +17014,7 @@
         <v>45126.47204861111</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>45548</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>44895</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>45003.90380787037</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>44984.39417824074</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>45019.67677083334</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>45461.49600694444</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>44980</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>44271</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17527,7 +17527,7 @@
         <v>44861</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>45609.51984953704</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         <v>45688</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17698,7 +17698,7 @@
         <v>44326.32891203704</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17755,7 +17755,7 @@
         <v>44326.34681712963</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>44840</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>45484.35097222222</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17931,7 +17931,7 @@
         <v>45475.46671296296</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>44347.43795138889</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>45386.35418981482</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>45400.91444444445</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>45132</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18216,7 +18216,7 @@
         <v>44907.44033564815</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>45775.59086805556</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>45474.61877314815</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>44453</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18444,7 +18444,7 @@
         <v>45566.63414351852</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>45789.54855324074</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>44600.50372685185</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>45481.92570601852</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>45400</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>45037.64929398148</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>44982.67675925926</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>45790.40994212963</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>45161.329375</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>45323.75855324074</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>44088</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>45273.62567129629</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>44993</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>45433</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>45146.35854166667</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>45455.38807870371</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>45714.62857638889</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>44494</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>45477.50987268519</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>45514.38017361111</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>44951</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>45795.67989583333</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>45559</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>45161</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19837,7 +19837,7 @@
         <v>44519</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>44530.5225462963</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>45743</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>45797.45761574074</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>44400.37826388889</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>45797.44099537037</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20179,7 +20179,7 @@
         <v>45800.58695601852</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20236,7 +20236,7 @@
         <v>45800.5805787037</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>44404</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>45126</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>45126</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20464,7 +20464,7 @@
         <v>45191.56679398148</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>45126</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>45189.50841435185</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>45189.50895833333</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>45632</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>45537</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>44550.40824074074</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>45205.49876157408</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>45099</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         <v>45070.62878472222</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>44977</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21091,7 +21091,7 @@
         <v>45167.65172453703</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>44896.4815625</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
         <v>45681.58681712963</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>44900.36804398148</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>45537</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>45799.55665509259</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>45665.45535879629</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>45562.50462962963</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>45803.56060185185</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>45475.36099537037</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21661,7 +21661,7 @@
         <v>45804.56436342592</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>45804.35590277778</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>44958</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>45741.70216435185</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>44893.57989583333</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21946,7 +21946,7 @@
         <v>45644.45738425926</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>45587.54915509259</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         <v>44683</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>45078.5972337963</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22179,7 +22179,7 @@
         <v>45078.59965277778</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>45084.66810185185</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>45554</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22360,7 +22360,7 @@
         <v>45349.64855324074</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>44995</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>45072</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>45622.56673611111</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>45155</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>45159.4650925926</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22702,7 +22702,7 @@
         <v>45573.3758912037</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>44299</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>45225.62575231482</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>45327.37474537037</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>45063</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>44783.34944444444</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>44897.66574074074</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>45091</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>44652</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>44949</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>44665.90422453704</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>45230</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>45349.90940972222</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>45007.53736111111</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>44376.82413194444</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>45400.68645833333</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>45813.45756944444</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
         <v>45232</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23733,7 +23733,7 @@
         <v>44580.64971064815</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>45818</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23847,7 +23847,7 @@
         <v>45022.634375</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         <v>45022.64363425926</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>44839</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>44955</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45182.57702546296</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>45818</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>45818</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24246,7 +24246,7 @@
         <v>45636.63883101852</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24303,7 +24303,7 @@
         <v>45098.91159722222</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>45211</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24417,7 +24417,7 @@
         <v>45706.44140046297</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>44445</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>45861.33920138889</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>45819.69038194444</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>45392.5746412037</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>44699.83489583333</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45691.394375</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>45040</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>45554</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>45166</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>45166</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>45252.41863425926</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>45825.73362268518</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>45826.36164351852</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45148.51032407407</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>45392.58935185185</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>44995.57965277778</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>45826.73186342593</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25448,7 +25448,7 @@
         <v>45826.35939814815</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25505,7 +25505,7 @@
         <v>45826.3639699074</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25562,7 +25562,7 @@
         <v>44973.864375</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>45826.36921296296</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>45531.50122685185</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>45126</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>45434.59488425926</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>44594</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>45825.44528935185</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>44524</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45867.57765046296</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>45826.35645833334</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>44978.31736111111</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>45825.4341087963</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>45707</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>45763</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>44953</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>44690</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>45021.50722222222</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>45021.50942129629</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>44619</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>45615</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>45048.435</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>45408</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>45238</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>44978.32152777778</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>45769.60783564814</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>45832.38621527778</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>45394</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>45182</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>45832.7072800926</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44222</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>44748.54626157408</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>45863</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>45832.40292824074</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>45857</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>45062.65315972222</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>44728.36712962963</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>45191.58287037037</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>45095</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>44777</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44960</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>45188</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>45188</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>45362.96539351852</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>45400.62210648148</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>45009.46947916667</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>45009</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>45107.47519675926</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>45422.47181712963</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>45559.60966435185</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>44673.38012731481</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28427,7 +28427,7 @@
         <v>44273</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>45084</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28541,7 +28541,7 @@
         <v>45355.42155092592</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>45164.64883101852</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28655,7 +28655,7 @@
         <v>44749.78425925926</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28712,7 +28712,7 @@
         <v>44700.61766203704</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28769,7 +28769,7 @@
         <v>44726</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>45707</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>45230.63987268518</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>44802.69710648148</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>45401.43559027778</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>44965.4890162037</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45099.4612037037</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>45629.44709490741</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>44852.5103125</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>45258</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29344,7 +29344,7 @@
         <v>45835.51372685185</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29401,7 +29401,7 @@
         <v>45258.50520833334</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29458,7 +29458,7 @@
         <v>45258</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>45736.56527777778</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29572,7 +29572,7 @@
         <v>45735.47873842593</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29629,7 +29629,7 @@
         <v>45574.38966435185</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>45881.41793981481</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>45009.36045138889</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45009.40710648148</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>45107</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>44922.58392361111</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>44743.42150462963</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>45475.36554398148</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>45716.5465625</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>45881.37207175926</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>44384</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>45757.63991898148</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>44799.28053240741</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>44827</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>45092</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>45092</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>45301</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30603,7 +30603,7 @@
         <v>45841.44533564815</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30660,7 +30660,7 @@
         <v>45841.44762731482</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>45727.45094907407</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>45776</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>45776</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>45805</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30945,7 +30945,7 @@
         <v>45805</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
         <v>45229.52315972222</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31059,7 +31059,7 @@
         <v>45309.61168981482</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31116,7 +31116,7 @@
         <v>45126.475625</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31173,7 +31173,7 @@
         <v>45884.31863425926</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31230,7 +31230,7 @@
         <v>45841.65936342593</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31287,7 +31287,7 @@
         <v>45841.36670138889</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>45515.76115740741</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31401,7 +31401,7 @@
         <v>45621</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>45307.37699074074</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31515,7 +31515,7 @@
         <v>45716.34990740741</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>45190</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>45846</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>45888.33114583333</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31743,7 +31743,7 @@
         <v>45673.67064814815</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>45310.58383101852</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>45887.58094907407</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>45477.69497685185</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31976,7 +31976,7 @@
         <v>44473</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>45887.57563657407</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>45845</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>45845.41</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>44235</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>45079</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>45727.64369212963</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>44851.49424768519</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>45887.56543981482</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>45887.5702662037</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>45645.58637731482</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>45089.38663194444</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>45614.54209490741</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32717,7 +32717,7 @@
         <v>45113.63261574074</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32774,7 +32774,7 @@
         <v>45596.75166666666</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32831,7 +32831,7 @@
         <v>44893.48324074074</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32888,7 +32888,7 @@
         <v>45772.39609953704</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>45775.59498842592</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33002,7 +33002,7 @@
         <v>45849.46575231481</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33059,7 +33059,7 @@
         <v>45716.39373842593</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33116,7 +33116,7 @@
         <v>45102</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33173,7 +33173,7 @@
         <v>45615</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>45852.5841087963</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33287,7 +33287,7 @@
         <v>45818</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>45159.46884259259</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>44769.56326388889</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>45551.56715277778</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33520,7 +33520,7 @@
         <v>45102</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33577,7 +33577,7 @@
         <v>45852.58133101852</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33634,7 +33634,7 @@
         <v>45187.47203703703</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>45851.91112268518</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>45851.91469907408</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>45852</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>44729.41611111111</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>45401.4321412037</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>44851.4281712963</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>45722</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>45196</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34147,7 +34147,7 @@
         <v>45392.58570601852</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34204,7 +34204,7 @@
         <v>44897.54603009259</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34261,7 +34261,7 @@
         <v>45897.39096064815</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34318,7 +34318,7 @@
         <v>44781</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34375,7 +34375,7 @@
         <v>45856.47141203703</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>45148.50620370371</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34489,7 +34489,7 @@
         <v>45323.39561342593</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45897.60010416667</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34603,7 +34603,7 @@
         <v>45897.63128472222</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34660,7 +34660,7 @@
         <v>45855.72674768518</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>44487.60532407407</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34774,7 +34774,7 @@
         <v>45323</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34831,7 +34831,7 @@
         <v>45726.59443287037</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34888,7 +34888,7 @@
         <v>44984.56648148148</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34945,7 +34945,7 @@
         <v>44761.65730324074</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>45113.64193287037</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35059,7 +35059,7 @@
         <v>45524.50288194444</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>45742.80981481481</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>44683.43862268519</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35230,7 +35230,7 @@
         <v>45637.58159722222</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35287,7 +35287,7 @@
         <v>44349.62881944444</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35344,7 +35344,7 @@
         <v>45722</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35401,7 +35401,7 @@
         <v>44424</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>45466.85056712963</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>45327.39550925926</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>44488</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35634,7 +35634,7 @@
         <v>45296</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         <v>45445.39274305556</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35748,7 +35748,7 @@
         <v>45743</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35805,7 +35805,7 @@
         <v>44235</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35862,7 +35862,7 @@
         <v>45021.67435185185</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35919,7 +35919,7 @@
         <v>45067</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>45637.57834490741</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>44278.36359953704</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36090,7 +36090,7 @@
         <v>45749.44238425926</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>44993.56126157408</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36204,7 +36204,7 @@
         <v>44424</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36261,7 +36261,7 @@
         <v>44143</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36323,7 +36323,7 @@
         <v>45716</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36380,7 +36380,7 @@
         <v>45716</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>44530.53258101852</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36494,7 +36494,7 @@
         <v>45028</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36551,7 +36551,7 @@
         <v>44586</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>44278</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>44416</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>45772.39268518519</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>44447</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36836,7 +36836,7 @@
         <v>45200.41958333334</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36893,7 +36893,7 @@
         <v>45740.50775462963</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36950,7 +36950,7 @@
         <v>45196.6208449074</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37007,7 +37007,7 @@
         <v>44589.42831018518</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37064,7 +37064,7 @@
         <v>44405.3347337963</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>44518</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37178,7 +37178,7 @@
         <v>45222</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>44433</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>45211</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37349,7 +37349,7 @@
         <v>45524.58461805555</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>44507</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37463,7 +37463,7 @@
         <v>44879</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>44095</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>45049</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37634,7 +37634,7 @@
         <v>44893.78201388889</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>44938.51150462963</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37748,7 +37748,7 @@
         <v>44418.40890046296</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37805,7 +37805,7 @@
         <v>45691.38957175926</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37862,7 +37862,7 @@
         <v>44979.50945601852</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37919,7 +37919,7 @@
         <v>44690.6797337963</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37976,7 +37976,7 @@
         <v>44524</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38033,7 +38033,7 @@
         <v>45606.57038194445</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38090,7 +38090,7 @@
         <v>45415</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38147,7 +38147,7 @@
         <v>45370.74839120371</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38204,7 +38204,7 @@
         <v>45091.60043981481</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38261,7 +38261,7 @@
         <v>45149.35745370371</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38318,7 +38318,7 @@
         <v>45191.37449074074</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38375,7 +38375,7 @@
         <v>45068.41424768518</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38437,7 +38437,7 @@
         <v>44239</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         <v>45155</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         <v>45251.67181712963</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38608,7 +38608,7 @@
         <v>44930.5281712963</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38665,7 +38665,7 @@
         <v>45755.52962962963</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38722,7 +38722,7 @@
         <v>45111.65074074074</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38779,7 +38779,7 @@
         <v>45772.39434027778</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>45049.61376157407</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>45181.58443287037</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38950,7 +38950,7 @@
         <v>45727.45439814815</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39007,7 +39007,7 @@
         <v>45084</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39064,7 +39064,7 @@
         <v>44728.36835648148</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>45425.51765046296</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39178,7 +39178,7 @@
         <v>45036.45335648148</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39235,7 +39235,7 @@
         <v>45117</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39292,7 +39292,7 @@
         <v>45099.49768518518</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>44834.45706018519</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39406,7 +39406,7 @@
         <v>44593.62643518519</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39463,7 +39463,7 @@
         <v>45051</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>45051.4380787037</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39577,7 +39577,7 @@
         <v>44816.64091435185</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39634,7 +39634,7 @@
         <v>45590.56064814814</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>44808.80826388889</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>44608</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>44126.66101851852</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39862,7 +39862,7 @@
         <v>45349.85878472222</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39919,7 +39919,7 @@
         <v>45107.60460648148</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>44944</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>45048</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>44210</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40147,7 +40147,7 @@
         <v>44487</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40209,7 +40209,7 @@
         <v>45514.3787037037</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40266,7 +40266,7 @@
         <v>45514.3809375</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40323,7 +40323,7 @@
         <v>45514.38158564815</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>44236.88402777778</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40437,7 +40437,7 @@
         <v>45740.51246527778</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40494,7 +40494,7 @@
         <v>44759.39475694444</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>45076.58376157407</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40608,7 +40608,7 @@
         <v>45392.57063657408</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>45317.44828703703</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40722,7 +40722,7 @@
         <v>45217</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>45104</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45688</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>45211.67291666667</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40950,7 +40950,7 @@
         <v>45211</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>44455</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>44159</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>45740.50475694444</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41183,7 +41183,7 @@
         <v>45117</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41240,7 +41240,7 @@
         <v>45180</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>45668.41509259259</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41354,7 +41354,7 @@
         <v>45714</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>44239</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41468,7 +41468,7 @@
         <v>44145</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41525,7 +41525,7 @@
         <v>44207.35459490741</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>45757.64254629629</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>45349.81209490741</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41696,7 +41696,7 @@
         <v>45349.86459490741</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41753,7 +41753,7 @@
         <v>45641.74149305555</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41810,7 +41810,7 @@
         <v>44791.33793981482</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41867,7 +41867,7 @@
         <v>45310.58832175926</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41924,7 +41924,7 @@
         <v>44911</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41981,7 +41981,7 @@
         <v>45728</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42038,7 +42038,7 @@
         <v>45394.41221064814</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
         <v>44900</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42152,7 +42152,7 @@
         <v>45189.35297453704</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42209,7 +42209,7 @@
         <v>45113</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42266,7 +42266,7 @@
         <v>45606.56679398148</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42323,7 +42323,7 @@
         <v>45007.52546296296</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42380,7 +42380,7 @@
         <v>45636.63569444444</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42437,7 +42437,7 @@
         <v>45392.57234953704</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42494,7 +42494,7 @@
         <v>45392.58719907407</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42551,7 +42551,7 @@
         <v>45164.64133101852</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42608,7 +42608,7 @@
         <v>45211</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42665,7 +42665,7 @@
         <v>45126.36510416667</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42722,7 +42722,7 @@
         <v>44698.34013888889</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42779,7 +42779,7 @@
         <v>45317.44657407407</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42836,7 +42836,7 @@
         <v>45373.48118055556</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42893,7 +42893,7 @@
         <v>45204</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42955,7 +42955,7 @@
         <v>45335.67450231482</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43012,7 +43012,7 @@
         <v>44228</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>45369.42106481481</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43126,7 +43126,7 @@
         <v>45273.62960648148</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43188,7 +43188,7 @@
         <v>45204</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43250,7 +43250,7 @@
         <v>45595.51280092593</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43307,7 +43307,7 @@
         <v>45433.48228009259</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43364,7 +43364,7 @@
         <v>45579.47649305555</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43421,7 +43421,7 @@
         <v>45716.34835648148</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43478,7 +43478,7 @@
         <v>45237.5672337963</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43535,7 +43535,7 @@
         <v>44531.67679398148</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>44504.38146990741</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43649,7 +43649,7 @@
         <v>45103.68170138889</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>45474.4828587963</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43763,7 +43763,7 @@
         <v>45341.38545138889</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43820,7 +43820,7 @@
         <v>45665.4533912037</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43877,7 +43877,7 @@
         <v>45126.47646990741</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43934,7 +43934,7 @@
         <v>45202.46894675926</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43991,7 +43991,7 @@
         <v>45740.36450231481</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44048,7 +44048,7 @@
         <v>45700</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44105,7 +44105,7 @@
         <v>45281</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>44449</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44219,7 +44219,7 @@
         <v>45155</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>44897.65846064815</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44333,7 +44333,7 @@
         <v>45692.20631944444</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>45716.35474537037</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44447,7 +44447,7 @@
         <v>44519</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>

--- a/Översikt EMMABODA.xlsx
+++ b/Översikt EMMABODA.xlsx
@@ -567,7 +567,7 @@
         <v>44314</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         <v>45377.5588425926</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>45369</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45818</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>44811</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>44238</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44445</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>45161.33116898148</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>44570.72098379629</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>44762</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>44495</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>44120</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>44984.36140046296</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>45229.67172453704</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>44966.54540509259</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>44488</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45335</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45068.42262731482</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>44405.32738425926</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>44140</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>44089</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>44082</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>44120.38783564815</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>44459.43425925926</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>44105</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>44379.56671296297</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>44530.4546875</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>44496.52702546296</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44441.48626157407</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>44488</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>44764.45645833333</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>44405.31638888889</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>44405.31894675926</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>44405</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44530.4562037037</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>44120.39879629629</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>44496.5110300926</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>44405.32319444444</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44228</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>44454.86018518519</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>44117.6835300926</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>44264.36884259259</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>44454</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>44529</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>44251</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>44490</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44110</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>44211</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>44601.34255787037</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>44431</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>44600</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>44383.5654050926</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>44097</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>44280.65521990741</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>44251</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>44507</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>44507.56921296296</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>44507</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>44507</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>44297</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>44416</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44416</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44442</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>44240</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>44238</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>44599.69461805555</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>44728.83878472223</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>44211</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>44326.44194444444</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>44691</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>44628.35012731481</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>44504.38268518518</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>44387</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>44379</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>44515.44268518518</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>44383.6131712963</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>44851.40596064815</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>44860.88715277778</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>44239</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>44118</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>44082</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>44240.59631944444</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>44648.3578587963</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>44462.69965277778</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>44523</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>44278</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>44628</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>44788.65715277778</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>44347.43119212963</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>44416</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>44382.6675925926</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>44361.39021990741</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>44347.44501157408</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>44405</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>44627.34532407407</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44392.4420949074</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>44075</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>44109</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>44112</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>44462</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>44240.57777777778</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>44148</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44498</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>44120</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>44768.83986111111</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>44851.49548611111</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>44529.29797453704</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>44249</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>44172</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>44277</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>44320</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>44208</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>44208</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>44385</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>44347.43444444444</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>44813</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>44809.43158564815</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>44771</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>44202</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>44202</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>44412</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         <v>44587.42887731481</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>44433</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>44251</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>44496</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>44466.39774305555</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>44507</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>44507</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44487</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>44405</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>44405</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44383.61637731481</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>44147</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>44416</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>44652</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>44628.36534722222</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>44600</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>44421</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>44120</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>44600.45505787037</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44110</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>44501</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>44116.37994212963</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44841.3953125</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>44293</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44148</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>44148</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>44256</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>44852.48653935185</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>44295</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>44847.55930555556</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>44148</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>44839.33949074074</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>44382.66943287037</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>44743.42285879629</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>44180</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>44722.49396990741</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>44083</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>44532.70575231482</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>44488</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>44120.39627314815</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>44223</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>44452.30709490741</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>44210.32178240741</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>44238</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>44385</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>44076</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>44615</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>44412</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>44470.31766203704</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>44083</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>44622.48368055555</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>44593.62412037037</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>44652</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>44655.9318287037</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44699.83193287037</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>44162.37409722222</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44524.72388888889</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>44712.48467592592</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>44589.43354166667</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>44820</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>44706</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>44383.559375</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>44383.61515046296</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>44110</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>44302.5521875</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>44167</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>44551</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>44340</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>44431.41373842592</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>44600.45703703703</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>44284.40975694444</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>44302.54723379629</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>44454</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>44743.38194444445</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12320,7 +12320,7 @@
         <v>44074</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>44725</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>44600.45854166667</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>44530</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>44739.37986111111</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>44078</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>45211</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>45719</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>44788.66310185185</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>45539.28254629629</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12890,7 +12890,7 @@
         <v>45348.45074074074</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>45069</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>45069</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>45397.44292824074</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>45048.43734953704</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>45126.47756944445</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>45187.44503472222</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>44959</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>45219</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>45335</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>45719</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>45204</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>45561</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>44977.37475694445</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>45327.39255787037</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>45078.59818287037</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>45411.45418981482</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>45190</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>45574.45165509259</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>44315</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14045,7 +14045,7 @@
         <v>44771.43327546296</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>45126.38699074074</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>44728.83686342592</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>45440</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>44979.50762731482</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>45422.39476851852</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>45093.61918981482</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>44236.8744212963</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>44382</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>45551</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>45229.67283564815</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>45385.48972222222</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>45523.52064814815</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>45771</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>45215</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>44203.61291666667</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>44949.42457175926</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15019,7 +15019,7 @@
         <v>45684.66949074074</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15076,7 +15076,7 @@
         <v>45624.64013888889</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45534.66148148148</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>45777.37217592593</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>45777.3700462963</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15304,7 +15304,7 @@
         <v>44852.57822916667</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>45121</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>45484.49533564815</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>45777.51607638889</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>45351.58540509259</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>45341.37961805556</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>45779.45815972222</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         <v>45779.46054398148</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>45296</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>45782.455</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>44953</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>45323.40695601852</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>44953</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44572</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>45531.38554398148</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>45600.65333333334</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>44223</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>44593.76921296296</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>45107</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>45750.91766203703</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>45317.45069444444</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>45769.35443287037</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45415.60552083333</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>45638</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>45376.6791087963</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>45610.70957175926</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>45582</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>45565.4407175926</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>45126.31585648148</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         <v>45445.3777662037</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17014,7 +17014,7 @@
         <v>45126.47204861111</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>45548</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>44895</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>45003.90380787037</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>44984.39417824074</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>45019.67677083334</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>45461.49600694444</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>44980</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>44271</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17527,7 +17527,7 @@
         <v>44861</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>45609.51984953704</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         <v>45688</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17698,7 +17698,7 @@
         <v>44326.32891203704</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17755,7 +17755,7 @@
         <v>44326.34681712963</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>44840</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>45484.35097222222</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17931,7 +17931,7 @@
         <v>45475.46671296296</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>44347.43795138889</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>45386.35418981482</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>45400.91444444445</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18159,7 +18159,7 @@
         <v>45132</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18216,7 +18216,7 @@
         <v>44907.44033564815</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>45775.59086805556</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>45474.61877314815</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>44453</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18444,7 +18444,7 @@
         <v>45566.63414351852</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>45789.54855324074</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>44600.50372685185</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>45481.92570601852</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>45400</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>45037.64929398148</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>44982.67675925926</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>45790.40994212963</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>45161.329375</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>45323.75855324074</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>44088</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>45273.62567129629</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>44993</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>45433</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>45146.35854166667</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19314,7 +19314,7 @@
         <v>45455.38807870371</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>45714.62857638889</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>44494</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>45477.50987268519</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>45514.38017361111</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>44951</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>45795.67989583333</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>45559</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>45161</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19837,7 +19837,7 @@
         <v>44519</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>44530.5225462963</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>45743</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>45797.45761574074</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>44400.37826388889</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>45797.44099537037</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20179,7 +20179,7 @@
         <v>45800.58695601852</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20236,7 +20236,7 @@
         <v>45800.5805787037</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>44404</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>45126</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>45126</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20464,7 +20464,7 @@
         <v>45191.56679398148</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>45126</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>45189.50841435185</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>45189.50895833333</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>45632</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>45537</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>44550.40824074074</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>45205.49876157408</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>45099</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         <v>45070.62878472222</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>44977</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21091,7 +21091,7 @@
         <v>45167.65172453703</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>44896.4815625</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
         <v>45681.58681712963</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>44900.36804398148</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>45537</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>45799.55665509259</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>45665.45535879629</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>45562.50462962963</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>45803.56060185185</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>45475.36099537037</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21661,7 +21661,7 @@
         <v>45804.56436342592</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>45804.35590277778</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>44958</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>45741.70216435185</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>44893.57989583333</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21946,7 +21946,7 @@
         <v>45644.45738425926</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>45587.54915509259</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         <v>44683</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>45078.5972337963</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22179,7 +22179,7 @@
         <v>45078.59965277778</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>45084.66810185185</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>45554</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22360,7 +22360,7 @@
         <v>45349.64855324074</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>44995</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>45072</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>45622.56673611111</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>45155</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>45159.4650925926</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22702,7 +22702,7 @@
         <v>45573.3758912037</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>44299</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>45225.62575231482</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>45327.37474537037</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>45063</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>44783.34944444444</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>44897.66574074074</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>45091</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>44652</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>44949</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>44665.90422453704</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>45230</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>45349.90940972222</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>45007.53736111111</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>44376.82413194444</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>45400.68645833333</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>45813.45756944444</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
         <v>45232</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23733,7 +23733,7 @@
         <v>44580.64971064815</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>45818</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23847,7 +23847,7 @@
         <v>45022.634375</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         <v>45022.64363425926</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>44839</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>44955</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45182.57702546296</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>45818</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>45818</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24246,7 +24246,7 @@
         <v>45636.63883101852</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24303,7 +24303,7 @@
         <v>45098.91159722222</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>45211</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24417,7 +24417,7 @@
         <v>45706.44140046297</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>44445</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>45861.33920138889</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>45819.69038194444</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>45392.5746412037</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>44699.83489583333</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45691.394375</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>45040</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>45554</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>45166</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>45166</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>45252.41863425926</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>45825.73362268518</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>45826.36164351852</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45148.51032407407</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>45392.58935185185</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>44995.57965277778</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>45826.73186342593</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25448,7 +25448,7 @@
         <v>45826.35939814815</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25505,7 +25505,7 @@
         <v>45826.3639699074</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25562,7 +25562,7 @@
         <v>44973.864375</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>45826.36921296296</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>45531.50122685185</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>45126</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>45434.59488425926</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>44594</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>45825.44528935185</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>44524</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45867.57765046296</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>45826.35645833334</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>44978.31736111111</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>45825.4341087963</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>45707</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>45763</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>44953</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>44690</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>45021.50722222222</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26536,7 +26536,7 @@
         <v>45021.50942129629</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>44619</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>45615</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>45048.435</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>45408</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>45238</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>44978.32152777778</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>45769.60783564814</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>45832.38621527778</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>45394</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>45182</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>45832.7072800926</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44222</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>44748.54626157408</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>45863</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>45832.40292824074</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>45857</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>45062.65315972222</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         <v>44728.36712962963</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>45191.58287037037</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>45095</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>44777</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>44960</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>45188</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>45188</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>45362.96539351852</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>45400.62210648148</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>45009.46947916667</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>45009</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>45107.47519675926</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>45422.47181712963</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>45559.60966435185</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>44673.38012731481</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28427,7 +28427,7 @@
         <v>44273</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>45084</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28541,7 +28541,7 @@
         <v>45355.42155092592</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>45164.64883101852</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28655,7 +28655,7 @@
         <v>44749.78425925926</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28712,7 +28712,7 @@
         <v>44700.61766203704</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28769,7 +28769,7 @@
         <v>44726</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>45707</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>45230.63987268518</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>44802.69710648148</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>45401.43559027778</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>44965.4890162037</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45099.4612037037</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>45629.44709490741</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>44852.5103125</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>45258</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29344,7 +29344,7 @@
         <v>45835.51372685185</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29401,7 +29401,7 @@
         <v>45258.50520833334</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29458,7 +29458,7 @@
         <v>45258</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>45736.56527777778</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29572,7 +29572,7 @@
         <v>45735.47873842593</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29629,7 +29629,7 @@
         <v>45574.38966435185</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>45881.41793981481</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>45009.36045138889</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45009.40710648148</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>45107</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>44922.58392361111</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>44743.42150462963</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30028,7 +30028,7 @@
         <v>45475.36554398148</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         <v>45716.5465625</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>45881.37207175926</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30199,7 +30199,7 @@
         <v>44384</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>45757.63991898148</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>44799.28053240741</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>44827</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>45092</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>45092</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>45301</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30603,7 +30603,7 @@
         <v>45841.44533564815</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30660,7 +30660,7 @@
         <v>45841.44762731482</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>45727.45094907407</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>45776</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>45776</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>45805</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30945,7 +30945,7 @@
         <v>45805</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
         <v>45229.52315972222</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31059,7 +31059,7 @@
         <v>45309.61168981482</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31116,7 +31116,7 @@
         <v>45126.475625</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31173,7 +31173,7 @@
         <v>45884.31863425926</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31230,7 +31230,7 @@
         <v>45841.65936342593</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31287,7 +31287,7 @@
         <v>45841.36670138889</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>45515.76115740741</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31401,7 +31401,7 @@
         <v>45621</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>45307.37699074074</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31515,7 +31515,7 @@
         <v>45716.34990740741</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>45190</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>45846</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>45888.33114583333</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31743,7 +31743,7 @@
         <v>45673.67064814815</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>45310.58383101852</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>45887.58094907407</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>45477.69497685185</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31976,7 +31976,7 @@
         <v>44473</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>45887.57563657407</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>45845</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>45845.41</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>44235</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>45079</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>45727.64369212963</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>44851.49424768519</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>45887.56543981482</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>45887.5702662037</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>45645.58637731482</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>45089.38663194444</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>45614.54209490741</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32717,7 +32717,7 @@
         <v>45113.63261574074</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32774,7 +32774,7 @@
         <v>45596.75166666666</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32831,7 +32831,7 @@
         <v>44893.48324074074</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32888,7 +32888,7 @@
         <v>45772.39609953704</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>45775.59498842592</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33002,7 +33002,7 @@
         <v>45849.46575231481</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33059,7 +33059,7 @@
         <v>45716.39373842593</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33116,7 +33116,7 @@
         <v>45102</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33173,7 +33173,7 @@
         <v>45615</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>45852.5841087963</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33287,7 +33287,7 @@
         <v>45818</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>45159.46884259259</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>44769.56326388889</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>45551.56715277778</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33520,7 +33520,7 @@
         <v>45102</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33577,7 +33577,7 @@
         <v>45852.58133101852</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33634,7 +33634,7 @@
         <v>45187.47203703703</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>45851.91112268518</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>45851.91469907408</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>45852</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>44729.41611111111</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>45401.4321412037</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>44851.4281712963</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>45722</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>45196</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34147,7 +34147,7 @@
         <v>45392.58570601852</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34204,7 +34204,7 @@
         <v>44897.54603009259</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34261,7 +34261,7 @@
         <v>45897.39096064815</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34318,7 +34318,7 @@
         <v>44781</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34375,7 +34375,7 @@
         <v>45856.47141203703</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>45148.50620370371</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34489,7 +34489,7 @@
         <v>45323.39561342593</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45897.60010416667</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34603,7 +34603,7 @@
         <v>45897.63128472222</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34660,7 +34660,7 @@
         <v>45855.72674768518</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>44487.60532407407</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34774,7 +34774,7 @@
         <v>45323</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34831,7 +34831,7 @@
         <v>45726.59443287037</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34888,7 +34888,7 @@
         <v>44984.56648148148</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34945,7 +34945,7 @@
         <v>44761.65730324074</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>45113.64193287037</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35059,7 +35059,7 @@
         <v>45524.50288194444</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>45742.80981481481</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>44683.43862268519</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35230,7 +35230,7 @@
         <v>45637.58159722222</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35287,7 +35287,7 @@
         <v>44349.62881944444</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35344,7 +35344,7 @@
         <v>45722</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35401,7 +35401,7 @@
         <v>44424</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>45466.85056712963</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35515,7 +35515,7 @@
         <v>45327.39550925926</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>44488</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35634,7 +35634,7 @@
         <v>45296</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         <v>45445.39274305556</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35748,7 +35748,7 @@
         <v>45743</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35805,7 +35805,7 @@
         <v>44235</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35862,7 +35862,7 @@
         <v>45021.67435185185</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35919,7 +35919,7 @@
         <v>45067</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>45637.57834490741</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>44278.36359953704</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36090,7 +36090,7 @@
         <v>45749.44238425926</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>44993.56126157408</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36204,7 +36204,7 @@
         <v>44424</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36261,7 +36261,7 @@
         <v>44143</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36323,7 +36323,7 @@
         <v>45716</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36380,7 +36380,7 @@
         <v>45716</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>44530.53258101852</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36494,7 +36494,7 @@
         <v>45028</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36551,7 +36551,7 @@
         <v>44586</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>44278</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>44416</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>45772.39268518519</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>44447</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36836,7 +36836,7 @@
         <v>45200.41958333334</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36893,7 +36893,7 @@
         <v>45740.50775462963</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36950,7 +36950,7 @@
         <v>45196.6208449074</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37007,7 +37007,7 @@
         <v>44589.42831018518</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37064,7 +37064,7 @@
         <v>44405.3347337963</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>44518</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37178,7 +37178,7 @@
         <v>45222</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>44433</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>45211</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37349,7 +37349,7 @@
         <v>45524.58461805555</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>44507</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37463,7 +37463,7 @@
         <v>44879</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>44095</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>45049</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37634,7 +37634,7 @@
         <v>44893.78201388889</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>44938.51150462963</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37748,7 +37748,7 @@
         <v>44418.40890046296</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37805,7 +37805,7 @@
         <v>45691.38957175926</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37862,7 +37862,7 @@
         <v>44979.50945601852</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37919,7 +37919,7 @@
         <v>44690.6797337963</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37976,7 +37976,7 @@
         <v>44524</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38033,7 +38033,7 @@
         <v>45606.57038194445</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38090,7 +38090,7 @@
         <v>45415</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38147,7 +38147,7 @@
         <v>45370.74839120371</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38204,7 +38204,7 @@
         <v>45091.60043981481</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38261,7 +38261,7 @@
         <v>45149.35745370371</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38318,7 +38318,7 @@
         <v>45191.37449074074</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38375,7 +38375,7 @@
         <v>45068.41424768518</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38437,7 +38437,7 @@
         <v>44239</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         <v>45155</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         <v>45251.67181712963</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38608,7 +38608,7 @@
         <v>44930.5281712963</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38665,7 +38665,7 @@
         <v>45755.52962962963</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38722,7 +38722,7 @@
         <v>45111.65074074074</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38779,7 +38779,7 @@
         <v>45772.39434027778</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>45049.61376157407</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>45181.58443287037</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38950,7 +38950,7 @@
         <v>45727.45439814815</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39007,7 +39007,7 @@
         <v>45084</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39064,7 +39064,7 @@
         <v>44728.36835648148</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>45425.51765046296</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39178,7 +39178,7 @@
         <v>45036.45335648148</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39235,7 +39235,7 @@
         <v>45117</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39292,7 +39292,7 @@
         <v>45099.49768518518</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>44834.45706018519</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39406,7 +39406,7 @@
         <v>44593.62643518519</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39463,7 +39463,7 @@
         <v>45051</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>45051.4380787037</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39577,7 +39577,7 @@
         <v>44816.64091435185</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39634,7 +39634,7 @@
         <v>45590.56064814814</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>44808.80826388889</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>44608</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>44126.66101851852</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39862,7 +39862,7 @@
         <v>45349.85878472222</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39919,7 +39919,7 @@
         <v>45107.60460648148</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>44944</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>45048</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>44210</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40147,7 +40147,7 @@
         <v>44487</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40209,7 +40209,7 @@
         <v>45514.3787037037</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40266,7 +40266,7 @@
         <v>45514.3809375</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40323,7 +40323,7 @@
         <v>45514.38158564815</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>44236.88402777778</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40437,7 +40437,7 @@
         <v>45740.51246527778</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40494,7 +40494,7 @@
         <v>44759.39475694444</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>45076.58376157407</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40608,7 +40608,7 @@
         <v>45392.57063657408</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>45317.44828703703</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40722,7 +40722,7 @@
         <v>45217</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>45104</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45688</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>45211.67291666667</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40950,7 +40950,7 @@
         <v>45211</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>44455</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>44159</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>45740.50475694444</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41183,7 +41183,7 @@
         <v>45117</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41240,7 +41240,7 @@
         <v>45180</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>45668.41509259259</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41354,7 +41354,7 @@
         <v>45714</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>44239</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41468,7 +41468,7 @@
         <v>44145</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41525,7 +41525,7 @@
         <v>44207.35459490741</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>45757.64254629629</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>45349.81209490741</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41696,7 +41696,7 @@
         <v>45349.86459490741</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41753,7 +41753,7 @@
         <v>45641.74149305555</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41810,7 +41810,7 @@
         <v>44791.33793981482</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41867,7 +41867,7 @@
         <v>45310.58832175926</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41924,7 +41924,7 @@
         <v>44911</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41981,7 +41981,7 @@
         <v>45728</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42038,7 +42038,7 @@
         <v>45394.41221064814</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
         <v>44900</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42152,7 +42152,7 @@
         <v>45189.35297453704</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42209,7 +42209,7 @@
         <v>45113</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42266,7 +42266,7 @@
         <v>45606.56679398148</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42323,7 +42323,7 @@
         <v>45007.52546296296</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42380,7 +42380,7 @@
         <v>45636.63569444444</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42437,7 +42437,7 @@
         <v>45392.57234953704</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42494,7 +42494,7 @@
         <v>45392.58719907407</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42551,7 +42551,7 @@
         <v>45164.64133101852</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42608,7 +42608,7 @@
         <v>45211</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42665,7 +42665,7 @@
         <v>45126.36510416667</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42722,7 +42722,7 @@
         <v>44698.34013888889</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42779,7 +42779,7 @@
         <v>45317.44657407407</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42836,7 +42836,7 @@
         <v>45373.48118055556</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42893,7 +42893,7 @@
         <v>45204</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42955,7 +42955,7 @@
         <v>45335.67450231482</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43012,7 +43012,7 @@
         <v>44228</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>45369.42106481481</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43126,7 +43126,7 @@
         <v>45273.62960648148</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43188,7 +43188,7 @@
         <v>45204</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43250,7 +43250,7 @@
         <v>45595.51280092593</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43307,7 +43307,7 @@
         <v>45433.48228009259</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43364,7 +43364,7 @@
         <v>45579.47649305555</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43421,7 +43421,7 @@
         <v>45716.34835648148</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43478,7 +43478,7 @@
         <v>45237.5672337963</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43535,7 +43535,7 @@
         <v>44531.67679398148</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>44504.38146990741</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43649,7 +43649,7 @@
         <v>45103.68170138889</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>45474.4828587963</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43763,7 +43763,7 @@
         <v>45341.38545138889</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43820,7 +43820,7 @@
         <v>45665.4533912037</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43877,7 +43877,7 @@
         <v>45126.47646990741</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43934,7 +43934,7 @@
         <v>45202.46894675926</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43991,7 +43991,7 @@
         <v>45740.36450231481</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44048,7 +44048,7 @@
         <v>45700</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44105,7 +44105,7 @@
         <v>45281</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>44449</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44219,7 +44219,7 @@
         <v>45155</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>44897.65846064815</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44333,7 +44333,7 @@
         <v>45692.20631944444</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>45716.35474537037</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44447,7 +44447,7 @@
         <v>44519</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>

--- a/Översikt EMMABODA.xlsx
+++ b/Översikt EMMABODA.xlsx
@@ -567,7 +567,7 @@
         <v>44314</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         <v>45369</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>44811</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>45818</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>45377.5588425926</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>44238</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>45068.42262731482</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>44762</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>44445</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>44966.54540509259</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>44120</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>44570.72098379629</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>44984.36140046296</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>45229.67172453704</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>44495</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>45335</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>44488</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45161.33116898148</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>44405.32738425926</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>44140</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>44089</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>44082</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>44120.38783564815</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>44459.43425925926</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>44105</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>44379.56671296297</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>44530.4546875</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>44496.52702546296</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44441.48626157407</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>44488</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>44764.45645833333</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>44530.4562037037</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>44120.39879629629</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>44496.5110300926</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>44405.31638888889</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>44405.31894675926</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>44405</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>44405.32319444444</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44228</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>44454.86018518519</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>44117.6835300926</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>44264.36884259259</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>44454</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>44529</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>44251</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>44490</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44110</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>44431</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>44211</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>44601.34255787037</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>44600</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>44383.5654050926</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>44097</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>44280.65521990741</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>44251</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>44297</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>44416</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>44416</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>44507</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>44507.56921296296</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>44507</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44507</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44442</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>44238</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>44240</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>44728.83878472223</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>44211</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>44599.69461805555</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>44691</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>44628.35012731481</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>44326.44194444444</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>44504.38268518518</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>44387</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>44383.6131712963</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>44379</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>44515.44268518518</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>44851.40596064815</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>44860.88715277778</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>44239</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>44118</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>44082</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>44240.59631944444</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>44648.3578587963</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>44462.69965277778</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>44523</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>44278</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>44628</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>44788.65715277778</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>44347.43119212963</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>44416</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>44382.6675925926</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>44361.39021990741</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>44347.44501157408</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>44405</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>44627.34532407407</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44392.4420949074</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>44109</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>44112</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>44462</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>44240.57777777778</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>44148</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>44120</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>44498</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>44768.83986111111</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>44851.49548611111</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>44529.29797453704</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>44249</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         <v>44172</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>44277</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44320</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>44208</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>44208</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>44385</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>44347.43444444444</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>44813</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>44809.43158564815</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>44771</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>44202</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>44202</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>44412</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>44587.42887731481</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         <v>44433</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>44251</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>44496</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>44466.39774305555</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>44507</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>44507</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>44487</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>44405</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>44405</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>44383.61637731481</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44147</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>44416</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>44628.36534722222</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>44600</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>44652</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>44421</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>44120</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44600.45505787037</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>44110</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44501</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>44293</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>44148</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44148</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>44852.48653935185</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44295</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>44847.55930555556</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>44148</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         <v>44743.42285879629</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         <v>44839.33949074074</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44382.66943287037</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>44180</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>44083</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>44722.49396990741</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>44532.70575231482</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>44120.39627314815</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>44615</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>44488</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>44385</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>44223</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>44412</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>44622.48368055555</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>44470.31766203704</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>44452.30709490741</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>44210.32178240741</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>44238</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>44524.72388888889</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>44083</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>44593.62412037037</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>44712.48467592592</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>44652</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>44655.9318287037</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>44699.83193287037</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>44162.37409722222</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>44820</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44706</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>44589.43354166667</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44110</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>44167</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>44551</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>44340</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>44383.559375</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>44383.61515046296</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>44431.41373842592</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>44454</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>44302.5521875</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>44600.45703703703</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>44116.37994212963</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>44725</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>44530</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>44600.45854166667</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>44284.40975694444</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>44302.54723379629</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>44743.38194444445</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>45191.37449074074</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>45126.31585648148</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>44788.66310185185</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>44980</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>45078.5972337963</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>44384</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         <v>45606.56679398148</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>45392.58935185185</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>45078.59965277778</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>44256</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>45099</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
         <v>45397.44292824074</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>44993.56126157408</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>45022.634375</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>45022.64363425926</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
         <v>45574.45165509259</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>44841.3953125</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>45727.45439814815</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>45187.47203703703</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>45394</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>44955</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>45637.58159722222</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>45048.435</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>45749.44238425926</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>45401.43559027778</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>45763</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>45351.58540509259</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>45534.66148148148</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>45215</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>45551</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>45777.51607638889</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14045,7 +14045,7 @@
         <v>45777.3700462963</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>45777.37217592593</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>45523.52064814815</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>44949.42457175926</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>44897.54603009259</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>44235</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>45684.66949074074</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>45624.64013888889</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>45722</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>45484.49533564815</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14615,7 +14615,7 @@
         <v>45159.46884259259</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>45219</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>45779.45815972222</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>45779.46054398148</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>45722</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>44652</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>45237.5672337963</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>45782.455</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>45614.54209490741</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>44455</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>45230</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>44095</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15304,7 +15304,7 @@
         <v>45049</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>45445.39274305556</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>45107</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>45445.3777662037</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>44977.37475694445</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>45317.45069444444</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>44690.6797337963</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         <v>45079</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>45211.67291666667</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>45230.63987268518</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>45548</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>45415.60552083333</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>45638</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44382</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>44953</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>45587.54915509259</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>45089.38663194444</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>45251.67181712963</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>45691.38957175926</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>44572</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>45392.58570601852</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>45301</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45019.67677083334</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>45565.4407175926</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>44400.37826388889</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>45386.35418981482</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>45775.59086805556</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>44895</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>45789.54855324074</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         <v>45692.20631944444</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17014,7 +17014,7 @@
         <v>44453</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>45481.92570601852</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>45622.56673611111</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>44973.864375</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>45474.61877314815</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>45566.63414351852</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>45582</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>45609.51984953704</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>45484.35097222222</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17532,7 +17532,7 @@
         <v>45688</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17589,7 +17589,7 @@
         <v>45411.45418981482</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>45610.70957175926</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17703,7 +17703,7 @@
         <v>45341.38545138889</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17760,7 +17760,7 @@
         <v>45078.59818287037</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>45400</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>44519</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>45238</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>44487.60532407407</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>45590.56064814814</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18107,7 +18107,7 @@
         <v>45040</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>45093.61918981482</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45790.40994212963</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>44965.4890162037</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>44743.42150462963</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18392,7 +18392,7 @@
         <v>44749.78425925926</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>45327.39550925926</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>45559.60966435185</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>45309.61168981482</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18620,7 +18620,7 @@
         <v>45327.37474537037</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>45211</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>45211</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18791,7 +18791,7 @@
         <v>44683.43862268519</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>45455.38807870371</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>45757.63991898148</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>44228</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19019,7 +19019,7 @@
         <v>45559</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>44273</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19138,7 +19138,7 @@
         <v>45757.64254629629</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>45665.4533912037</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>45771</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19309,7 +19309,7 @@
         <v>45182</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>45795.67989583333</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>45797.45761574074</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>45433.48228009259</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>45107.47519675926</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>44978.31736111111</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>44978.32152777778</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>45007.52546296296</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
         <v>45007.53736111111</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>45148.50620370371</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19879,7 +19879,7 @@
         <v>45164.64883101852</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19936,7 +19936,7 @@
         <v>45166</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>45166</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20050,7 +20050,7 @@
         <v>44896.4815625</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>45706.44140046297</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>45797.44099537037</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>45148.51032407407</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>45084.66810185185</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>45741.70216435185</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>45475.36554398148</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>44739.37986111111</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>45394.41221064814</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>45606.57038194445</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>45665.45535879629</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>45537</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>44977</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>44949</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>45281</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>45537</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>45799.55665509259</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>45211</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>45021.67435185185</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>45355.42155092592</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>45188</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>45422.39476851852</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>44530.5225462963</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>45189.50841435185</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>44145</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>45369.42106481481</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>44982.67675925926</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>44938.51150462963</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>44834.45706018519</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>44447</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>44791.33793981482</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>44851.49424768519</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>44960</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>44958</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>45803.56060185185</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22050,7 +22050,7 @@
         <v>45800.58695601852</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>44494</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>45800.5805787037</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>44207.35459490741</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44771.43327546296</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>44893.48324074074</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>44783.34944444444</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22449,7 +22449,7 @@
         <v>45349.86459490741</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22506,7 +22506,7 @@
         <v>44416</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>44405.3347337963</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>45804.56436342592</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>44518</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22734,7 +22734,7 @@
         <v>44728.36712962963</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>45804.35590277778</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         <v>45009.36045138889</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45009.40710648148</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22962,7 +22962,7 @@
         <v>45009.46947916667</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>45009</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23076,7 +23076,7 @@
         <v>44487</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>44593.76921296296</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>45539.28254629629</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>45021.50942129629</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>44911</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>45159.4650925926</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>44600.50372685185</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>45415</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>45514.3787037037</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>45514.3809375</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>45514.38158564815</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23708,7 +23708,7 @@
         <v>45202.46894675926</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23765,7 +23765,7 @@
         <v>45475.36099537037</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23822,7 +23822,7 @@
         <v>45323</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>44879</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23936,7 +23936,7 @@
         <v>44088</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -23993,7 +23993,7 @@
         <v>45740.50475694444</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24050,7 +24050,7 @@
         <v>44424</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>45475.46671296296</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>45735.47873842593</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>45155</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>45037.64929398148</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>45126</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24392,7 +24392,7 @@
         <v>45126.36510416667</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24449,7 +24449,7 @@
         <v>44690</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>45126.47646990741</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24563,7 +24563,7 @@
         <v>45155</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24620,7 +24620,7 @@
         <v>45813.45756944444</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>45641.74149305555</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>44593.62643518519</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24791,7 +24791,7 @@
         <v>44953</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24848,7 +24848,7 @@
         <v>45362.96539351852</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>45818</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24962,7 +24962,7 @@
         <v>44665.90422453704</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>45818</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         <v>44504.38146990741</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
         <v>44347.43795138889</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>45819.69038194444</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>45818</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>45126</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25361,7 +25361,7 @@
         <v>45126</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25418,7 +25418,7 @@
         <v>44700.61766203704</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>45867.57765046296</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>45825.44528935185</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25589,7 +25589,7 @@
         <v>45825.4341087963</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>45825.73362268518</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>45826.35645833334</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>44799.28053240741</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>45155</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25874,7 +25874,7 @@
         <v>45225.62575231482</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>45826.36921296296</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -25988,7 +25988,7 @@
         <v>45826.73186342593</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>45826.36164351852</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>45615</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26159,7 +26159,7 @@
         <v>45826.35939814815</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>45826.3639699074</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>45063</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26335,7 +26335,7 @@
         <v>44424</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>45832.40292824074</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26449,7 +26449,7 @@
         <v>45832.38621527778</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>44893.78201388889</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>45832.7072800926</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>45743</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26677,7 +26677,7 @@
         <v>45296</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>44530.53258101852</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26791,7 +26791,7 @@
         <v>45835.51372685185</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>44777</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26905,7 +26905,7 @@
         <v>45644.45738425926</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>45181.58443287037</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>45881.41793981481</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>45881.37207175926</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>45841.36670138889</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>45776</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>45776</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>44852.5103125</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>45190</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>45805</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>45805</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>45433</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>45067</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>45440</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>45841.65936342593</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>44953</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>45841.44533564815</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>45841.44762731482</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27936,7 +27936,7 @@
         <v>45107</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -27993,7 +27993,7 @@
         <v>45845.41</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28050,7 +28050,7 @@
         <v>44222</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>44143</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28169,7 +28169,7 @@
         <v>45887.58094907407</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28226,7 +28226,7 @@
         <v>45621</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28283,7 +28283,7 @@
         <v>44223</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>45211</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>45887.56543981482</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28454,7 +28454,7 @@
         <v>45887.5702662037</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>45884.31863425926</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28568,7 +28568,7 @@
         <v>45887.57563657407</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28625,7 +28625,7 @@
         <v>44729.41611111111</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28682,7 +28682,7 @@
         <v>45727.64369212963</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>45845</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>45636.63883101852</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>45164.64133101852</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>45888.33114583333</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>45846</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>45190</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44993</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>45719</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>45719</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>45349.64855324074</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44984.39417824074</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>45849.46575231481</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>45852</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>45852.5841087963</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>45852.58133101852</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>45775.59498842592</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>45716.39373842593</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>45851.91112268518</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>45851.91469907408</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>45818</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>45772.39609953704</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>45531.38554398148</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>45897.39096064815</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>45897.60010416667</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>45855.72674768518</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>45897.63128472222</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30221,7 +30221,7 @@
         <v>45857</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30278,7 +30278,7 @@
         <v>45856.47141203703</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30335,7 +30335,7 @@
         <v>45901.39177083333</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30392,7 +30392,7 @@
         <v>45579.47649305555</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>45126.475625</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30506,7 +30506,7 @@
         <v>44861</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30563,7 +30563,7 @@
         <v>44507</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30620,7 +30620,7 @@
         <v>45772.39268518519</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30677,7 +30677,7 @@
         <v>45902.4652199074</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30734,7 +30734,7 @@
         <v>45861.33920138889</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>45205.49876157408</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30848,7 +30848,7 @@
         <v>45902.47142361111</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>45474.4828587963</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -30962,7 +30962,7 @@
         <v>45084</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
         <v>45726.59443287037</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31076,7 +31076,7 @@
         <v>44473</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31133,7 +31133,7 @@
         <v>45189.35297453704</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>44404</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31247,7 +31247,7 @@
         <v>45048</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31304,7 +31304,7 @@
         <v>45191.56679398148</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31361,7 +31361,7 @@
         <v>45905.41212962963</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>45126.47756944445</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31475,7 +31475,7 @@
         <v>44619</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>45904.42120370371</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31589,7 +31589,7 @@
         <v>45434.59488425926</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31646,7 +31646,7 @@
         <v>45863</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31703,7 +31703,7 @@
         <v>45574.38966435185</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31760,7 +31760,7 @@
         <v>45036.45335648148</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31817,7 +31817,7 @@
         <v>45204</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>45232</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>44907.44033564815</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>45323.75855324074</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>45098.91159722222</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32112,7 +32112,7 @@
         <v>45273.62960648148</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32174,7 +32174,7 @@
         <v>45392.5746412037</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32231,7 +32231,7 @@
         <v>45211</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>45229.52315972222</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32345,7 +32345,7 @@
         <v>45132</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>45740.50775462963</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32459,7 +32459,7 @@
         <v>45084</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>45341.37961805556</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         <v>44995.57965277778</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32630,7 +32630,7 @@
         <v>45003.90380787037</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>44315</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32744,7 +32744,7 @@
         <v>45477.50987268519</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>44519</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>44995</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>44299</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -32972,7 +32972,7 @@
         <v>45102</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>45102</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33086,7 +33086,7 @@
         <v>45126</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33143,7 +33143,7 @@
         <v>45514.38017361111</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33200,7 +33200,7 @@
         <v>45146.35854166667</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33257,7 +33257,7 @@
         <v>44839</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33314,7 +33314,7 @@
         <v>44126.66101851852</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33371,7 +33371,7 @@
         <v>44271</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33428,7 +33428,7 @@
         <v>44959</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33485,7 +33485,7 @@
         <v>45068.41424768518</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33547,7 +33547,7 @@
         <v>45707</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33604,7 +33604,7 @@
         <v>44851.4281712963</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33661,7 +33661,7 @@
         <v>45317.44828703703</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33718,7 +33718,7 @@
         <v>44608</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33775,7 +33775,7 @@
         <v>45095</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33832,7 +33832,7 @@
         <v>45196.6208449074</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33889,7 +33889,7 @@
         <v>44580.64971064815</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33946,7 +33946,7 @@
         <v>45107.60460648148</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34003,7 +34003,7 @@
         <v>44979.50945601852</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34060,7 +34060,7 @@
         <v>45716.35474537037</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34117,7 +34117,7 @@
         <v>45091</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34174,7 +34174,7 @@
         <v>45716</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34231,7 +34231,7 @@
         <v>45716</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34288,7 +34288,7 @@
         <v>45373.48118055556</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34345,7 +34345,7 @@
         <v>45121</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34402,7 +34402,7 @@
         <v>45191.58287037037</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34459,7 +34459,7 @@
         <v>44326.32891203704</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34516,7 +34516,7 @@
         <v>44326.34681712963</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34573,7 +34573,7 @@
         <v>45161.329375</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34635,7 +34635,7 @@
         <v>44979.50762731482</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>44984.56648148148</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34749,7 +34749,7 @@
         <v>45252.41863425926</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34806,7 +34806,7 @@
         <v>45113.63261574074</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34863,7 +34863,7 @@
         <v>45113.64193287037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34920,7 +34920,7 @@
         <v>45477.69497685185</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -34982,7 +34982,7 @@
         <v>44761.65730324074</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35039,7 +35039,7 @@
         <v>44802.69710648148</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35096,7 +35096,7 @@
         <v>45728</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35153,7 +35153,7 @@
         <v>45422.47181712963</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35210,7 +35210,7 @@
         <v>45167.65172453703</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35267,7 +35267,7 @@
         <v>45637.57834490741</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>45524.50288194444</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35381,7 +35381,7 @@
         <v>44808.80826388889</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35438,7 +35438,7 @@
         <v>45069</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>45069</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35552,7 +35552,7 @@
         <v>45401.4321412037</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>45524.58461805555</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>44210</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>45348.45074074074</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35780,7 +35780,7 @@
         <v>44449</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>45408</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35894,7 +35894,7 @@
         <v>45189.50895833333</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>45772.39434027778</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>45645.58637731482</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>45376.6791087963</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>44445</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>45636.63569444444</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>45049.61376157407</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>44531.67679398148</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>44683</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>45629.44709490741</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>45051</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>45051.4380787037</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>45736.56527777778</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>45126.38699074074</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36692,7 +36692,7 @@
         <v>45126.47204861111</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45461.49600694444</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>45349.90940972222</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36863,7 +36863,7 @@
         <v>45323.40695601852</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36920,7 +36920,7 @@
         <v>44673.38012731481</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>45596.75166666666</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>45632</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>44893.57989583333</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>45554</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>45668.41509259259</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>44759.39475694444</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37324,7 +37324,7 @@
         <v>44349.62881944444</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37381,7 +37381,7 @@
         <v>44159</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37438,7 +37438,7 @@
         <v>45707</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37495,7 +37495,7 @@
         <v>44524</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37552,7 +37552,7 @@
         <v>45091.60043981481</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>44594</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37666,7 +37666,7 @@
         <v>44897.65846064815</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37723,7 +37723,7 @@
         <v>45323.39561342593</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37780,7 +37780,7 @@
         <v>44852.57822916667</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37837,7 +37837,7 @@
         <v>45113</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37894,7 +37894,7 @@
         <v>45072</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37951,7 +37951,7 @@
         <v>45149.35745370371</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38008,7 +38008,7 @@
         <v>44236.8744212963</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38065,7 +38065,7 @@
         <v>44235</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>45681.58681712963</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38179,7 +38179,7 @@
         <v>45111.65074074074</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38236,7 +38236,7 @@
         <v>45310.58832175926</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>45104</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>45335</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>45335.67450231482</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>45200.41958333334</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         <v>45755.52962962963</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         <v>44239</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>45070.62878472222</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>45204</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45062.65315972222</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         <v>44236.88402777778</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>45222</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>44944</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>44278</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>45370.74839120371</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>45400.68645833333</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45562.50462962963</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>45103.68170138889</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>45688</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39324,7 +39324,7 @@
         <v>44589.42831018518</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39381,7 +39381,7 @@
         <v>45021.50722222222</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39438,7 +39438,7 @@
         <v>44726</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39495,7 +39495,7 @@
         <v>45742.80981481481</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39552,7 +39552,7 @@
         <v>45740.36450231481</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39609,7 +39609,7 @@
         <v>44900</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>44524</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39723,7 +39723,7 @@
         <v>44728.83686342592</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39780,7 +39780,7 @@
         <v>45117</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39837,7 +39837,7 @@
         <v>45182.57702546296</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39894,7 +39894,7 @@
         <v>44816.64091435185</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39951,7 +39951,7 @@
         <v>44922.58392361111</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40008,7 +40008,7 @@
         <v>45691.394375</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40065,7 +40065,7 @@
         <v>44840</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40127,7 +40127,7 @@
         <v>44239</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40184,7 +40184,7 @@
         <v>45595.51280092593</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40241,7 +40241,7 @@
         <v>44781</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40298,7 +40298,7 @@
         <v>45673.67064814815</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40355,7 +40355,7 @@
         <v>45466.85056712963</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40412,7 +40412,7 @@
         <v>44203.61291666667</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40469,7 +40469,7 @@
         <v>45714.62857638889</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40526,7 +40526,7 @@
         <v>44897.66574074074</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40583,7 +40583,7 @@
         <v>45273.62567129629</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40645,7 +40645,7 @@
         <v>45349.85878472222</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40702,7 +40702,7 @@
         <v>44827</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40759,7 +40759,7 @@
         <v>45716.34990740741</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>45700</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>45327.39255787037</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>45092</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>45092</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41044,7 +41044,7 @@
         <v>45217</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>45296</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41158,7 +41158,7 @@
         <v>44376.82413194444</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41215,7 +41215,7 @@
         <v>45425.51765046296</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41272,7 +41272,7 @@
         <v>44550.40824074074</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41329,7 +41329,7 @@
         <v>45750.91766203703</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41386,7 +41386,7 @@
         <v>45076.58376157407</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41443,7 +41443,7 @@
         <v>45385.48972222222</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41500,7 +41500,7 @@
         <v>44951</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>44278.36359953704</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41614,7 +41614,7 @@
         <v>45716.34835648148</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41671,7 +41671,7 @@
         <v>45515.76115740741</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41728,7 +41728,7 @@
         <v>45307.37699074074</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41785,7 +41785,7 @@
         <v>45317.44657407407</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>45187.44503472222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41899,7 +41899,7 @@
         <v>45099.49768518518</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41956,7 +41956,7 @@
         <v>44748.54626157408</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42013,7 +42013,7 @@
         <v>45204</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42075,7 +42075,7 @@
         <v>45561</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42137,7 +42137,7 @@
         <v>45392.57234953704</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42194,7 +42194,7 @@
         <v>45392.58719907407</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42251,7 +42251,7 @@
         <v>44433</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42308,7 +42308,7 @@
         <v>45258</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42365,7 +42365,7 @@
         <v>45727.45094907407</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42422,7 +42422,7 @@
         <v>45349.81209490741</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42479,7 +42479,7 @@
         <v>45310.58383101852</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42536,7 +42536,7 @@
         <v>44699.83489583333</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42593,7 +42593,7 @@
         <v>45740.51246527778</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42650,7 +42650,7 @@
         <v>45573.3758912037</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42707,7 +42707,7 @@
         <v>45400.91444444445</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42764,7 +42764,7 @@
         <v>45117</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42821,7 +42821,7 @@
         <v>45743</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42878,7 +42878,7 @@
         <v>45229.67283564815</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42935,7 +42935,7 @@
         <v>45099.4612037037</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>45188</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43059,7 +43059,7 @@
         <v>45769.60783564814</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43116,7 +43116,7 @@
         <v>45714</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43173,7 +43173,7 @@
         <v>44769.56326388889</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43230,7 +43230,7 @@
         <v>44728.36835648148</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>44488</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43349,7 +43349,7 @@
         <v>45258.50520833334</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45258</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45600.65333333334</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45769.35443287037</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>44930.5281712963</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43634,7 +43634,7 @@
         <v>45400.62210648148</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43691,7 +43691,7 @@
         <v>44698.34013888889</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>45028</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43805,7 +43805,7 @@
         <v>45554</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43867,7 +43867,7 @@
         <v>45551.56715277778</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43929,7 +43929,7 @@
         <v>45392.57063657408</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43986,7 +43986,7 @@
         <v>45531.50122685185</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44043,7 +44043,7 @@
         <v>44900.36804398148</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44100,7 +44100,7 @@
         <v>45196</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44157,7 +44157,7 @@
         <v>44586</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44214,7 +44214,7 @@
         <v>45615</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44271,7 +44271,7 @@
         <v>45161</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44333,7 +44333,7 @@
         <v>45180</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>44418.40890046296</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44447,7 +44447,7 @@
         <v>45716.5465625</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44504,7 +44504,7 @@
         <v>45048.43734953704</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>

--- a/Översikt EMMABODA.xlsx
+++ b/Översikt EMMABODA.xlsx
@@ -567,7 +567,7 @@
         <v>45377.5588425926</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         <v>45369</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>44314</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45818</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>44811</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>44238</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44445</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>45161.33116898148</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>44570.72098379629</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>44762</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>44495</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>44120</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>44984.36140046296</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>45229.67172453704</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>44966.54540509259</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>44488</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45335</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45068.42262731482</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>44405.32738425926</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>44140</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>44089</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>44120.38783564815</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44459.43425925926</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>44105</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>44379.56671296297</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>44530.4546875</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>44441.48626157407</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>44488</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44496.52702546296</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>44120.39879629629</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>44405.31638888889</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>44405.31894675926</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44405</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>44764.45645833333</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>44496.5110300926</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>44530.4562037037</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>44405.32319444444</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>44228</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44454.86018518519</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>44117.6835300926</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>44264.36884259259</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>44251</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>44454</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>44529</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>44490</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>44110</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44601.34255787037</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>44431</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>44211</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>44600</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>44097</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>44280.65521990741</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>44251</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>44507</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>44507.56921296296</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>44507</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>44507</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>44297</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>44416</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>44416</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>44442</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44240</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44383.5654050926</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>44238</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>44728.83878472223</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>44211</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>44599.69461805555</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>44691</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>44628.35012731481</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>44326.44194444444</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>44504.38268518518</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>44387</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>44379</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>44383.6131712963</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>44515.44268518518</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>44851.40596064815</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>44860.88715277778</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>44239</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>44118</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>44240.59631944444</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>44648.3578587963</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>44462.69965277778</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>44523</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>44278</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>44628</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>44788.65715277778</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>44347.43119212963</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>44382.6675925926</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>44416</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>44361.39021990741</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>44347.44501157408</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>44405</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>44627.34532407407</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>44392.4420949074</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>44109</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44112</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>44462</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>44240.57777777778</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>44148</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>44498</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44768.83986111111</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>44120</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>44851.49548611111</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>44529.29797453704</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>44249</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>44172</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>44277</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>44320</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>44208</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44208</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>44385</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>44347.43444444444</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>44813</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>44771</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>44202</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>44809.43158564815</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>44202</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>44412</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>44587.42887731481</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>44433</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>44251</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         <v>44496</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>44466.39774305555</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>44507</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>44507</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>44487</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44405</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
         <v>44405</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>44383.61637731481</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>44147</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>44652</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>44416</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>44628.36534722222</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>44600</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>44421</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>44120</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>44600.45505787037</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>44501</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44110</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>44841.3953125</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>44256</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>44116.37994212963</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>44293</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>44148</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>44148</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>44852.48653935185</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>44295</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>44839.33949074074</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>44382.66943287037</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>44180</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>44722.49396990741</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>44532.70575231482</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>44120.39627314815</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>44847.55930555556</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>44148</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>44655.9318287037</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44743.42285879629</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>44615</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>44385</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>44412</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>44622.48368055555</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>44470.31766203704</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>44593.62412037037</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>44652</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>44699.83193287037</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>44162.37409722222</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>44524.72388888889</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>44488</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>44712.48467592592</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>44820</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>44706</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>44223</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>44383.559375</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>44383.61515046296</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>44454</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44302.5521875</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>44530</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44452.30709490741</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>44210.32178240741</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>45190</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>44284.40975694444</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>44238</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>44302.54723379629</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>44788.66310185185</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>44739.37986111111</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>44743.38194444445</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>45048.43734953704</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>45211</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>45719</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>45348.45074074074</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>45069</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>45069</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>45397.44292824074</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>45187.44503472222</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>45219</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>45719</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>45335</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>45078.59818287037</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>45204</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>45411.45418981482</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>44315</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>44771.43327546296</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>45440</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>45422.39476851852</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>45539.28254629629</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>45561</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>45126.47756944445</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>44959</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>44236.8744212963</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
         <v>44977.37475694445</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>45327.39255787037</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         <v>44382</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>45229.67283564815</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>45385.48972222222</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>45574.45165509259</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13470,7 +13470,7 @@
         <v>45126.38699074074</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>44979.50762731482</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>44728.83686342592</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>45093.61918981482</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>45296</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>45551</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         <v>45771</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>45523.52064814815</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>44203.61291666667</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>45215</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>44949.42457175926</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>45684.66949074074</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>45624.64013888889</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>44852.57822916667</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14268,7 +14268,7 @@
         <v>45534.66148148148</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>45121</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         <v>45341.37961805556</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>45777.37217592593</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>45777.3700462963</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>45484.49533564815</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>45777.51607638889</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
         <v>45351.58540509259</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
         <v>44953</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>45323.40695601852</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>44953</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>45779.45815972222</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>45779.46054398148</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>44572</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>45531.38554398148</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>45782.455</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>45600.65333333334</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
         <v>44589.43354166667</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>44223</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>44593.76921296296</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>45376.6791087963</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15465,7 +15465,7 @@
         <v>45769.35443287037</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>45107</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>45126.31585648148</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>45317.45069444444</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>45003.90380787037</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>45126.47204861111</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>44984.39417824074</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>45019.67677083334</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15921,7 +15921,7 @@
         <v>45415.60552083333</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>45638</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>44980</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>45610.70957175926</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>44271</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>45582</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>45565.4407175926</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>45445.3777662037</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>45461.49600694444</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>44840</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>45548</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>44895</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>45475.46671296296</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>44861</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>45132</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>44326.32891203704</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>44326.34681712963</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>44600.50372685185</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>45609.51984953704</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>45688</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>45037.64929398148</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>45484.35097222222</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>44347.43795138889</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>44110</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         <v>45386.35418981482</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>45400.91444444445</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17408,7 +17408,7 @@
         <v>44982.67675925926</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>44907.44033564815</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>45775.59086805556</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>44453</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>45474.61877314815</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>45566.63414351852</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>45789.54855324074</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>45481.92570601852</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>44993</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>45400</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>45433</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>44167</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>44551</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>44340</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>45146.35854166667</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18268,7 +18268,7 @@
         <v>44431.41373842592</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>45161.329375</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>45323.75855324074</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>44088</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>45273.62567129629</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>44600.45703703703</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>44494</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>45455.38807870371</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>45559</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>45477.50987268519</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>45514.38017361111</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>44725</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>44951</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>45743</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45161</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>45795.67989583333</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>44519</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>45126</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>45126</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>45191.56679398148</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>45126</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>44530.5225462963</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>45205.49876157408</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>45167.65172453703</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>45681.58681712963</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>45797.45761574074</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>44400.37826388889</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19832,7 +19832,7 @@
         <v>44404</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>45741.70216435185</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>45189.50841435185</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20003,7 +20003,7 @@
         <v>45189.50895833333</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>45632</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>45797.44099537037</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>45800.58695601852</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         <v>44550.40824074074</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         <v>44600.45854166667</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>45800.5805787037</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>45099</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>45644.45738425926</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>45070.62878472222</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>45537</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>44896.4815625</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>45078.5972337963</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>45078.59965277778</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>45084.66810185185</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>44977</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>44900.36804398148</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>45072</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21039,7 +21039,7 @@
         <v>45622.56673611111</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         <v>45537</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>45159.4650925926</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         <v>45573.3758912037</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
         <v>45799.55665509259</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>45665.45535879629</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45562.50462962963</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>44299</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>45225.62575231482</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>45803.56060185185</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>45327.37474537037</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>45063</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>45475.36099537037</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21785,7 +21785,7 @@
         <v>45804.56436342592</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>45804.35590277778</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>44958</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21956,7 +21956,7 @@
         <v>44783.34944444444</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         <v>45091</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>44652</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>44665.90422453704</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>44893.57989583333</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>45230</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>45587.54915509259</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22355,7 +22355,7 @@
         <v>44683</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22412,7 +22412,7 @@
         <v>44376.82413194444</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22469,7 +22469,7 @@
         <v>45232</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>45554</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>45349.64855324074</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>44995</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22702,7 +22702,7 @@
         <v>45155</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>45182.57702546296</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>44897.66574074074</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>44949</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>45392.5746412037</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>44699.83489583333</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>45349.90940972222</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45007.53736111111</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>45400.68645833333</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>45148.51032407407</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23272,7 +23272,7 @@
         <v>44580.64971064815</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>45022.634375</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23386,7 +23386,7 @@
         <v>45022.64363425926</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>45531.50122685185</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23500,7 +23500,7 @@
         <v>45126</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23557,7 +23557,7 @@
         <v>45434.59488425926</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>44839</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23671,7 +23671,7 @@
         <v>44955</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>45813.45756944444</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23785,7 +23785,7 @@
         <v>44619</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>45818</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>45636.63883101852</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>45098.91159722222</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
         <v>45211</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24070,7 +24070,7 @@
         <v>45818</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>45706.44140046297</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>45408</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24241,7 +24241,7 @@
         <v>44445</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>45394</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>45818</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>45691.394375</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>45040</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>45819.69038194444</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>44728.36712962963</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>45554</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>45166</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45166</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>45252.41863425926</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>45188</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>45188</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>45400.62210648148</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>45392.58935185185</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>44995.57965277778</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>45825.73362268518</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>45826.36164351852</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>45107.47519675926</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44973.864375</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>45826.73186342593</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>45826.35939814815</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>45826.3639699074</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>45826.36921296296</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25629,7 +25629,7 @@
         <v>44673.38012731481</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25686,7 +25686,7 @@
         <v>44273</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25743,7 +25743,7 @@
         <v>45825.44528935185</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>44594</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>45826.35645833334</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25914,7 +25914,7 @@
         <v>45164.64883101852</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>44749.78425925926</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26028,7 +26028,7 @@
         <v>44524</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>45825.4341087963</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>44726</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>45707</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>44802.69710648148</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>44978.31736111111</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>45707</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>45763</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>44953</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>45401.43559027778</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         <v>44690</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26655,7 +26655,7 @@
         <v>45615</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         <v>45021.50722222222</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>45021.50942129629</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>45258.50520833334</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26883,7 +26883,7 @@
         <v>45258</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26940,7 +26940,7 @@
         <v>45736.56527777778</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26997,7 +26997,7 @@
         <v>45832.38621527778</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>45735.47873842593</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>45048.435</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>45832.7072800926</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>45238</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>44978.32152777778</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>45832.40292824074</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>45769.60783564814</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>45182</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>45475.36554398148</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>44222</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>45716.5465625</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>44748.54626157408</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>44384</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>45062.65315972222</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>45757.63991898148</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>45191.58287037037</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>44799.28053240741</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>45095</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>44777</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>44960</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>45362.96539351852</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>45009.46947916667</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>45009</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>45422.47181712963</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28427,7 +28427,7 @@
         <v>45559.60966435185</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>45084</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28541,7 +28541,7 @@
         <v>45355.42155092592</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>44700.61766203704</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28655,7 +28655,7 @@
         <v>45230.63987268518</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28712,7 +28712,7 @@
         <v>44827</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28769,7 +28769,7 @@
         <v>45301</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>45727.45094907407</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>45309.61168981482</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>45126.475625</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>44965.4890162037</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>45099.4612037037</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>45835.51372685185</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>45307.37699074074</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>45629.44709490741</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>44852.5103125</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29344,7 +29344,7 @@
         <v>45258</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29401,7 +29401,7 @@
         <v>45574.38966435185</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29458,7 +29458,7 @@
         <v>45009.36045138889</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>45009.40710648148</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29572,7 +29572,7 @@
         <v>45107</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29629,7 +29629,7 @@
         <v>45716.34990740741</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>45190</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>44922.58392361111</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45310.58383101852</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>44743.42150462963</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>45477.69497685185</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>45092</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>45092</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>44851.49424768519</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>45229.52315972222</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>45881.41793981481</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>45515.76115740741</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>45089.38663194444</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>45673.67064814815</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>44473</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>44235</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>45079</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30603,7 +30603,7 @@
         <v>45645.58637731482</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30660,7 +30660,7 @@
         <v>45614.54209490741</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>45113.63261574074</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>45596.75166666666</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>44893.48324074074</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>45102</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30945,7 +30945,7 @@
         <v>45615</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
         <v>45102</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31059,7 +31059,7 @@
         <v>44729.41611111111</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31116,7 +31116,7 @@
         <v>45159.46884259259</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31173,7 +31173,7 @@
         <v>44769.56326388889</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31230,7 +31230,7 @@
         <v>45722</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31287,7 +31287,7 @@
         <v>45551.56715277778</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>45187.47203703703</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>45881.37207175926</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>44781</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>45148.50620370371</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31577,7 +31577,7 @@
         <v>45401.4321412037</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>44851.4281712963</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>45726.59443287037</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>44984.56648148148</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>44761.65730324074</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>45196</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31919,7 +31919,7 @@
         <v>45113.64193287037</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31976,7 +31976,7 @@
         <v>45392.58570601852</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>45742.80981481481</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>44683.43862268519</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>44349.62881944444</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>45722</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>44897.54603009259</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>45445.39274305556</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>45841.44533564815</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>45841.44762731482</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>45021.67435185185</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>45067</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>45637.57834490741</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>44278.36359953704</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32717,7 +32717,7 @@
         <v>45323.39561342593</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32774,7 +32774,7 @@
         <v>45749.44238425926</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32831,7 +32831,7 @@
         <v>45776</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32888,7 +32888,7 @@
         <v>45776</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>45805</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33002,7 +33002,7 @@
         <v>45805</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33059,7 +33059,7 @@
         <v>45716</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33116,7 +33116,7 @@
         <v>45716</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33173,7 +33173,7 @@
         <v>45028</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>45772.39268518519</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33287,7 +33287,7 @@
         <v>45200.41958333334</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>45740.50775462963</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>45196.6208449074</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>44518</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>45222</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>44433</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>45211</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>44879</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>45884.31863425926</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>44095</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>45049</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>44487.60532407407</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         <v>45323</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>45841.65936342593</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34085,7 +34085,7 @@
         <v>44418.40890046296</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34142,7 +34142,7 @@
         <v>45691.38957175926</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>45524.50288194444</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34256,7 +34256,7 @@
         <v>44690.6797337963</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34313,7 +34313,7 @@
         <v>44524</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45415</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>45068.41424768518</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34489,7 +34489,7 @@
         <v>45755.52962962963</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45111.65074074074</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34603,7 +34603,7 @@
         <v>45772.39434027778</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34660,7 +34660,7 @@
         <v>45049.61376157407</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>45727.45439814815</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34774,7 +34774,7 @@
         <v>45841.36670138889</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34831,7 +34831,7 @@
         <v>45637.58159722222</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34888,7 +34888,7 @@
         <v>45084</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34945,7 +34945,7 @@
         <v>44424</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>45466.85056712963</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35059,7 +35059,7 @@
         <v>45327.39550925926</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>45117</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>44488</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>45296</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>45099.49768518518</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35349,7 +35349,7 @@
         <v>45621</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35406,7 +35406,7 @@
         <v>45846</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35463,7 +35463,7 @@
         <v>45888.33114583333</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35520,7 +35520,7 @@
         <v>45743</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35577,7 +35577,7 @@
         <v>44235</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35634,7 +35634,7 @@
         <v>44593.62643518519</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         <v>44816.64091435185</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35748,7 +35748,7 @@
         <v>44608</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35805,7 +35805,7 @@
         <v>45349.85878472222</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35862,7 +35862,7 @@
         <v>45887.58094907407</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35919,7 +35919,7 @@
         <v>44993.56126157408</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44424</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>45107.60460648148</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36090,7 +36090,7 @@
         <v>44143</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36152,7 +36152,7 @@
         <v>45887.57563657407</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36209,7 +36209,7 @@
         <v>45845</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>45845.41</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36323,7 +36323,7 @@
         <v>44210</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36380,7 +36380,7 @@
         <v>45727.64369212963</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>44236.88402777778</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36494,7 +36494,7 @@
         <v>45887.56543981482</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36551,7 +36551,7 @@
         <v>45887.5702662037</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>44530.53258101852</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>44586</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>45740.51246527778</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>44759.39475694444</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36836,7 +36836,7 @@
         <v>44278</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36893,7 +36893,7 @@
         <v>45317.44828703703</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36950,7 +36950,7 @@
         <v>44416</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37007,7 +37007,7 @@
         <v>44447</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37064,7 +37064,7 @@
         <v>44589.42831018518</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>45104</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37178,7 +37178,7 @@
         <v>44405.3347337963</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>45211.67291666667</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>45211</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37349,7 +37349,7 @@
         <v>44159</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>45772.39609953704</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37463,7 +37463,7 @@
         <v>45775.59498842592</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>45524.58461805555</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>45849.46575231481</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37634,7 +37634,7 @@
         <v>45716.39373842593</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>44507</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37748,7 +37748,7 @@
         <v>45852.5841087963</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37805,7 +37805,7 @@
         <v>45818</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37862,7 +37862,7 @@
         <v>44893.78201388889</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37919,7 +37919,7 @@
         <v>44938.51150462963</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37976,7 +37976,7 @@
         <v>44979.50945601852</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38033,7 +38033,7 @@
         <v>45852.58133101852</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38090,7 +38090,7 @@
         <v>45851.91112268518</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38147,7 +38147,7 @@
         <v>45851.91469907408</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38204,7 +38204,7 @@
         <v>45852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38261,7 +38261,7 @@
         <v>45606.57038194445</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38318,7 +38318,7 @@
         <v>45370.74839120371</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38375,7 +38375,7 @@
         <v>45091.60043981481</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38432,7 +38432,7 @@
         <v>45149.35745370371</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>45897.39096064815</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38546,7 +38546,7 @@
         <v>45191.37449074074</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38603,7 +38603,7 @@
         <v>45856.47141203703</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38660,7 +38660,7 @@
         <v>45897.60010416667</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38717,7 +38717,7 @@
         <v>44239</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38774,7 +38774,7 @@
         <v>45155</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38831,7 +38831,7 @@
         <v>45897.63128472222</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38888,7 +38888,7 @@
         <v>45855.72674768518</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38945,7 +38945,7 @@
         <v>45251.67181712963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>44930.5281712963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39059,7 +39059,7 @@
         <v>45181.58443287037</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>44728.36835648148</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>45425.51765046296</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45036.45335648148</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39287,7 +39287,7 @@
         <v>44834.45706018519</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>45902.4652199074</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>45857</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>45902.47142361111</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>45901.39177083333</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39572,7 +39572,7 @@
         <v>45051</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39629,7 +39629,7 @@
         <v>45051.4380787037</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>45590.56064814814</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>44808.80826388889</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39800,7 +39800,7 @@
         <v>45861.33920138889</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39857,7 +39857,7 @@
         <v>44126.66101851852</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45904.42120370371</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39971,7 +39971,7 @@
         <v>44944</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40028,7 +40028,7 @@
         <v>45048</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40085,7 +40085,7 @@
         <v>44487</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40147,7 +40147,7 @@
         <v>45514.3787037037</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>45514.3809375</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40261,7 +40261,7 @@
         <v>45514.38158564815</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40318,7 +40318,7 @@
         <v>45905.41212962963</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40375,7 +40375,7 @@
         <v>45750.91766203703</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40432,7 +40432,7 @@
         <v>45863</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>45076.58376157407</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40546,7 +40546,7 @@
         <v>45392.57063657408</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40603,7 +40603,7 @@
         <v>45790.40994212963</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40660,7 +40660,7 @@
         <v>45217</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40717,7 +40717,7 @@
         <v>45688</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40774,7 +40774,7 @@
         <v>44455</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45909.39206018519</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>45740.50475694444</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40950,7 +40950,7 @@
         <v>45117</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>45867.57765046296</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>45180</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>45668.41509259259</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41178,7 +41178,7 @@
         <v>45714</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41235,7 +41235,7 @@
         <v>44239</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41292,7 +41292,7 @@
         <v>44145</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>45909.83339120371</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41406,7 +41406,7 @@
         <v>45909.37060185185</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>44207.35459490741</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41520,7 +41520,7 @@
         <v>45757.64254629629</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41577,7 +41577,7 @@
         <v>45349.81209490741</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41634,7 +41634,7 @@
         <v>45349.86459490741</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41691,7 +41691,7 @@
         <v>45641.74149305555</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41748,7 +41748,7 @@
         <v>45908</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41805,7 +41805,7 @@
         <v>45908</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41862,7 +41862,7 @@
         <v>44791.33793981482</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41919,7 +41919,7 @@
         <v>45310.58832175926</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41976,7 +41976,7 @@
         <v>44911</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42033,7 +42033,7 @@
         <v>45728</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42090,7 +42090,7 @@
         <v>45394.41221064814</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42147,7 +42147,7 @@
         <v>44900</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42204,7 +42204,7 @@
         <v>45189.35297453704</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         <v>45113</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42318,7 +42318,7 @@
         <v>45606.56679398148</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42375,7 +42375,7 @@
         <v>45007.52546296296</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42432,7 +42432,7 @@
         <v>45636.63569444444</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42489,7 +42489,7 @@
         <v>45392.57234953704</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42546,7 +42546,7 @@
         <v>45392.58719907407</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42603,7 +42603,7 @@
         <v>45164.64133101852</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>45211</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42717,7 +42717,7 @@
         <v>45126.36510416667</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>44698.34013888889</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42831,7 +42831,7 @@
         <v>45317.44657407407</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42888,7 +42888,7 @@
         <v>45373.48118055556</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42945,7 +42945,7 @@
         <v>45204</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43007,7 +43007,7 @@
         <v>45335.67450231482</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43064,7 +43064,7 @@
         <v>44228</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43121,7 +43121,7 @@
         <v>45369.42106481481</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43178,7 +43178,7 @@
         <v>45273.62960648148</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43240,7 +43240,7 @@
         <v>45204</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43302,7 +43302,7 @@
         <v>45595.51280092593</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>45433.48228009259</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43416,7 +43416,7 @@
         <v>45579.47649305555</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43473,7 +43473,7 @@
         <v>45716.34835648148</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45237.5672337963</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>44531.67679398148</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>44504.38146990741</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>45103.68170138889</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43758,7 +43758,7 @@
         <v>45474.4828587963</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43815,7 +43815,7 @@
         <v>45341.38545138889</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43872,7 +43872,7 @@
         <v>45665.4533912037</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43929,7 +43929,7 @@
         <v>45126.47646990741</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43986,7 +43986,7 @@
         <v>45202.46894675926</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44043,7 +44043,7 @@
         <v>45740.36450231481</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44100,7 +44100,7 @@
         <v>45700</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44157,7 +44157,7 @@
         <v>45281</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44214,7 +44214,7 @@
         <v>44449</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44271,7 +44271,7 @@
         <v>45155</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44328,7 +44328,7 @@
         <v>44897.65846064815</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44385,7 +44385,7 @@
         <v>45692.20631944444</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44442,7 +44442,7 @@
         <v>45716.35474537037</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44499,7 +44499,7 @@
         <v>44519</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>

--- a/Översikt EMMABODA.xlsx
+++ b/Översikt EMMABODA.xlsx
@@ -567,7 +567,7 @@
         <v>45377.5588425926</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         <v>45369</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>44314</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>45818</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>44811</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>44238</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44445</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>45161.33116898148</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>44570.72098379629</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>44762</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>44495</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>44120</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>44984.36140046296</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>45229.67172453704</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>44966.54540509259</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>44488</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45335</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45068.42262731482</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>44405.32738425926</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>44140</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>44089</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>44120.38783564815</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>44459.43425925926</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>44105</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>44379.56671296297</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>44530.4546875</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>44441.48626157407</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>44488</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44496.52702546296</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>44120.39879629629</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>44405.31638888889</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>44405.31894675926</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>44405</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>44764.45645833333</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>44496.5110300926</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>44530.4562037037</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>44405.32319444444</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>44228</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44454.86018518519</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>44117.6835300926</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>44264.36884259259</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>44251</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>44454</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>44529</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>44490</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>44110</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44601.34255787037</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>44431</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>44211</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>44600</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>44097</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>44280.65521990741</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>44251</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>44507</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>44507.56921296296</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>44507</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>44507</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>44297</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>44416</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>44416</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>44442</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>44240</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>44383.5654050926</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>44238</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>44728.83878472223</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>44211</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>44599.69461805555</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>44691</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>44628.35012731481</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>44326.44194444444</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>44504.38268518518</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>44387</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>44379</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>44383.6131712963</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>44515.44268518518</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>44851.40596064815</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>44860.88715277778</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         <v>44239</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>44118</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>44240.59631944444</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>44648.3578587963</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>44462.69965277778</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>44523</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>44278</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>44628</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>44788.65715277778</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>44347.43119212963</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>44382.6675925926</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>44416</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>44361.39021990741</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>44347.44501157408</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>44405</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>44627.34532407407</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>44392.4420949074</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>44109</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44112</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>44462</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>44240.57777777778</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>44148</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>44498</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44768.83986111111</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>44120</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>44851.49548611111</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>44529.29797453704</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>44249</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>44172</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>44277</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>44320</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>44208</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44208</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>44385</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>44347.43444444444</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>44813</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>44771</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>44202</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>44809.43158564815</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>44202</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>44412</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>44587.42887731481</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         <v>44433</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>44251</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         <v>44496</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>44466.39774305555</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>44507</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>44507</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>44487</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44405</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
         <v>44405</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>44383.61637731481</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>44147</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>44652</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>44416</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>44628.36534722222</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>44600</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>44421</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>44120</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>44600.45505787037</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>44501</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44110</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>44841.3953125</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>44256</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>44116.37994212963</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>44293</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>44148</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>44148</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>44852.48653935185</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>44295</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>44839.33949074074</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>44382.66943287037</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>44180</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>44722.49396990741</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>44532.70575231482</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>44120.39627314815</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>44847.55930555556</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>44148</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>44655.9318287037</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44743.42285879629</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>44615</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>44385</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>44412</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>44622.48368055555</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>44470.31766203704</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>44593.62412037037</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>44652</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>44699.83193287037</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>44162.37409722222</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>44524.72388888889</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>44488</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>44712.48467592592</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>44820</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>44706</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>44223</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>44383.559375</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>44383.61515046296</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>44454</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44302.5521875</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>44530</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44452.30709490741</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>44210.32178240741</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>45190</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>44284.40975694444</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>44238</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>44302.54723379629</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>44788.66310185185</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>44739.37986111111</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>44743.38194444445</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>45048.43734953704</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>45211</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>45719</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>45348.45074074074</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>45069</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>45069</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>45397.44292824074</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>45187.44503472222</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>45219</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>45719</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>45335</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>45078.59818287037</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>45204</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>45411.45418981482</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>44315</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>44771.43327546296</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>45440</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>45422.39476851852</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>45539.28254629629</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>45561</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>45126.47756944445</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>44959</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>44236.8744212963</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
         <v>44977.37475694445</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>45327.39255787037</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         <v>44382</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>45229.67283564815</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>45385.48972222222</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>45574.45165509259</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13470,7 +13470,7 @@
         <v>45126.38699074074</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>44979.50762731482</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>44728.83686342592</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>45093.61918981482</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>45296</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>45551</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         <v>45771</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>45523.52064814815</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>44203.61291666667</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>45215</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>44949.42457175926</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>45684.66949074074</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>45624.64013888889</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>44852.57822916667</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14268,7 +14268,7 @@
         <v>45534.66148148148</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>45121</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         <v>45341.37961805556</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>45777.37217592593</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>45777.3700462963</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>45484.49533564815</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>45777.51607638889</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
         <v>45351.58540509259</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
         <v>44953</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>45323.40695601852</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>44953</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>45779.45815972222</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>45779.46054398148</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>44572</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>45531.38554398148</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>45782.455</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>45600.65333333334</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
         <v>44589.43354166667</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>44223</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>44593.76921296296</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>45376.6791087963</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15465,7 +15465,7 @@
         <v>45769.35443287037</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>45107</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>45126.31585648148</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>45317.45069444444</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>45003.90380787037</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>45126.47204861111</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>44984.39417824074</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>45019.67677083334</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15921,7 +15921,7 @@
         <v>45415.60552083333</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>45638</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>44980</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>45610.70957175926</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>44271</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>45582</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>45565.4407175926</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>45445.3777662037</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>45461.49600694444</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>44840</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>45548</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>44895</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>45475.46671296296</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>44861</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>45132</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>44326.32891203704</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>44326.34681712963</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>44600.50372685185</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>45609.51984953704</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>45688</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>45037.64929398148</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>45484.35097222222</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>44347.43795138889</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>44110</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         <v>45386.35418981482</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>45400.91444444445</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17408,7 +17408,7 @@
         <v>44982.67675925926</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>44907.44033564815</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>45775.59086805556</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>44453</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>45474.61877314815</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>45566.63414351852</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>45789.54855324074</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         <v>45481.92570601852</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>44993</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>45400</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>45433</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>44167</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>44551</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>44340</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>45146.35854166667</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18268,7 +18268,7 @@
         <v>44431.41373842592</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>45161.329375</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>45323.75855324074</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>44088</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>45273.62567129629</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>44600.45703703703</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>44494</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>45455.38807870371</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>45559</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>45477.50987268519</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>45514.38017361111</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>44725</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>44951</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>45743</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45161</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>45795.67989583333</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>44519</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>45126</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>45126</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>45191.56679398148</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>45126</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>44530.5225462963</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>45205.49876157408</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>45167.65172453703</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>45681.58681712963</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>45797.45761574074</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>44400.37826388889</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19832,7 +19832,7 @@
         <v>44404</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>45741.70216435185</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>45189.50841435185</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20003,7 +20003,7 @@
         <v>45189.50895833333</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>45632</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>45797.44099537037</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>45800.58695601852</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         <v>44550.40824074074</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         <v>44600.45854166667</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>45800.5805787037</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>45099</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>45644.45738425926</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>45070.62878472222</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>45537</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>44896.4815625</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>45078.5972337963</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>45078.59965277778</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>45084.66810185185</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>44977</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>44900.36804398148</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>45072</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21039,7 +21039,7 @@
         <v>45622.56673611111</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         <v>45537</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>45159.4650925926</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         <v>45573.3758912037</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
         <v>45799.55665509259</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>45665.45535879629</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45562.50462962963</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>44299</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>45225.62575231482</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>45803.56060185185</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>45327.37474537037</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>45063</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>45475.36099537037</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21785,7 +21785,7 @@
         <v>45804.56436342592</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>45804.35590277778</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>44958</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21956,7 +21956,7 @@
         <v>44783.34944444444</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         <v>45091</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>44652</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>44665.90422453704</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>44893.57989583333</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>45230</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>45587.54915509259</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22355,7 +22355,7 @@
         <v>44683</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22412,7 +22412,7 @@
         <v>44376.82413194444</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22469,7 +22469,7 @@
         <v>45232</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>45554</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>45349.64855324074</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>44995</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22702,7 +22702,7 @@
         <v>45155</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>45182.57702546296</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>44897.66574074074</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>44949</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>45392.5746412037</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>44699.83489583333</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>45349.90940972222</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45007.53736111111</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>45400.68645833333</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>45148.51032407407</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23272,7 +23272,7 @@
         <v>44580.64971064815</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>45022.634375</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23386,7 +23386,7 @@
         <v>45022.64363425926</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>45531.50122685185</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23500,7 +23500,7 @@
         <v>45126</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23557,7 +23557,7 @@
         <v>45434.59488425926</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>44839</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23671,7 +23671,7 @@
         <v>44955</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>45813.45756944444</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23785,7 +23785,7 @@
         <v>44619</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>45818</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>45636.63883101852</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>45098.91159722222</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
         <v>45211</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24070,7 +24070,7 @@
         <v>45818</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>45706.44140046297</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>45408</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24241,7 +24241,7 @@
         <v>44445</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>45394</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>45818</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>45691.394375</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>45040</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>45819.69038194444</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>44728.36712962963</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>45554</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>45166</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45166</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>45252.41863425926</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>45188</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>45188</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>45400.62210648148</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>45392.58935185185</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>44995.57965277778</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>45825.73362268518</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>45826.36164351852</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>45107.47519675926</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44973.864375</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>45826.73186342593</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>45826.35939814815</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>45826.3639699074</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>45826.36921296296</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25629,7 +25629,7 @@
         <v>44673.38012731481</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25686,7 +25686,7 @@
         <v>44273</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25743,7 +25743,7 @@
         <v>45825.44528935185</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>44594</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>45826.35645833334</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25914,7 +25914,7 @@
         <v>45164.64883101852</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>44749.78425925926</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26028,7 +26028,7 @@
         <v>44524</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>45825.4341087963</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>44726</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>45707</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>44802.69710648148</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>44978.31736111111</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>45707</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>45763</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>44953</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
         <v>45401.43559027778</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         <v>44690</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26655,7 +26655,7 @@
         <v>45615</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         <v>45021.50722222222</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>45021.50942129629</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>45258.50520833334</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26883,7 +26883,7 @@
         <v>45258</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26940,7 +26940,7 @@
         <v>45736.56527777778</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -26997,7 +26997,7 @@
         <v>45832.38621527778</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>45735.47873842593</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>45048.435</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>45832.7072800926</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>45238</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>44978.32152777778</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>45832.40292824074</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>45769.60783564814</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27453,7 +27453,7 @@
         <v>45182</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>45475.36554398148</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>44222</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>45716.5465625</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>44748.54626157408</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>44384</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>45062.65315972222</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>45757.63991898148</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>45191.58287037037</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>44799.28053240741</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>45095</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>44777</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>44960</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>45362.96539351852</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>45009.46947916667</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>45009</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>45422.47181712963</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28427,7 +28427,7 @@
         <v>45559.60966435185</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>45084</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28541,7 +28541,7 @@
         <v>45355.42155092592</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>44700.61766203704</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28655,7 +28655,7 @@
         <v>45230.63987268518</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28712,7 +28712,7 @@
         <v>44827</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28769,7 +28769,7 @@
         <v>45301</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>45727.45094907407</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>45309.61168981482</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>45126.475625</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>44965.4890162037</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>45099.4612037037</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>45835.51372685185</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>45307.37699074074</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>45629.44709490741</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>44852.5103125</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29344,7 +29344,7 @@
         <v>45258</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29401,7 +29401,7 @@
         <v>45574.38966435185</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29458,7 +29458,7 @@
         <v>45009.36045138889</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>45009.40710648148</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29572,7 +29572,7 @@
         <v>45107</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29629,7 +29629,7 @@
         <v>45716.34990740741</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
         <v>45190</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>44922.58392361111</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45310.58383101852</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>44743.42150462963</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>45477.69497685185</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>45092</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30033,7 +30033,7 @@
         <v>45092</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>44851.49424768519</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>45229.52315972222</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>45881.41793981481</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>45515.76115740741</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>45089.38663194444</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>45673.67064814815</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>44473</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>44235</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>45079</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30603,7 +30603,7 @@
         <v>45645.58637731482</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30660,7 +30660,7 @@
         <v>45614.54209490741</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>45113.63261574074</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>45596.75166666666</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>44893.48324074074</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>45102</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30945,7 +30945,7 @@
         <v>45615</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
         <v>45102</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31059,7 +31059,7 @@
         <v>44729.41611111111</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31116,7 +31116,7 @@
         <v>45159.46884259259</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31173,7 +31173,7 @@
         <v>44769.56326388889</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31230,7 +31230,7 @@
         <v>45722</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31287,7 +31287,7 @@
         <v>45551.56715277778</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>45187.47203703703</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>45881.37207175926</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>44781</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>45148.50620370371</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31577,7 +31577,7 @@
         <v>45401.4321412037</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>44851.4281712963</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>45726.59443287037</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>44984.56648148148</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>44761.65730324074</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>45196</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31919,7 +31919,7 @@
         <v>45113.64193287037</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -31976,7 +31976,7 @@
         <v>45392.58570601852</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>45742.80981481481</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>44683.43862268519</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>44349.62881944444</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>45722</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>44897.54603009259</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>45445.39274305556</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>45841.44533564815</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>45841.44762731482</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>45021.67435185185</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>45067</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>45637.57834490741</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>44278.36359953704</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32717,7 +32717,7 @@
         <v>45323.39561342593</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32774,7 +32774,7 @@
         <v>45749.44238425926</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32831,7 +32831,7 @@
         <v>45776</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32888,7 +32888,7 @@
         <v>45776</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>45805</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33002,7 +33002,7 @@
         <v>45805</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33059,7 +33059,7 @@
         <v>45716</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33116,7 +33116,7 @@
         <v>45716</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33173,7 +33173,7 @@
         <v>45028</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>45772.39268518519</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33287,7 +33287,7 @@
         <v>45200.41958333334</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>45740.50775462963</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>45196.6208449074</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>44518</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>45222</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>44433</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>45211</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>44879</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>45884.31863425926</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>44095</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>45049</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>44487.60532407407</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         <v>45323</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>45841.65936342593</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34085,7 +34085,7 @@
         <v>44418.40890046296</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34142,7 +34142,7 @@
         <v>45691.38957175926</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>45524.50288194444</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34256,7 +34256,7 @@
         <v>44690.6797337963</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34313,7 +34313,7 @@
         <v>44524</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45415</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>45068.41424768518</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34489,7 +34489,7 @@
         <v>45755.52962962963</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45111.65074074074</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34603,7 +34603,7 @@
         <v>45772.39434027778</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34660,7 +34660,7 @@
         <v>45049.61376157407</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>45727.45439814815</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34774,7 +34774,7 @@
         <v>45841.36670138889</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34831,7 +34831,7 @@
         <v>45637.58159722222</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34888,7 +34888,7 @@
         <v>45084</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34945,7 +34945,7 @@
         <v>44424</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>45466.85056712963</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35059,7 +35059,7 @@
         <v>45327.39550925926</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>45117</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>44488</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>45296</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>45099.49768518518</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35349,7 +35349,7 @@
         <v>45621</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35406,7 +35406,7 @@
         <v>45846</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35463,7 +35463,7 @@
         <v>45888.33114583333</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35520,7 +35520,7 @@
         <v>45743</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35577,7 +35577,7 @@
         <v>44235</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35634,7 +35634,7 @@
         <v>44593.62643518519</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         <v>44816.64091435185</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35748,7 +35748,7 @@
         <v>44608</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35805,7 +35805,7 @@
         <v>45349.85878472222</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35862,7 +35862,7 @@
         <v>45887.58094907407</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35919,7 +35919,7 @@
         <v>44993.56126157408</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>44424</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>45107.60460648148</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36090,7 +36090,7 @@
         <v>44143</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36152,7 +36152,7 @@
         <v>45887.57563657407</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36209,7 +36209,7 @@
         <v>45845</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>45845.41</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36323,7 +36323,7 @@
         <v>44210</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36380,7 +36380,7 @@
         <v>45727.64369212963</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>44236.88402777778</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36494,7 +36494,7 @@
         <v>45887.56543981482</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36551,7 +36551,7 @@
         <v>45887.5702662037</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>44530.53258101852</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>44586</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>45740.51246527778</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>44759.39475694444</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36836,7 +36836,7 @@
         <v>44278</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36893,7 +36893,7 @@
         <v>45317.44828703703</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36950,7 +36950,7 @@
         <v>44416</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37007,7 +37007,7 @@
         <v>44447</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37064,7 +37064,7 @@
         <v>44589.42831018518</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>45104</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37178,7 +37178,7 @@
         <v>44405.3347337963</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>45211.67291666667</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>45211</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37349,7 +37349,7 @@
         <v>44159</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>45772.39609953704</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37463,7 +37463,7 @@
         <v>45775.59498842592</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>45524.58461805555</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>45849.46575231481</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37634,7 +37634,7 @@
         <v>45716.39373842593</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>44507</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37748,7 +37748,7 @@
         <v>45852.5841087963</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37805,7 +37805,7 @@
         <v>45818</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37862,7 +37862,7 @@
         <v>44893.78201388889</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37919,7 +37919,7 @@
         <v>44938.51150462963</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -37976,7 +37976,7 @@
         <v>44979.50945601852</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38033,7 +38033,7 @@
         <v>45852.58133101852</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38090,7 +38090,7 @@
         <v>45851.91112268518</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38147,7 +38147,7 @@
         <v>45851.91469907408</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38204,7 +38204,7 @@
         <v>45852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38261,7 +38261,7 @@
         <v>45606.57038194445</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38318,7 +38318,7 @@
         <v>45370.74839120371</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38375,7 +38375,7 @@
         <v>45091.60043981481</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38432,7 +38432,7 @@
         <v>45149.35745370371</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>45897.39096064815</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38546,7 +38546,7 @@
         <v>45191.37449074074</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38603,7 +38603,7 @@
         <v>45856.47141203703</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38660,7 +38660,7 @@
         <v>45897.60010416667</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38717,7 +38717,7 @@
         <v>44239</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38774,7 +38774,7 @@
         <v>45155</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38831,7 +38831,7 @@
         <v>45897.63128472222</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38888,7 +38888,7 @@
         <v>45855.72674768518</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38945,7 +38945,7 @@
         <v>45251.67181712963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>44930.5281712963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39059,7 +39059,7 @@
         <v>45181.58443287037</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>44728.36835648148</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>45425.51765046296</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45036.45335648148</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39287,7 +39287,7 @@
         <v>44834.45706018519</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>45902.4652199074</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>45857</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>45902.47142361111</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>45901.39177083333</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39572,7 +39572,7 @@
         <v>45051</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39629,7 +39629,7 @@
         <v>45051.4380787037</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>45590.56064814814</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>44808.80826388889</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39800,7 +39800,7 @@
         <v>45861.33920138889</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39857,7 +39857,7 @@
         <v>44126.66101851852</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45904.42120370371</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -39971,7 +39971,7 @@
         <v>44944</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40028,7 +40028,7 @@
         <v>45048</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40085,7 +40085,7 @@
         <v>44487</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40147,7 +40147,7 @@
         <v>45514.3787037037</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>45514.3809375</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40261,7 +40261,7 @@
         <v>45514.38158564815</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40318,7 +40318,7 @@
         <v>45905.41212962963</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40375,7 +40375,7 @@
         <v>45750.91766203703</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40432,7 +40432,7 @@
         <v>45863</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>45076.58376157407</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40546,7 +40546,7 @@
         <v>45392.57063657408</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40603,7 +40603,7 @@
         <v>45790.40994212963</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40660,7 +40660,7 @@
         <v>45217</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40717,7 +40717,7 @@
         <v>45688</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40774,7 +40774,7 @@
         <v>44455</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45909.39206018519</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>45740.50475694444</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40950,7 +40950,7 @@
         <v>45117</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>45867.57765046296</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>45180</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>45668.41509259259</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41178,7 +41178,7 @@
         <v>45714</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41235,7 +41235,7 @@
         <v>44239</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41292,7 +41292,7 @@
         <v>44145</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>45909.83339120371</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41406,7 +41406,7 @@
         <v>45909.37060185185</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>44207.35459490741</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41520,7 +41520,7 @@
         <v>45757.64254629629</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41577,7 +41577,7 @@
         <v>45349.81209490741</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41634,7 +41634,7 @@
         <v>45349.86459490741</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41691,7 +41691,7 @@
         <v>45641.74149305555</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41748,7 +41748,7 @@
         <v>45908</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41805,7 +41805,7 @@
         <v>45908</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41862,7 +41862,7 @@
         <v>44791.33793981482</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41919,7 +41919,7 @@
         <v>45310.58832175926</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -41976,7 +41976,7 @@
         <v>44911</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42033,7 +42033,7 @@
         <v>45728</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42090,7 +42090,7 @@
         <v>45394.41221064814</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42147,7 +42147,7 @@
         <v>44900</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42204,7 +42204,7 @@
         <v>45189.35297453704</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         <v>45113</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42318,7 +42318,7 @@
         <v>45606.56679398148</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42375,7 +42375,7 @@
         <v>45007.52546296296</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42432,7 +42432,7 @@
         <v>45636.63569444444</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42489,7 +42489,7 @@
         <v>45392.57234953704</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42546,7 +42546,7 @@
         <v>45392.58719907407</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42603,7 +42603,7 @@
         <v>45164.64133101852</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>45211</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42717,7 +42717,7 @@
         <v>45126.36510416667</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>44698.34013888889</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42831,7 +42831,7 @@
         <v>45317.44657407407</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42888,7 +42888,7 @@
         <v>45373.48118055556</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42945,7 +42945,7 @@
         <v>45204</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43007,7 +43007,7 @@
         <v>45335.67450231482</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43064,7 +43064,7 @@
         <v>44228</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43121,7 +43121,7 @@
         <v>45369.42106481481</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43178,7 +43178,7 @@
         <v>45273.62960648148</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43240,7 +43240,7 @@
         <v>45204</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43302,7 +43302,7 @@
         <v>45595.51280092593</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43359,7 +43359,7 @@
         <v>45433.48228009259</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43416,7 +43416,7 @@
         <v>45579.47649305555</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43473,7 +43473,7 @@
         <v>45716.34835648148</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45237.5672337963</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>44531.67679398148</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>44504.38146990741</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>45103.68170138889</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43758,7 +43758,7 @@
         <v>45474.4828587963</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43815,7 +43815,7 @@
         <v>45341.38545138889</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43872,7 +43872,7 @@
         <v>45665.4533912037</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43929,7 +43929,7 @@
         <v>45126.47646990741</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -43986,7 +43986,7 @@
         <v>45202.46894675926</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44043,7 +44043,7 @@
         <v>45740.36450231481</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44100,7 +44100,7 @@
         <v>45700</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44157,7 +44157,7 @@
         <v>45281</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44214,7 +44214,7 @@
         <v>44449</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44271,7 +44271,7 @@
         <v>45155</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44328,7 +44328,7 @@
         <v>44897.65846064815</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44385,7 +44385,7 @@
         <v>45692.20631944444</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44442,7 +44442,7 @@
         <v>45716.35474537037</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44499,7 +44499,7 @@
         <v>44519</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>

--- a/Översikt EMMABODA.xlsx
+++ b/Översikt EMMABODA.xlsx
@@ -567,7 +567,7 @@
         <v>44314</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         <v>45369</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>44811</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         <v>45818</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>45377.5588425926</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>44238</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44445</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>45068.42262731482</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>44966.54540509259</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>44120</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>44570.72098379629</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>44762</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>44984.36140046296</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>45229.67172453704</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>44495</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>45104</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>45335</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>45867.57765046296</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>45161.33116898148</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>44488</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44405.32738425926</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>44140</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>44120.38783564815</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>44459.43425925926</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>44105</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>44379.56671296297</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44530.4546875</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>44441.48626157407</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>44496.52702546296</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>44488</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>44405.31638888889</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>44530.4562037037</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>44120.39879629629</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>44405.31894675926</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>44405</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>44764.45645833333</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>44496.5110300926</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>44405.32319444444</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>44228</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>44454.86018518519</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>44117.6835300926</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>44264.36884259259</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>44454</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>44529</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>44251</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>44490</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>44110</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>44601.34255787037</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>44211</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>44431</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>44600</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>44383.5654050926</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>44251</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>44280.65521990741</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>44507</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44507.56921296296</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>44507</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>44507</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>44297</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>44442</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>44238</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>44416</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44416</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>44240</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>44599.69461805555</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>44211</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>44691</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>44728.83878472223</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>44628.35012731481</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>44326.44194444444</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>44504.38268518518</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>44379</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>44387</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>44383.6131712963</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>44515.44268518518</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>44851.40596064815</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>44860.88715277778</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>44239</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>44118</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44240.59631944444</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>44462.69965277778</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>44523</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>44648.3578587963</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>44278</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>44628</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>44788.65715277778</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>44347.43119212963</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44416</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>44382.6675925926</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>44361.39021990741</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>44347.44501157408</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44405</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>44627.34532407407</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>44392.4420949074</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>44109</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>44112</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>44462</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>44240.57777777778</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>44148</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>44120</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>44498</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>44768.83986111111</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>44851.49548611111</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>44529.29797453704</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>44249</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>44172</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>44277</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>44320</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>44208</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>44208</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
         <v>44385</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>44347.43444444444</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>44813</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>44809.43158564815</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>44771</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>44202</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>44202</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>44412</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>44587.42887731481</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>44433</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>44251</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>44496</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>44466.39774305555</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>44487</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>44507</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>44507</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>44405</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>44405</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>44383.61637731481</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>44147</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>44416</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44628.36534722222</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>44600</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>44652</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>44421</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>44120</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>44501</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>44600.45505787037</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>44110</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>44116.37994212963</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>44841.3953125</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>44293</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44148</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>44148</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>44852.48653935185</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>44295</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>44847.55930555556</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>44148</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>44839.33949074074</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>44743.42285879629</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>44382.66943287037</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>44180</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44488</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>44722.49396990741</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>44532.70575231482</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>44120.39627314815</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>44223</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>44256</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>44452.30709490741</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>44210.32178240741</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>44238</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>44615</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>44385</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>44412</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>44470.31766203704</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>44622.48368055555</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>44593.62412037037</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>44652</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>44699.83193287037</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         <v>44524.72388888889</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         <v>44712.48467592592</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10993,7 +10993,7 @@
         <v>44162.37409722222</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11050,7 +11050,7 @@
         <v>44589.43354166667</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>44383.559375</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>44383.61515046296</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>44302.5521875</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>44110</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>44820</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>44706</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>44167</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>44551</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>44284.40975694444</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         <v>44302.54723379629</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>44340</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>44431.41373842592</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>44600.45703703703</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>44743.38194444445</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11915,7 +11915,7 @@
         <v>44725</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11972,7 +11972,7 @@
         <v>44600.45854166667</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>44382</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>44953</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
         <v>45089.38663194444</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12200,7 +12200,7 @@
         <v>45251.67181712963</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>45691.38957175926</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>45394</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>44955</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12428,7 +12428,7 @@
         <v>45048.435</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12485,7 +12485,7 @@
         <v>45749.44238425926</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>45411.45418981482</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>45351.58540509259</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>45534.66148148148</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>44487.60532407407</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>45590.56064814814</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>45215</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>45551</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>45777.51607638889</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>45727.45439814815</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>45040</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>45777.3700462963</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>45777.37217592593</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>45523.52064814815</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>44949.42457175926</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45684.66949074074</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>45624.64013888889</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>45484.49533564815</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>45191.37449074074</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>45126.31585648148</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>44897.54603009259</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>44235</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         <v>45779.45815972222</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>45779.46054398148</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13853,7 +13853,7 @@
         <v>45722</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>44384</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>45606.56679398148</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45392.58935185185</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>45722</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>45099</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>45782.455</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>45614.54209490741</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14314,7 +14314,7 @@
         <v>44455</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>44993.56126157408</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>45230</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>45022.634375</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>45022.64363425926</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>45574.45165509259</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>45187.47203703703</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>45637.58159722222</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>44977.37475694445</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>45107</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>45445.3777662037</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14946,7 +14946,7 @@
         <v>45317.45069444444</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>45159.46884259259</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>45219</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>45587.54915509259</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>45548</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>45415.60552083333</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>45638</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>45301</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>44652</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>45237.5672337963</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>44400.37826388889</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         <v>45565.4407175926</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>45386.35418981482</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>45692.20631944444</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15744,7 +15744,7 @@
         <v>45622.56673611111</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>45775.59086805556</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>45049</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15915,7 +15915,7 @@
         <v>44895</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>45093.61918981482</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>45789.54855324074</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>44453</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         <v>45481.92570601852</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16200,7 +16200,7 @@
         <v>44655.9318287037</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>45566.63414351852</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16314,7 +16314,7 @@
         <v>45582</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>45609.51984953704</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
         <v>45484.35097222222</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45230.63987268518</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>44965.4890162037</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>45688</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45610.70957175926</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>44743.42150462963</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>45400</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>44749.78425925926</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
         <v>44572</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16941,7 +16941,7 @@
         <v>45327.39550925926</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         <v>45392.58570601852</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>45019.67677083334</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>45327.37474537037</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>44973.864375</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         <v>45474.61877314815</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>45341.38545138889</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>44228</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>45078.59818287037</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45559</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>44519</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>45238</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44273</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17697,7 +17697,7 @@
         <v>45771</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>45182</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         <v>45433.48228009259</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         <v>45455.38807870371</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>45107.47519675926</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>45007.52546296296</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>45007.53736111111</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>45795.67989583333</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>45797.45761574074</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>45706.44140046297</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>45148.51032407407</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         <v>45084.66810185185</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>45559.60966435185</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>45741.70216435185</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>45309.61168981482</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         <v>45537</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18609,7 +18609,7 @@
         <v>44454</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18666,7 +18666,7 @@
         <v>45281</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>45211</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18780,7 +18780,7 @@
         <v>45021.67435185185</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>44530.5225462963</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>45189.50841435185</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18951,7 +18951,7 @@
         <v>44938.51150462963</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>45211</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>45211</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>44683.43862268519</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>44851.49424768519</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>45757.63991898148</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>44960</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>45797.44099537037</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19407,7 +19407,7 @@
         <v>45757.64254629629</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45665.4533912037</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>44530</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>45665.45535879629</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>44494</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>44978.31736111111</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>44978.32152777778</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19806,7 +19806,7 @@
         <v>45148.50620370371</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>44771.43327546296</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>44977</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
         <v>45537</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>45799.55665509259</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>45164.64883101852</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>45166</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         <v>45166</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20262,7 +20262,7 @@
         <v>44896.4815625</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44893.48324074074</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>44416</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>44405.3347337963</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>45475.36554398148</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>44739.37986111111</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>44518</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>45394.41221064814</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>45606.57038194445</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>44728.36712962963</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>45009.36045138889</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>45009.40710648148</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20946,7 +20946,7 @@
         <v>45009.46947916667</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>45009</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>44958</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21117,7 +21117,7 @@
         <v>45803.56060185185</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>44788.66310185185</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>45800.58695601852</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>44980</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>45078.5972337963</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>45078.59965277778</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>44911</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
         <v>45800.5805787037</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>45159.4650925926</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>44949</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21697,7 +21697,7 @@
         <v>45355.42155092592</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>45188</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>45422.39476851852</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>44145</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>45369.42106481481</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>44982.67675925926</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22044,7 +22044,7 @@
         <v>45804.56436342592</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22101,7 +22101,7 @@
         <v>44834.45706018519</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>45804.35590277778</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
         <v>45514.3787037037</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>45514.3809375</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>45514.38158564815</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>44447</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>44791.33793981482</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>45202.46894675926</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>44879</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22614,7 +22614,7 @@
         <v>44207.35459490741</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45397.44292824074</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         <v>44783.34944444444</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45349.86459490741</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>44487</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>44593.76921296296</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>45126</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>45126.36510416667</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23075,7 +23075,7 @@
         <v>45126.47646990741</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23132,7 +23132,7 @@
         <v>45539.28254629629</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23189,7 +23189,7 @@
         <v>45021.50942129629</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45155</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23303,7 +23303,7 @@
         <v>45813.45756944444</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23360,7 +23360,7 @@
         <v>44600.50372685185</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>45415</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23474,7 +23474,7 @@
         <v>45475.36099537037</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>45323</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>45740.50475694444</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>44953</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>45818</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>45362.96539351852</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>44424</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>44665.90422453704</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>45475.46671296296</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>45735.47873842593</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>45818</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>45155</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>45819.69038194444</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>45818</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>44347.43795138889</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>45401.43559027778</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24386,7 +24386,7 @@
         <v>45763</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>45037.64929398148</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24500,7 +24500,7 @@
         <v>44690</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>44700.61766203704</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24614,7 +24614,7 @@
         <v>45445.39274305556</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24671,7 +24671,7 @@
         <v>44690.6797337963</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>45079</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>45211.67291666667</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>45641.74149305555</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24899,7 +24899,7 @@
         <v>44593.62643518519</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>45743</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25013,7 +25013,7 @@
         <v>45296</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>44530.53258101852</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>44777</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>45644.45738425926</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>45181.58443287037</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>44504.38146990741</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>44222</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>44143</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>44223</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>45211</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45126</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>45126</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25702,7 +25702,7 @@
         <v>45636.63883101852</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>44799.28053240741</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25816,7 +25816,7 @@
         <v>45155</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25873,7 +25873,7 @@
         <v>45225.62575231482</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25930,7 +25930,7 @@
         <v>45164.64133101852</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -25987,7 +25987,7 @@
         <v>45063</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26049,7 +26049,7 @@
         <v>44424</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>44893.78201388889</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>45190</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>44993</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>45719</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>45719</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26391,7 +26391,7 @@
         <v>45349.64855324074</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>44852.5103125</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26505,7 +26505,7 @@
         <v>45190</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>45433</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26619,7 +26619,7 @@
         <v>45067</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         <v>45440</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>44953</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26795,7 +26795,7 @@
         <v>45107</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26852,7 +26852,7 @@
         <v>45531.38554398148</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>45579.47649305555</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>45126.475625</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>44861</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>44729.41611111111</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27137,7 +27137,7 @@
         <v>45772.39268518519</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27194,7 +27194,7 @@
         <v>45205.49876157408</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>44984.39417824074</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27308,7 +27308,7 @@
         <v>45474.4828587963</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>45084</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>45726.59443287037</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27479,7 +27479,7 @@
         <v>44404</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>44507</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>45126.47756944445</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
         <v>44473</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>45189.35297453704</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27764,7 +27764,7 @@
         <v>45048</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27821,7 +27821,7 @@
         <v>45191.56679398148</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27878,7 +27878,7 @@
         <v>44619</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>45574.38966435185</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -27992,7 +27992,7 @@
         <v>45434.59488425926</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45204</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28111,7 +28111,7 @@
         <v>45232</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>45036.45335648148</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>45323.75855324074</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>44907.44033564815</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28344,7 +28344,7 @@
         <v>45098.91159722222</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>45273.62960648148</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28463,7 +28463,7 @@
         <v>45392.5746412037</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>45211</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>45229.52315972222</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>45132</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>45084</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28748,7 +28748,7 @@
         <v>45740.50775462963</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>45341.37961805556</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>44995.57965277778</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28919,7 +28919,7 @@
         <v>44519</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>44299</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45003.90380787037</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>44315</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>45102</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45102</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>45477.50987268519</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29318,7 +29318,7 @@
         <v>44995</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29375,7 +29375,7 @@
         <v>44839</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29432,7 +29432,7 @@
         <v>45126</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29489,7 +29489,7 @@
         <v>45317.44828703703</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>45514.38017361111</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29603,7 +29603,7 @@
         <v>45196.6208449074</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>45825.44528935185</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29717,7 +29717,7 @@
         <v>45146.35854166667</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29774,7 +29774,7 @@
         <v>45825.4341087963</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         <v>44126.66101851852</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29888,7 +29888,7 @@
         <v>45825.73362268518</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29945,7 +29945,7 @@
         <v>44271</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>44959</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>45068.41424768518</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30121,7 +30121,7 @@
         <v>45707</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>44851.4281712963</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30235,7 +30235,7 @@
         <v>44608</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30292,7 +30292,7 @@
         <v>45095</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30349,7 +30349,7 @@
         <v>44979.50945601852</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30406,7 +30406,7 @@
         <v>45716.35474537037</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>45826.35645833334</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30520,7 +30520,7 @@
         <v>44580.64971064815</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30577,7 +30577,7 @@
         <v>45107.60460648148</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>45091</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>45373.48118055556</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>45826.36921296296</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>45716</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>45716</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>45161.329375</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>44984.56648148148</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>45252.41863425926</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>45826.73186342593</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44761.65730324074</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>45121</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>44802.69710648148</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31323,7 +31323,7 @@
         <v>45826.36164351852</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>45191.58287037037</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>45728</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>44326.32891203704</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>44326.34681712963</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>45422.47181712963</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>44979.50762731482</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31722,7 +31722,7 @@
         <v>45615</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>45826.35939814815</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>45826.3639699074</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31893,7 +31893,7 @@
         <v>45113.63261574074</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31950,7 +31950,7 @@
         <v>45113.64193287037</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>45477.69497685185</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>45167.65172453703</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>45637.57834490741</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>44808.80826388889</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>45524.50288194444</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>44210</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>45069</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>45069</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>45401.4321412037</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>45524.58461805555</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
         <v>45348.45074074074</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>44449</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>45189.50895833333</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>45772.39434027778</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32810,7 +32810,7 @@
         <v>45408</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>45832.40292824074</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>45832.38621527778</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>45049.61376157407</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>45645.58637731482</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33095,7 +33095,7 @@
         <v>45376.6791087963</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>44445</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33209,7 +33209,7 @@
         <v>45636.63569444444</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>44531.67679398148</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>44683</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>45629.44709490741</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>45832.7072800926</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>45051</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>45051.4380787037</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33608,7 +33608,7 @@
         <v>45835.51372685185</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>45736.56527777778</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>45461.49600694444</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>45349.90940972222</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33836,7 +33836,7 @@
         <v>45126.38699074074</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33893,7 +33893,7 @@
         <v>45126.47204861111</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33950,7 +33950,7 @@
         <v>45323.40695601852</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         <v>45632</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>44673.38012731481</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34121,7 +34121,7 @@
         <v>45596.75166666666</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34178,7 +34178,7 @@
         <v>44893.57989583333</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34235,7 +34235,7 @@
         <v>45841.36670138889</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34292,7 +34292,7 @@
         <v>44159</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34349,7 +34349,7 @@
         <v>45554</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>45776</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34468,7 +34468,7 @@
         <v>45776</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34525,7 +34525,7 @@
         <v>45805</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34582,7 +34582,7 @@
         <v>45805</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34639,7 +34639,7 @@
         <v>45707</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34696,7 +34696,7 @@
         <v>44524</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34753,7 +34753,7 @@
         <v>45091.60043981481</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>45841.65936342593</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>45841.44533564815</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>45841.44762731482</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>45845.41</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>45668.41509259259</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>44759.39475694444</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35152,7 +35152,7 @@
         <v>44349.62881944444</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>45887.58094907407</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35266,7 +35266,7 @@
         <v>44897.65846064815</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>45621</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>45113</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>45887.56543981482</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>45887.5702662037</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>44236.8744212963</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>45884.31863425926</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35665,7 +35665,7 @@
         <v>44235</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>44594</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35779,7 +35779,7 @@
         <v>45681.58681712963</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35836,7 +35836,7 @@
         <v>45335</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>45335.67450231482</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35950,7 +35950,7 @@
         <v>45200.41958333334</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36007,7 +36007,7 @@
         <v>45887.57563657407</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         <v>45755.52962962963</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36121,7 +36121,7 @@
         <v>45070.62878472222</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36178,7 +36178,7 @@
         <v>45727.64369212963</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>45845</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36292,7 +36292,7 @@
         <v>44236.88402777778</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>45323.39561342593</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>44852.57822916667</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>45888.33114583333</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>45222</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>44944</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36634,7 +36634,7 @@
         <v>45846</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>45072</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36748,7 +36748,7 @@
         <v>45149.35745370371</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>45370.74839120371</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36862,7 +36862,7 @@
         <v>45400.68645833333</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36919,7 +36919,7 @@
         <v>45111.65074074074</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -36976,7 +36976,7 @@
         <v>45310.58832175926</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45021.50722222222</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37090,7 +37090,7 @@
         <v>45849.46575231481</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         <v>44239</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>45852</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37261,7 +37261,7 @@
         <v>45204</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>45852.5841087963</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         <v>45062.65315972222</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37437,7 +37437,7 @@
         <v>44900</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37494,7 +37494,7 @@
         <v>45852.58133101852</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>45775.59498842592</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>45716.39373842593</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37665,7 +37665,7 @@
         <v>45851.91112268518</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>45851.91469907408</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37779,7 +37779,7 @@
         <v>44922.58392361111</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37836,7 +37836,7 @@
         <v>45818</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37893,7 +37893,7 @@
         <v>45772.39609953704</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37950,7 +37950,7 @@
         <v>44239</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38007,7 +38007,7 @@
         <v>44278</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38064,7 +38064,7 @@
         <v>45897.39096064815</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38121,7 +38121,7 @@
         <v>44781</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38178,7 +38178,7 @@
         <v>45897.60010416667</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38235,7 +38235,7 @@
         <v>45466.85056712963</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38292,7 +38292,7 @@
         <v>45855.72674768518</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38349,7 +38349,7 @@
         <v>44203.61291666667</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38406,7 +38406,7 @@
         <v>45897.63128472222</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>45857</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>45562.50462962963</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45103.68170138889</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45688</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>45856.47141203703</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38748,7 +38748,7 @@
         <v>45901.39177083333</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38805,7 +38805,7 @@
         <v>44589.42831018518</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>45716.34990740741</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>45327.39255787037</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -38976,7 +38976,7 @@
         <v>45902.4652199074</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39033,7 +39033,7 @@
         <v>44726</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39090,7 +39090,7 @@
         <v>45861.33920138889</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39147,7 +39147,7 @@
         <v>45742.80981481481</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39204,7 +39204,7 @@
         <v>45740.36450231481</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39261,7 +39261,7 @@
         <v>45217</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39318,7 +39318,7 @@
         <v>44524</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39375,7 +39375,7 @@
         <v>45425.51765046296</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39432,7 +39432,7 @@
         <v>44728.83686342592</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39489,7 +39489,7 @@
         <v>45902.47142361111</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39546,7 +39546,7 @@
         <v>45117</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>45182.57702546296</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39660,7 +39660,7 @@
         <v>44816.64091435185</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39717,7 +39717,7 @@
         <v>44951</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39774,7 +39774,7 @@
         <v>45905.41212962963</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39831,7 +39831,7 @@
         <v>45904.42120370371</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>45691.394375</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39945,7 +39945,7 @@
         <v>44840</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40007,7 +40007,7 @@
         <v>45863</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40064,7 +40064,7 @@
         <v>45595.51280092593</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40121,7 +40121,7 @@
         <v>45673.67064814815</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>45099.49768518518</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40235,7 +40235,7 @@
         <v>45909.39206018519</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40292,7 +40292,7 @@
         <v>45909.83339120371</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40349,7 +40349,7 @@
         <v>45204</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45561</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45909.37060185185</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>44897.66574074074</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45392.57234953704</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>45392.58719907407</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>45750.91766203703</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>44433</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45790.40994212963</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40872,7 +40872,7 @@
         <v>45258</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40929,7 +40929,7 @@
         <v>45273.62567129629</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -40991,7 +40991,7 @@
         <v>45349.85878472222</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41048,7 +41048,7 @@
         <v>44827</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41105,7 +41105,7 @@
         <v>45727.45094907407</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41162,7 +41162,7 @@
         <v>45700</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41219,7 +41219,7 @@
         <v>45349.81209490741</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41276,7 +41276,7 @@
         <v>45092</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41333,7 +41333,7 @@
         <v>45092</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41390,7 +41390,7 @@
         <v>45310.58383101852</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41447,7 +41447,7 @@
         <v>45296</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41504,7 +41504,7 @@
         <v>44376.82413194444</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41561,7 +41561,7 @@
         <v>44550.40824074074</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>45076.58376157407</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>45385.48972222222</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41732,7 +41732,7 @@
         <v>44278.36359953704</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41789,7 +41789,7 @@
         <v>45716.34835648148</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41846,7 +41846,7 @@
         <v>45740.51246527778</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41903,7 +41903,7 @@
         <v>45573.3758912037</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41960,7 +41960,7 @@
         <v>45515.76115740741</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42017,7 +42017,7 @@
         <v>45908</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42074,7 +42074,7 @@
         <v>45908</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42131,7 +42131,7 @@
         <v>45743</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>45915.56016203704</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42245,7 +42245,7 @@
         <v>45307.37699074074</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42302,7 +42302,7 @@
         <v>45317.44657407407</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
         <v>45187.44503472222</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42416,7 +42416,7 @@
         <v>44748.54626157408</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42473,7 +42473,7 @@
         <v>44728.36835648148</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42530,7 +42530,7 @@
         <v>45915.56546296296</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42587,7 +42587,7 @@
         <v>45258.50520833334</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42644,7 +42644,7 @@
         <v>45258</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>45600.65333333334</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42758,7 +42758,7 @@
         <v>44930.5281712963</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42815,7 +42815,7 @@
         <v>45400.62210648148</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42872,7 +42872,7 @@
         <v>44698.34013888889</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42929,7 +42929,7 @@
         <v>45915.55810185185</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -42986,7 +42986,7 @@
         <v>45028</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43043,7 +43043,7 @@
         <v>45554</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43105,7 +43105,7 @@
         <v>45915</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43162,7 +43162,7 @@
         <v>45551.56715277778</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43224,7 +43224,7 @@
         <v>45915</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>45392.57063657408</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43343,7 +43343,7 @@
         <v>44699.83489583333</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43400,7 +43400,7 @@
         <v>45531.50122685185</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>44900.36804398148</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>45400.91444444445</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43571,7 +43571,7 @@
         <v>45196</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43628,7 +43628,7 @@
         <v>44586</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43685,7 +43685,7 @@
         <v>45117</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>45229.67283564815</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>45615</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>45161</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43918,7 +43918,7 @@
         <v>45099.4612037037</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
         <v>45188</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44042,7 +44042,7 @@
         <v>45180</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44099,7 +44099,7 @@
         <v>45769.60783564814</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44156,7 +44156,7 @@
         <v>45714</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44213,7 +44213,7 @@
         <v>44418.40890046296</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>44769.56326388889</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44327,7 +44327,7 @@
         <v>45716.5465625</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44384,7 +44384,7 @@
         <v>45048.43734953704</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44441,7 +44441,7 @@
         <v>44488</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44503,7 +44503,7 @@
         <v>45769.35443287037</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>45923.58583333333</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44617,7 +44617,7 @@
         <v>45923.41541666666</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44674,7 +44674,7 @@
         <v>45923.41280092593</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44731,7 +44731,7 @@
         <v>45915</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>45915</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44855,7 +44855,7 @@
         <v>45881.41793981481</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44912,7 +44912,7 @@
         <v>45881.37207175926</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44969,7 +44969,7 @@
         <v>45923.41530092592</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45026,7 +45026,7 @@
         <v>45921.69402777778</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>45921.83252314815</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>

--- a/Översikt EMMABODA.xlsx
+++ b/Översikt EMMABODA.xlsx
@@ -567,7 +567,7 @@
         <v>44314</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         <v>45377.5588425926</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>44811</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>45369</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>45818</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>44238</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44445</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44120</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>44762</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>45867.57765046296</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>44984.36140046296</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>45161.33116898148</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>45229.67172453704</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>44495</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>44966.54540509259</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>44488</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45335</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45068.42262731482</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>45104</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>44570.72098379629</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44405.32738425926</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>44140</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>44120.38783564815</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>44459.43425925926</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>44105</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>44379.56671296297</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44530.4546875</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>44496.52702546296</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>44441.48626157407</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>44488</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>44764.45645833333</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>44120.39879629629</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>44530.4562037037</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>44496.5110300926</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>44405.31638888889</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>44405.31894675926</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>44405</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>44405.32319444444</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>44228</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>44454.86018518519</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>44117.6835300926</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>44264.36884259259</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>44454</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>44251</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>44529</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>44490</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>44601.34255787037</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>44110</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>44600</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>44431</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>44211</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>44383.5654050926</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>44280.65521990741</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>44251</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>44507</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44507.56921296296</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>44507</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>44507</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>44297</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>44416</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>44416</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>44442</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44238</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>44240</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>44211</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>44728.83878472223</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>44599.69461805555</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>44691</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>44628.35012731481</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>44326.44194444444</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>44504.38268518518</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>44379</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>44387</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>44383.6131712963</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>44515.44268518518</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>44851.40596064815</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>44860.88715277778</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>44239</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>44118</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44240.59631944444</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>44648.3578587963</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>44523</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>44462.69965277778</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>44278</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>44628</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>44347.43119212963</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>44788.65715277778</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44382.6675925926</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>44416</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>44361.39021990741</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         <v>44347.44501157408</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44405</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>44627.34532407407</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>44392.4420949074</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>44109</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>44112</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>44462</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>44240.57777777778</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>44148</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>44120</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>44498</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>44768.83986111111</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>44851.49548611111</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>44529.29797453704</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>44249</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>44172</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>44277</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>44320</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>44208</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>44208</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
         <v>44385</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>44347.43444444444</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>44813</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>44809.43158564815</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>44771</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>44202</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>44202</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>44412</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>44587.42887731481</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>44433</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>44251</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>44496</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>44466.39774305555</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>44487</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>44507</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>44507</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>44405</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>44405</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>44383.61637731481</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>44416</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>44652</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>44147</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>44628.36534722222</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>44600</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>44421</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>44120</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>44501</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>44600.45505787037</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>44110</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>44293</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>44148</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>44148</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44852.48653935185</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>44295</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>44839.33949074074</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>44452.30709490741</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>44210.32178240741</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>44382.66943287037</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>44180</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>44238</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>44722.49396990741</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>44532.70575231482</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44120.39627314815</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>44655.9318287037</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>44385</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>44615</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>44412</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>44470.31766203704</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>44589.43354166667</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10299,7 +10299,7 @@
         <v>44622.48368055555</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>44593.62412037037</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>44652</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>44524.72388888889</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>44110</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>44699.83193287037</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>44712.48467592592</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>44162.37409722222</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>44167</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>44551</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44340</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>44820</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -10993,7 +10993,7 @@
         <v>44431.41373842592</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11050,7 +11050,7 @@
         <v>44706</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>44454</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>44383.559375</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>44383.61515046296</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>44302.5521875</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>44530</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         <v>44600.45703703703</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>44725</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>44788.66310185185</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>45048.43734953704</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>45187.44503472222</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>45219</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>45335</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>45204</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
         <v>44600.45854166667</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>45190</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
         <v>44284.40975694444</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>44302.54723379629</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>44256</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         <v>44743.38194444445</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         <v>44739.37986111111</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         <v>45211</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>45719</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>45348.45074074074</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>45069</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>45069</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>45397.44292824074</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>44116.37994212963</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>45719</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>45078.59818287037</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>45411.45418981482</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>44315</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>44771.43327546296</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>45440</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         <v>45422.39476851852</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>44236.8744212963</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>44841.3953125</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>44847.55930555556</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>44148</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>44743.42285879629</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>44382</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>45229.67283564815</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
         <v>45385.48972222222</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>44488</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>45392.58570601852</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>44223</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>44897.54603009259</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>45296</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>45852.58133101852</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>45851.91112268518</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>45851.91469907408</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>45852</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>45554</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>45166</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>45166</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>45252.41863425926</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>45323.39561342593</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>45392.58935185185</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>44995.57965277778</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>44973.864375</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>44487.60532407407</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         <v>45323</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>45524.50288194444</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>44594</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>45897.39096064815</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
         <v>45856.47141203703</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>44524</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>45897.60010416667</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>45376.6791087963</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15018,7 +15018,7 @@
         <v>44978.31736111111</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
         <v>45897.63128472222</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
         <v>45637.58159722222</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         <v>45707</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15246,7 +15246,7 @@
         <v>45855.72674768518</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>44424</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
         <v>45466.85056712963</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>45763</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>45126.47204861111</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>44953</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44690</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>45461.49600694444</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>45327.39550925926</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>44488</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>45296</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>45021.50722222222</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>45021.50942129629</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>44861</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>45902.4652199074</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>45743</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>44235</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16220,7 +16220,7 @@
         <v>44326.32891203704</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16277,7 +16277,7 @@
         <v>44326.34681712963</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45048.435</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>45857</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>44993.56126157408</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>45902.47142361111</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>44424</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>44143</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         <v>45238</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>45901.39177083333</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         <v>44978.32152777778</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>45769.60783564814</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>45182</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>44530.53258101852</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>45861.33920138889</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17080,7 +17080,7 @@
         <v>44586</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>44347.43795138889</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>44278</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>44222</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>45400.91444444445</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>44416</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>44748.54626157408</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>44907.44033564815</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>44447</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>44589.42831018518</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>45904.42120370371</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>45474.61877314815</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>45062.65315972222</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>44405.3347337963</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>45905.41212962963</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>45191.58287037037</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>45750.91766203703</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>45524.58461805555</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>45095</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>44507</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>44777</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>44960</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>45863</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>44893.78201388889</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>45790.40994212963</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>45161.329375</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>44938.51150462963</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>45323.75855324074</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>45362.96539351852</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>45009.46947916667</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         <v>45009</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>44979.50945601852</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>45273.62567129629</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>45909.39206018519</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>45606.57038194445</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>45422.47181712963</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45559.60966435185</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>45909.83339120371</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>45909.37060185185</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>45084</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>45355.42155092592</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45370.74839120371</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>45091.60043981481</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19546,7 +19546,7 @@
         <v>45149.35745370371</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>45191.37449074074</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45477.50987268519</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45514.38017361111</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>44239</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>45155</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>44700.61766203704</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>45251.67181712963</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>44930.5281712963</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>45230.63987268518</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>45908</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20173,7 +20173,7 @@
         <v>44951</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>45181.58443287037</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>45161</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>44519</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>44530.5225462963</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>45908</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>44400.37826388889</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>44965.4890162037</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>44404</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45189.50841435185</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45189.50895833333</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>45632</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>45099.4612037037</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>44728.36835648148</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>44550.40824074074</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>45425.51765046296</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>45629.44709490741</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>45099</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21209,7 +21209,7 @@
         <v>45036.45335648148</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>44852.5103125</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>45258</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>45070.62878472222</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>44834.45706018519</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45574.38966435185</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>45009.36045138889</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>45009.40710648148</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21665,7 +21665,7 @@
         <v>44896.4815625</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>44900.36804398148</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>45537</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>45051</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>45051.4380787037</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>45562.50462962963</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         <v>45590.56064814814</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>44808.80826388889</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>45915</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>45107</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>44126.66101851852</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>45915.56546296296</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>45915</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>44944</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>45915.56016203704</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>44922.58392361111</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>45475.36099537037</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>45048</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>45915.55810185185</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>44743.42150462963</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>44487</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>45514.3787037037</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>45514.3809375</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>45514.38158564815</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>45092</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>45092</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>45076.58376157407</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>45392.57063657408</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>45217</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>45229.52315972222</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>44893.57989583333</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>45688</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>45515.76115740741</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>44455</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23618,7 +23618,7 @@
         <v>45587.54915509259</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>44683</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23732,7 +23732,7 @@
         <v>45740.50475694444</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -23789,7 +23789,7 @@
         <v>45117</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -23846,7 +23846,7 @@
         <v>45673.67064814815</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -23903,7 +23903,7 @@
         <v>45180</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>45668.41509259259</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>45714</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24074,7 +24074,7 @@
         <v>44239</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24131,7 +24131,7 @@
         <v>45915</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24193,7 +24193,7 @@
         <v>45915</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>44473</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>44145</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>44235</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         <v>45079</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>44207.35459490741</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>45757.64254629629</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24597,7 +24597,7 @@
         <v>45349.81209490741</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>45349.86459490741</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>45641.74149305555</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>45921.69402777778</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -24825,7 +24825,7 @@
         <v>45554</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>45349.64855324074</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -24944,7 +24944,7 @@
         <v>44995</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>45645.58637731482</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>45921.83252314815</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25115,7 +25115,7 @@
         <v>45923.41280092593</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>45155</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>45614.54209490741</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>44897.66574074074</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25343,7 +25343,7 @@
         <v>45923.58583333333</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>45881.37207175926</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>45881.41793981481</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>44791.33793981482</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25571,7 +25571,7 @@
         <v>45113.63261574074</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>45310.58832175926</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>44911</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -25742,7 +25742,7 @@
         <v>45728</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -25799,7 +25799,7 @@
         <v>45923.41530092592</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>45394.41221064814</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>44900</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -25970,7 +25970,7 @@
         <v>45923.41541666666</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>44949</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26084,7 +26084,7 @@
         <v>45596.75166666666</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>45349.90940972222</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>45189.35297453704</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>45102</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26312,7 +26312,7 @@
         <v>45007.53736111111</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>45400.68645833333</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26426,7 +26426,7 @@
         <v>45102</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>44729.41611111111</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26540,7 +26540,7 @@
         <v>44580.64971064815</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>45615</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         <v>45722</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26711,7 +26711,7 @@
         <v>45022.634375</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>45022.64363425926</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>44839</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -26882,7 +26882,7 @@
         <v>45113</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>44955</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>45606.56679398148</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27053,7 +27053,7 @@
         <v>45007.52546296296</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27110,7 +27110,7 @@
         <v>44781</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27167,7 +27167,7 @@
         <v>45148.50620370371</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>45636.63569444444</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27281,7 +27281,7 @@
         <v>45636.63883101852</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>45392.57234953704</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27395,7 +27395,7 @@
         <v>45392.58719907407</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>45726.59443287037</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27509,7 +27509,7 @@
         <v>45098.91159722222</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27566,7 +27566,7 @@
         <v>44984.56648148148</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>44761.65730324074</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>45211</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>45706.44140046297</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -27794,7 +27794,7 @@
         <v>45113.64193287037</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -27851,7 +27851,7 @@
         <v>44445</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>45164.64133101852</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -27965,7 +27965,7 @@
         <v>45742.80981481481</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>44683.43862268519</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>45691.394375</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>45040</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28193,7 +28193,7 @@
         <v>44349.62881944444</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28250,7 +28250,7 @@
         <v>45722</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>45211</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28364,7 +28364,7 @@
         <v>45615</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>45884.31863425926</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>45126.36510416667</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28535,7 +28535,7 @@
         <v>44698.34013888889</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28592,7 +28592,7 @@
         <v>45445.39274305556</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>45317.44657407407</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>45021.67435185185</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>45373.48118055556</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>45067</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>45637.57834490741</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -28934,7 +28934,7 @@
         <v>44278.36359953704</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>45926.33395833334</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>45749.44238425926</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>45716</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29162,7 +29162,7 @@
         <v>45716</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29219,7 +29219,7 @@
         <v>45204</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>45028</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>45335.67450231482</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>44228</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>45369.42106481481</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>45772.39268518519</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>45273.62960648148</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
         <v>45200.41958333334</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         <v>45740.50775462963</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -29742,7 +29742,7 @@
         <v>45196.6208449074</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -29799,7 +29799,7 @@
         <v>45204</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>45595.51280092593</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>45433.48228009259</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -29975,7 +29975,7 @@
         <v>44518</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30032,7 +30032,7 @@
         <v>45222</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30089,7 +30089,7 @@
         <v>45579.47649305555</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         <v>44433</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>45211</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>45716.34835648148</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>45237.5672337963</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30374,7 +30374,7 @@
         <v>44879</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30431,7 +30431,7 @@
         <v>45049</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30488,7 +30488,7 @@
         <v>44531.67679398148</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>44504.38146990741</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>45103.68170138889</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30659,7 +30659,7 @@
         <v>45474.4828587963</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -30716,7 +30716,7 @@
         <v>44418.40890046296</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -30773,7 +30773,7 @@
         <v>45691.38957175926</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -30830,7 +30830,7 @@
         <v>45341.38545138889</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>44690.6797337963</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -30944,7 +30944,7 @@
         <v>44524</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>45665.4533912037</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>45126.47646990741</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>45415</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31172,7 +31172,7 @@
         <v>45202.46894675926</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>45740.36450231481</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31286,7 +31286,7 @@
         <v>45700</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>45281</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>45068.41424768518</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31462,7 +31462,7 @@
         <v>44449</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>45155</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>45755.52962962963</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45111.65074074074</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -31690,7 +31690,7 @@
         <v>45772.39434027778</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -31747,7 +31747,7 @@
         <v>45049.61376157407</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -31804,7 +31804,7 @@
         <v>44897.65846064815</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -31861,7 +31861,7 @@
         <v>45692.20631944444</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -31918,7 +31918,7 @@
         <v>45716.35474537037</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -31975,7 +31975,7 @@
         <v>45727.45439814815</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32032,7 +32032,7 @@
         <v>45084</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32089,7 +32089,7 @@
         <v>44519</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32146,7 +32146,7 @@
         <v>45117</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32203,7 +32203,7 @@
         <v>45099.49768518518</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32260,7 +32260,7 @@
         <v>45561</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>44593.62643518519</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>45574.45165509259</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32436,7 +32436,7 @@
         <v>44816.64091435185</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32493,7 +32493,7 @@
         <v>44608</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>44979.50762731482</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>45551</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32664,7 +32664,7 @@
         <v>45523.52064814815</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -32721,7 +32721,7 @@
         <v>45215</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -32778,7 +32778,7 @@
         <v>44949.42457175926</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -32835,7 +32835,7 @@
         <v>45684.66949074074</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -32892,7 +32892,7 @@
         <v>45624.64013888889</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -32949,7 +32949,7 @@
         <v>45534.66148148148</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>45777.37217592593</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33063,7 +33063,7 @@
         <v>45777.3700462963</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33120,7 +33120,7 @@
         <v>45484.49533564815</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33177,7 +33177,7 @@
         <v>45777.51607638889</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33234,7 +33234,7 @@
         <v>45351.58540509259</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33291,7 +33291,7 @@
         <v>45779.45815972222</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33348,7 +33348,7 @@
         <v>45779.46054398148</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33405,7 +33405,7 @@
         <v>45782.455</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33462,7 +33462,7 @@
         <v>45349.85878472222</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33519,7 +33519,7 @@
         <v>45107</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33576,7 +33576,7 @@
         <v>45317.45069444444</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>45107.60460648148</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -33690,7 +33690,7 @@
         <v>44210</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -33747,7 +33747,7 @@
         <v>45415.60552083333</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -33804,7 +33804,7 @@
         <v>45638</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>44236.88402777778</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>45610.70957175926</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -33975,7 +33975,7 @@
         <v>45582</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34032,7 +34032,7 @@
         <v>45565.4407175926</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34089,7 +34089,7 @@
         <v>45445.3777662037</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>45548</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>45740.51246527778</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>44759.39475694444</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34317,7 +34317,7 @@
         <v>44895</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34374,7 +34374,7 @@
         <v>45317.44828703703</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>45609.51984953704</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>45688</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>45211.67291666667</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>45211</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>44159</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>45484.35097222222</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
         <v>45539.28254629629</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>45386.35418981482</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -34887,7 +34887,7 @@
         <v>45775.59086805556</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>45126.47756944445</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>44453</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35058,7 +35058,7 @@
         <v>44959</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>45566.63414351852</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>45789.54855324074</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35229,7 +35229,7 @@
         <v>45481.92570601852</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>44977.37475694445</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35343,7 +35343,7 @@
         <v>45400</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>45327.39255787037</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>45126.38699074074</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
         <v>44728.83686342592</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         <v>45093.61918981482</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>45455.38807870371</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>45771</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>44203.61291666667</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>44852.57822916667</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -35856,7 +35856,7 @@
         <v>45121</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>45341.37961805556</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -35970,7 +35970,7 @@
         <v>44953</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>45323.40695601852</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>44953</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>44572</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>45531.38554398148</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>45600.65333333334</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>44223</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>44593.76921296296</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>45795.67989583333</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>45769.35443287037</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36540,7 +36540,7 @@
         <v>45126.31585648148</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -36597,7 +36597,7 @@
         <v>45003.90380787037</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -36654,7 +36654,7 @@
         <v>44984.39417824074</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>45019.67677083334</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -36768,7 +36768,7 @@
         <v>44980</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -36825,7 +36825,7 @@
         <v>45797.45761574074</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -36882,7 +36882,7 @@
         <v>44271</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>44840</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37001,7 +37001,7 @@
         <v>45797.44099537037</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>45475.46671296296</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37115,7 +37115,7 @@
         <v>45800.58695601852</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>45800.5805787037</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>45132</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37286,7 +37286,7 @@
         <v>45537</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>44977</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37400,7 +37400,7 @@
         <v>45799.55665509259</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37457,7 +37457,7 @@
         <v>45665.45535879629</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37514,7 +37514,7 @@
         <v>45803.56060185185</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>45804.56436342592</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -37628,7 +37628,7 @@
         <v>45804.35590277778</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         <v>44958</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>44600.50372685185</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>45037.64929398148</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>44982.67675925926</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>44993</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>45433</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>45146.35854166667</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>45813.45756944444</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38141,7 +38141,7 @@
         <v>45818</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38198,7 +38198,7 @@
         <v>44494</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38255,7 +38255,7 @@
         <v>45818</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38312,7 +38312,7 @@
         <v>45818</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38369,7 +38369,7 @@
         <v>45819.69038194444</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38426,7 +38426,7 @@
         <v>45559</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38488,7 +38488,7 @@
         <v>45825.73362268518</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>45826.36164351852</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -38602,7 +38602,7 @@
         <v>45826.73186342593</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>45826.35939814815</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>45826.3639699074</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>45826.36921296296</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -38830,7 +38830,7 @@
         <v>45743</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -38887,7 +38887,7 @@
         <v>45825.44528935185</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>45826.35645833334</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>45825.4341087963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>45126</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>45126</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>45191.56679398148</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39229,7 +39229,7 @@
         <v>45126</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39286,7 +39286,7 @@
         <v>45205.49876157408</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39343,7 +39343,7 @@
         <v>45167.65172453703</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39400,7 +39400,7 @@
         <v>45832.38621527778</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>45832.7072800926</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39514,7 +39514,7 @@
         <v>45681.58681712963</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -39571,7 +39571,7 @@
         <v>45832.40292824074</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>45741.70216435185</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -39685,7 +39685,7 @@
         <v>45644.45738425926</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -39742,7 +39742,7 @@
         <v>45078.5972337963</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -39804,7 +39804,7 @@
         <v>45078.59965277778</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         <v>45084.66810185185</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -39923,7 +39923,7 @@
         <v>45835.51372685185</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -39980,7 +39980,7 @@
         <v>45072</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40037,7 +40037,7 @@
         <v>45622.56673611111</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40094,7 +40094,7 @@
         <v>45159.4650925926</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
         <v>45573.3758912037</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40208,7 +40208,7 @@
         <v>45841.44533564815</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40265,7 +40265,7 @@
         <v>45841.44762731482</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40322,7 +40322,7 @@
         <v>45776</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40379,7 +40379,7 @@
         <v>45776</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>45805</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40493,7 +40493,7 @@
         <v>45805</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -40550,7 +40550,7 @@
         <v>45841.65936342593</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -40607,7 +40607,7 @@
         <v>44299</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -40664,7 +40664,7 @@
         <v>45225.62575231482</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -40721,7 +40721,7 @@
         <v>45841.36670138889</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -40778,7 +40778,7 @@
         <v>45621</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -40835,7 +40835,7 @@
         <v>45327.37474537037</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -40892,7 +40892,7 @@
         <v>45846</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -40949,7 +40949,7 @@
         <v>45888.33114583333</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41006,7 +41006,7 @@
         <v>45063</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41068,7 +41068,7 @@
         <v>45887.58094907407</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41125,7 +41125,7 @@
         <v>44783.34944444444</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>45887.57563657407</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>45845</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>45845.41</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45727.64369212963</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41410,7 +41410,7 @@
         <v>45091</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41467,7 +41467,7 @@
         <v>45887.56543981482</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41524,7 +41524,7 @@
         <v>45887.5702662037</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -41581,7 +41581,7 @@
         <v>44652</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -41638,7 +41638,7 @@
         <v>44665.90422453704</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -41695,7 +41695,7 @@
         <v>45230</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -41752,7 +41752,7 @@
         <v>44376.82413194444</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -41809,7 +41809,7 @@
         <v>45232</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -41866,7 +41866,7 @@
         <v>45772.39609953704</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -41923,7 +41923,7 @@
         <v>45775.59498842592</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -41980,7 +41980,7 @@
         <v>45849.46575231481</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42037,7 +42037,7 @@
         <v>45716.39373842593</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42094,7 +42094,7 @@
         <v>45852.5841087963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         <v>45182.57702546296</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42208,7 +42208,7 @@
         <v>45818</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42265,7 +42265,7 @@
         <v>45392.5746412037</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42322,7 +42322,7 @@
         <v>44699.83489583333</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42379,7 +42379,7 @@
         <v>45148.51032407407</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>45531.50122685185</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42493,7 +42493,7 @@
         <v>45126</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>45434.59488425926</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -42607,7 +42607,7 @@
         <v>44619</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -42664,7 +42664,7 @@
         <v>45408</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>45394</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -42778,7 +42778,7 @@
         <v>44728.36712962963</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -42835,7 +42835,7 @@
         <v>45188</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -42897,7 +42897,7 @@
         <v>45188</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -42959,7 +42959,7 @@
         <v>45400.62210648148</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43016,7 +43016,7 @@
         <v>45107.47519675926</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43073,7 +43073,7 @@
         <v>44673.38012731481</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43130,7 +43130,7 @@
         <v>44273</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43187,7 +43187,7 @@
         <v>45164.64883101852</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43244,7 +43244,7 @@
         <v>44749.78425925926</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43301,7 +43301,7 @@
         <v>44726</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43358,7 +43358,7 @@
         <v>45707</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43415,7 +43415,7 @@
         <v>44802.69710648148</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43472,7 +43472,7 @@
         <v>45401.43559027778</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -43529,7 +43529,7 @@
         <v>45258.50520833334</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -43586,7 +43586,7 @@
         <v>45258</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -43643,7 +43643,7 @@
         <v>45736.56527777778</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -43700,7 +43700,7 @@
         <v>45735.47873842593</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -43757,7 +43757,7 @@
         <v>45475.36554398148</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -43814,7 +43814,7 @@
         <v>45716.5465625</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -43871,7 +43871,7 @@
         <v>44384</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -43933,7 +43933,7 @@
         <v>45757.63991898148</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -43990,7 +43990,7 @@
         <v>44799.28053240741</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44047,7 +44047,7 @@
         <v>44827</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44104,7 +44104,7 @@
         <v>45301</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44161,7 +44161,7 @@
         <v>45727.45094907407</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>45309.61168981482</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44275,7 +44275,7 @@
         <v>45126.475625</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44332,7 +44332,7 @@
         <v>45307.37699074074</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44389,7 +44389,7 @@
         <v>45716.34990740741</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44446,7 +44446,7 @@
         <v>45190</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -44503,7 +44503,7 @@
         <v>45310.58383101852</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>45477.69497685185</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>44851.49424768519</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
         <v>45089.38663194444</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>44893.48324074074</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>45159.46884259259</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>44769.56326388889</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -44907,7 +44907,7 @@
         <v>45551.56715277778</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -44969,7 +44969,7 @@
         <v>45187.47203703703</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45026,7 +45026,7 @@
         <v>45401.4321412037</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>44851.4281712963</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45140,7 +45140,7 @@
         <v>45196</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>

--- a/Översikt EMMABODA.xlsx
+++ b/Översikt EMMABODA.xlsx
@@ -567,7 +567,7 @@
         <v>44314</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         <v>45377.5588425926</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>44811</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         <v>45369</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>45818</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>44238</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>44445</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>44120</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>44762</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>45867.57765046296</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>44984.36140046296</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>45161.33116898148</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>45229.67172453704</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>44495</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>44966.54540509259</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>44488</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45335</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45068.42262731482</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>45104</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>44570.72098379629</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44405.32738425926</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>44140</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>44120.38783564815</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>44459.43425925926</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>44105</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>44379.56671296297</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44530.4546875</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>44496.52702546296</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>44441.48626157407</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>44488</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>44764.45645833333</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>44120.39879629629</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>44530.4562037037</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>44496.5110300926</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>44405.31638888889</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>44405.31894675926</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>44405</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>44405.32319444444</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>44228</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>44454.86018518519</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>44117.6835300926</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>44264.36884259259</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>44454</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>44251</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>44529</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>44490</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>44601.34255787037</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>44110</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>44600</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>44431</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>44211</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>44383.5654050926</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>44280.65521990741</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>44251</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>44507</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44507.56921296296</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>44507</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>44507</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>44297</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>44416</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>44416</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>44442</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44238</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>44240</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>44211</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>44728.83878472223</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>44599.69461805555</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>44691</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>44628.35012731481</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>44326.44194444444</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>44504.38268518518</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>44379</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5290,7 